--- a/research/traditional_assets/database/data/united_states/united_states_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ25"/>
+  <dimension ref="A1:AQ26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03759999999999999</v>
+        <v>0.03105</v>
       </c>
       <c r="E2">
-        <v>0.08460000000000001</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F2">
-        <v>0.0949</v>
+        <v>0.0825</v>
       </c>
       <c r="G2">
-        <v>0.08495091549977773</v>
+        <v>0.1429236371297488</v>
       </c>
       <c r="H2">
-        <v>0.08495091549977773</v>
+        <v>0.1429236371297488</v>
       </c>
       <c r="I2">
-        <v>0.1209201631006142</v>
+        <v>0.08391171025722445</v>
       </c>
       <c r="J2">
-        <v>0.1029006790194621</v>
+        <v>0.07314289201831981</v>
       </c>
       <c r="K2">
-        <v>21895.538</v>
+        <v>15306.226</v>
       </c>
       <c r="L2">
-        <v>0.0887218012818253</v>
+        <v>0.06068823406214149</v>
       </c>
       <c r="M2">
-        <v>16589.98</v>
+        <v>19119.079</v>
       </c>
       <c r="N2">
-        <v>0.07950830357159974</v>
+        <v>0.0915357874053616</v>
       </c>
       <c r="O2">
-        <v>0.7576877078791121</v>
+        <v>1.249104710723597</v>
       </c>
       <c r="P2">
-        <v>5767.791</v>
+        <v>5853.451</v>
       </c>
       <c r="Q2">
-        <v>0.02764242499180474</v>
+        <v>0.02802437535425745</v>
       </c>
       <c r="R2">
-        <v>0.2634231230125517</v>
+        <v>0.3824228781150886</v>
       </c>
       <c r="S2">
-        <v>10822.189</v>
+        <v>13265.628</v>
       </c>
       <c r="T2">
-        <v>0.6523328539274912</v>
+        <v>0.6938424178277625</v>
       </c>
       <c r="U2">
-        <v>69393.99000000001</v>
+        <v>67845.88</v>
       </c>
       <c r="V2">
-        <v>0.3325741455363151</v>
+        <v>0.3248234942702875</v>
       </c>
       <c r="W2">
-        <v>0.07343787297332036</v>
+        <v>0.07248349629266004</v>
       </c>
       <c r="X2">
-        <v>0.06103450612888447</v>
+        <v>0.09477540510670333</v>
       </c>
       <c r="Y2">
-        <v>0.01240336684443588</v>
+        <v>-0.02229190881404329</v>
       </c>
       <c r="Z2">
-        <v>0.6262601513531455</v>
+        <v>0.6495091917970077</v>
       </c>
       <c r="AA2">
-        <v>0.07267286532989904</v>
+        <v>0.05599746604142315</v>
       </c>
       <c r="AB2">
-        <v>0.05391755155487555</v>
+        <v>0.08369078258206245</v>
       </c>
       <c r="AC2">
-        <v>0.0199455204384166</v>
+        <v>-0.02714799197968988</v>
       </c>
       <c r="AD2">
-        <v>190108.28</v>
+        <v>190586.59</v>
       </c>
       <c r="AE2">
-        <v>3110.385723057195</v>
+        <v>2514.311398276825</v>
       </c>
       <c r="AF2">
-        <v>193218.6657230572</v>
+        <v>193100.9013982768</v>
       </c>
       <c r="AG2">
-        <v>123824.6757230572</v>
+        <v>125255.0213982768</v>
       </c>
       <c r="AH2">
-        <v>0.4807919116402204</v>
+        <v>0.480385285428418</v>
       </c>
       <c r="AI2">
-        <v>0.410696809437649</v>
+        <v>0.615141850023759</v>
       </c>
       <c r="AJ2">
-        <v>0.3724253403400483</v>
+        <v>0.3748747239067743</v>
       </c>
       <c r="AK2">
-        <v>0.3087346850080135</v>
+        <v>0.509028278512668</v>
       </c>
       <c r="AL2">
-        <v>2286.358</v>
+        <v>2244.076</v>
       </c>
       <c r="AM2">
-        <v>2286.358</v>
+        <v>2244.076</v>
       </c>
       <c r="AN2">
-        <v>5.703391498092687</v>
+        <v>9.08105978373645</v>
       </c>
       <c r="AO2">
-        <v>13.01802254939953</v>
+        <v>9.374119236603395</v>
       </c>
       <c r="AP2">
-        <v>3.71483347686365</v>
+        <v>5.968144650318473</v>
       </c>
       <c r="AQ2">
-        <v>13.01802254939953</v>
+        <v>9.374119236603395</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pekin Life Insurance Company (OTCPK:PKIN)</t>
+          <t>American Equity Investment Life Holding Company (NYSE:AEL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,106 +725,112 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0171</v>
+        <v>-0.107</v>
+      </c>
+      <c r="E3">
+        <v>0.388</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.3417633534727049</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.3417633534727049</v>
       </c>
       <c r="I3">
-        <v>0.01169325660240491</v>
+        <v>0.9267251592520813</v>
       </c>
       <c r="J3">
-        <v>0.005997834205543898</v>
+        <v>0.7266454482190176</v>
       </c>
       <c r="K3">
-        <v>1.19</v>
+        <v>1332.5</v>
       </c>
       <c r="L3">
-        <v>0.004798387096774193</v>
+        <v>0.7124525477196172</v>
       </c>
       <c r="M3">
-        <v>0.171</v>
+        <v>554</v>
       </c>
       <c r="N3">
-        <v>0.001805702217529039</v>
+        <v>0.1416988515742896</v>
       </c>
       <c r="O3">
-        <v>0.1436974789915967</v>
+        <v>0.4157598499061914</v>
       </c>
       <c r="P3">
-        <v>0.171</v>
+        <v>31.5</v>
       </c>
       <c r="Q3">
-        <v>0.001805702217529039</v>
+        <v>0.008056884159909967</v>
       </c>
       <c r="R3">
-        <v>0.1436974789915967</v>
+        <v>0.02363977485928705</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>522.5</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.9431407942238267</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1808.1</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.4624651507788322</v>
+      </c>
+      <c r="W3">
+        <v>0.2090130505709625</v>
       </c>
       <c r="X3">
-        <v>0.05498833953521853</v>
-      </c>
-      <c r="Z3">
-        <v>46253.01165326244</v>
-      </c>
-      <c r="AA3">
-        <v>277.417895403358</v>
+        <v>0.09431889800585067</v>
+      </c>
+      <c r="Y3">
+        <v>0.1146941525651118</v>
       </c>
       <c r="AB3">
-        <v>0.0549865079847557</v>
-      </c>
-      <c r="AC3">
-        <v>277.3629088953732</v>
+        <v>0.08346477127854775</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>873.5</v>
       </c>
       <c r="AE3">
-        <v>0.005361813017909882</v>
+        <v>10.77967325416197</v>
       </c>
       <c r="AF3">
-        <v>0.005361813017909882</v>
+        <v>884.2796732541619</v>
       </c>
       <c r="AG3">
-        <v>0.005361813017909882</v>
+        <v>-923.820326745838</v>
       </c>
       <c r="AH3">
-        <v>5.661572814109521e-05</v>
+        <v>0.1844562834063732</v>
       </c>
       <c r="AI3">
-        <v>1</v>
+        <v>0.2159476575172314</v>
       </c>
       <c r="AJ3">
-        <v>5.661572814109521e-05</v>
+        <v>-0.3093963681862009</v>
       </c>
       <c r="AK3">
-        <v>1</v>
+        <v>-0.4039830935838307</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>33.5</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>33.5</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.499197055680331</v>
+      </c>
+      <c r="AO3">
+        <v>51.72835820895523</v>
       </c>
       <c r="AP3">
-        <v>5.361813017909882</v>
+        <v>-0.5279546503596607</v>
+      </c>
+      <c r="AQ3">
+        <v>51.72835820895523</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Midwest Holding Inc. (NasdaqCM:MDWT)</t>
+          <t>Novus Acquisition &amp; Development Corp. (OTCPK:NDEV)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -843,35 +849,32 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.301</v>
-      </c>
       <c r="G4">
-        <v>-0.8181818181818182</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>-0.8181818181818182</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>-1.532529883371379</v>
+        <v>0.3609022556390977</v>
       </c>
       <c r="J4">
-        <v>-1.532529883371379</v>
+        <v>0.3609022556390977</v>
       </c>
       <c r="K4">
-        <v>-21.6</v>
+        <v>0.096</v>
       </c>
       <c r="L4">
-        <v>-1.636363636363636</v>
+        <v>0.3609022556390977</v>
       </c>
       <c r="M4">
-        <v>0.025</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.0003810975609756098</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0.001157407407407407</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -880,76 +883,46 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>0.025</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.219512195121951</v>
-      </c>
-      <c r="W4">
-        <v>-0.8605577689243028</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.05519396175865277</v>
-      </c>
-      <c r="Y4">
-        <v>-0.9157517306829556</v>
-      </c>
-      <c r="Z4">
-        <v>-0.1199639805994472</v>
-      </c>
-      <c r="AA4">
-        <v>0.1838483851968372</v>
+        <v>0.08626698429789872</v>
       </c>
       <c r="AB4">
-        <v>0.05496384927652202</v>
-      </c>
-      <c r="AC4">
-        <v>0.1288845359203152</v>
+        <v>0.08626698429789872</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>0.4669723025110362</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.4669723025110362</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-79.53302769748896</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>0.007068165624010105</v>
-      </c>
-      <c r="AI4">
-        <v>0.005796076098747502</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>5.708237249239269</v>
-      </c>
-      <c r="AK4">
-        <v>-140.2767425238401</v>
+        <v>0</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>-0</v>
-      </c>
-      <c r="AP4">
-        <v>3.949792793876091</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +933,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Primerica, Inc. (NYSE:PRI)</t>
+          <t>F&amp;G Annuities &amp; Life, Inc. (NYSE:FG)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,121 +942,112 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.121</v>
+        <v>0.353</v>
       </c>
       <c r="E5">
-        <v>0.158</v>
+        <v>0.665</v>
       </c>
       <c r="G5">
-        <v>0.2319700635016632</v>
+        <v>0.3436406067677946</v>
       </c>
       <c r="H5">
-        <v>0.2319700635016632</v>
+        <v>0.3436406067677946</v>
       </c>
       <c r="I5">
-        <v>0.2567200094302971</v>
+        <v>0.2790396090767829</v>
       </c>
       <c r="J5">
-        <v>0.1948222101053859</v>
+        <v>0.2115397468379067</v>
       </c>
       <c r="K5">
-        <v>438.6</v>
+        <v>702</v>
       </c>
       <c r="L5">
-        <v>0.1657846991230723</v>
+        <v>0.2047841306884481</v>
       </c>
       <c r="M5">
-        <v>91.8</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.01516703565409906</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.2093023255813953</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>71.8</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.01186267058784654</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.163702690378477</v>
+        <v>-0</v>
       </c>
       <c r="S5">
-        <v>20</v>
-      </c>
-      <c r="T5">
-        <v>0.2178649237472767</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>325.6</v>
+        <v>1384</v>
       </c>
       <c r="V5">
-        <v>0.05379506327859102</v>
-      </c>
-      <c r="W5">
-        <v>0.2549407114624506</v>
+        <v>0.5533122776156398</v>
       </c>
       <c r="X5">
-        <v>0.06485252570671038</v>
-      </c>
-      <c r="Y5">
-        <v>0.1900881857557402</v>
+        <v>0.09456836123051325</v>
       </c>
       <c r="Z5">
-        <v>0.8290538070375784</v>
+        <v>279.5833882337852</v>
       </c>
       <c r="AA5">
-        <v>0.1615180949833452</v>
+        <v>59.14299916705912</v>
       </c>
       <c r="AB5">
-        <v>0.05360595575647897</v>
+        <v>0.08502527521290887</v>
       </c>
       <c r="AC5">
-        <v>0.1079121392268662</v>
+        <v>59.05797389184621</v>
       </c>
       <c r="AD5">
-        <v>1995.5</v>
+        <v>571</v>
       </c>
       <c r="AE5">
-        <v>55.30771525603011</v>
+        <v>12.26110042394055</v>
       </c>
       <c r="AF5">
-        <v>2050.80771525603</v>
+        <v>583.2611004239405</v>
       </c>
       <c r="AG5">
-        <v>1725.20771525603</v>
+        <v>-800.7388995760595</v>
       </c>
       <c r="AH5">
-        <v>0.2530796656565902</v>
+        <v>0.1890904674716209</v>
       </c>
       <c r="AI5">
-        <v>0.4932900152492581</v>
+        <v>0.2582788590364709</v>
       </c>
       <c r="AJ5">
-        <v>0.2218115667570524</v>
+        <v>-0.4708674680236067</v>
       </c>
       <c r="AK5">
-        <v>0.450233373764361</v>
+        <v>-0.9159036118475027</v>
       </c>
       <c r="AL5">
-        <v>90.59999999999999</v>
+        <v>31</v>
       </c>
       <c r="AM5">
-        <v>90.59999999999999</v>
+        <v>31</v>
       </c>
       <c r="AN5">
-        <v>2.790362726179489</v>
+        <v>0.562007874015748</v>
       </c>
       <c r="AO5">
-        <v>7.530905077262693</v>
+        <v>30.87096774193548</v>
       </c>
       <c r="AP5">
-        <v>2.412405564303535</v>
+        <v>-0.7881288381654128</v>
       </c>
       <c r="AQ5">
-        <v>7.530905077262693</v>
+        <v>30.87096774193548</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1058,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UTG, Inc. (OTCPK:UTGN)</t>
+          <t>Midwest Holding Inc. (NasdaqCM:MDWT)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1103,34 +1067,34 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.115</v>
+        <v>0.537</v>
       </c>
       <c r="G6">
-        <v>0.09703196347031964</v>
+        <v>-0.3146666666666667</v>
       </c>
       <c r="H6">
-        <v>0.09703196347031964</v>
+        <v>-0.3146666666666667</v>
       </c>
       <c r="I6">
-        <v>0.4132420091324202</v>
+        <v>0.2041031360922816</v>
       </c>
       <c r="J6">
-        <v>0.3383561643835617</v>
+        <v>0.1020515680461408</v>
       </c>
       <c r="K6">
-        <v>14.8</v>
+        <v>9.9</v>
       </c>
       <c r="L6">
-        <v>0.3378995433789955</v>
+        <v>0.264</v>
       </c>
       <c r="M6">
-        <v>0.534</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.006202090592334495</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.03608108108108108</v>
+        <v>-0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1142,61 +1106,58 @@
         <v>-0</v>
       </c>
       <c r="S6">
-        <v>0.534</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>24.1</v>
+        <v>208.5</v>
       </c>
       <c r="V6">
-        <v>0.2799070847851336</v>
+        <v>4.389473684210526</v>
       </c>
       <c r="W6">
-        <v>0.1151750972762646</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="X6">
-        <v>0.05498669094562519</v>
+        <v>0.08824610420635261</v>
       </c>
       <c r="Y6">
-        <v>0.06018840633063941</v>
+        <v>0.03534940141162493</v>
       </c>
       <c r="Z6">
-        <v>0.4219653179190752</v>
+        <v>13.68282562269671</v>
       </c>
       <c r="AA6">
-        <v>0.1427745664739885</v>
+        <v>1.396353810098112</v>
       </c>
       <c r="AB6">
-        <v>0.05498669094562519</v>
+        <v>0.08577105061102079</v>
       </c>
       <c r="AC6">
-        <v>0.08778787552836326</v>
+        <v>1.310582759487091</v>
       </c>
       <c r="AD6">
         <v>0</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>2.640661982697205</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.640661982697205</v>
       </c>
       <c r="AG6">
-        <v>-24.1</v>
+        <v>-205.8593380173028</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.05266508016205407</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.0620738338244773</v>
       </c>
       <c r="AJ6">
-        <v>-0.3887096774193549</v>
+        <v>1.299950736058331</v>
       </c>
       <c r="AK6">
-        <v>-0.2092013888888889</v>
+        <v>1.240420337154153</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1208,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>-1.126168224299066</v>
+        <v>-24.44304654681819</v>
       </c>
     </row>
     <row r="7">
@@ -1219,7 +1180,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aflac Incorporated (NYSE:AFL)</t>
+          <t>Principal Financial Group, Inc. (NasdaqGS:PFG)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1228,121 +1189,118 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.00502</v>
+        <v>0.05139999999999999</v>
       </c>
       <c r="E7">
-        <v>0.09949999999999999</v>
+        <v>0.243</v>
+      </c>
+      <c r="F7">
+        <v>0.055</v>
       </c>
       <c r="G7">
-        <v>0.196696630208564</v>
+        <v>0.12777955332138</v>
       </c>
       <c r="H7">
-        <v>0.196696630208564</v>
+        <v>0.12777955332138</v>
       </c>
       <c r="I7">
-        <v>0.2467794704713353</v>
+        <v>0.3618397520645849</v>
       </c>
       <c r="J7">
-        <v>0.197070170691072</v>
+        <v>0.290044082043427</v>
       </c>
       <c r="K7">
-        <v>4238</v>
+        <v>5292.9</v>
       </c>
       <c r="L7">
-        <v>0.1876632865429748</v>
+        <v>0.2867117714929553</v>
       </c>
       <c r="M7">
-        <v>3012</v>
+        <v>2451.3</v>
       </c>
       <c r="N7">
-        <v>0.07797735239446392</v>
+        <v>0.1193787803523946</v>
       </c>
       <c r="O7">
-        <v>0.7107126002831524</v>
+        <v>0.4631298531995693</v>
       </c>
       <c r="P7">
-        <v>836</v>
+        <v>654.6</v>
       </c>
       <c r="Q7">
-        <v>0.02164311640165068</v>
+        <v>0.03187914560383368</v>
       </c>
       <c r="R7">
-        <v>0.1972628598395469</v>
+        <v>0.1236751119424134</v>
       </c>
       <c r="S7">
-        <v>2176</v>
+        <v>1796.7</v>
       </c>
       <c r="T7">
-        <v>0.7224435590969456</v>
+        <v>0.7329580222738955</v>
       </c>
       <c r="U7">
-        <v>6208</v>
+        <v>4239.6</v>
       </c>
       <c r="V7">
-        <v>0.1607182615089084</v>
+        <v>0.206469333489174</v>
       </c>
       <c r="W7">
-        <v>0.1304843129406694</v>
+        <v>0.3293509305755194</v>
       </c>
       <c r="X7">
-        <v>0.06324464854399352</v>
+        <v>0.09468241965674198</v>
       </c>
       <c r="Y7">
-        <v>0.06723966439667585</v>
+        <v>0.2346685109187774</v>
       </c>
       <c r="Z7">
-        <v>0.6232045907804565</v>
+        <v>1.159983389079865</v>
       </c>
       <c r="AA7">
-        <v>0.1228150350805643</v>
+        <v>0.3364463172712928</v>
       </c>
       <c r="AB7">
-        <v>0.05378126155359052</v>
+        <v>0.08336244719388838</v>
       </c>
       <c r="AC7">
-        <v>0.06903377352697374</v>
+        <v>0.2530838700774044</v>
       </c>
       <c r="AD7">
-        <v>10815</v>
+        <v>4654</v>
       </c>
       <c r="AE7">
-        <v>139.8960917291718</v>
+        <v>199.9244453065915</v>
       </c>
       <c r="AF7">
-        <v>10954.89609172917</v>
+        <v>4853.924445306591</v>
       </c>
       <c r="AG7">
-        <v>4746.896091729172</v>
+        <v>614.3244453065909</v>
       </c>
       <c r="AH7">
-        <v>0.2209472677359687</v>
+        <v>0.1911917886049032</v>
       </c>
       <c r="AI7">
-        <v>0.2461392964620812</v>
+        <v>0.3325215153977927</v>
       </c>
       <c r="AJ7">
-        <v>0.1094423212205472</v>
+        <v>0.02904864906083566</v>
       </c>
       <c r="AK7">
-        <v>0.123943418117325</v>
+        <v>0.05931075387750449</v>
       </c>
       <c r="AL7">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>1.916873449131514</v>
-      </c>
-      <c r="AO7">
-        <v>22.9297520661157</v>
+        <v>0.6636530865429863</v>
       </c>
       <c r="AP7">
-        <v>0.8413498921887933</v>
-      </c>
-      <c r="AQ7">
-        <v>22.9297520661157</v>
+        <v>0.08760170052998001</v>
       </c>
     </row>
     <row r="8">
@@ -1353,7 +1311,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Principal Financial Group, Inc. (NasdaqGS:PFG)</t>
+          <t>UTG, Inc. (OTCPK:UTGN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1362,118 +1320,118 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0358</v>
-      </c>
-      <c r="E8">
-        <v>0.0645</v>
-      </c>
-      <c r="F8">
-        <v>0.169</v>
+        <v>0.184</v>
       </c>
       <c r="G8">
-        <v>0.1395882813004513</v>
+        <v>0.2914171656686627</v>
       </c>
       <c r="H8">
-        <v>0.1395882813004513</v>
+        <v>0.2914171656686627</v>
       </c>
       <c r="I8">
-        <v>0.1489650947115544</v>
+        <v>0.499001996007984</v>
       </c>
       <c r="J8">
-        <v>0.1257140817193579</v>
+        <v>0.38562874251497</v>
       </c>
       <c r="K8">
-        <v>1711.4</v>
+        <v>19.2</v>
       </c>
       <c r="L8">
-        <v>0.1227980798897874</v>
+        <v>0.3832335329341317</v>
       </c>
       <c r="M8">
-        <v>1299.4</v>
+        <v>0.748</v>
       </c>
       <c r="N8">
-        <v>0.067774155691746</v>
+        <v>0.009444444444444445</v>
       </c>
       <c r="O8">
-        <v>0.7592614233960501</v>
+        <v>0.03895833333333334</v>
       </c>
       <c r="P8">
-        <v>639.3</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.0333446342417525</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.3735538155895757</v>
+        <v>-0</v>
       </c>
       <c r="S8">
-        <v>660.1000000000001</v>
+        <v>0.748</v>
       </c>
       <c r="T8">
-        <v>0.5080036940126212</v>
+        <v>1</v>
       </c>
       <c r="U8">
-        <v>3145.4</v>
+        <v>24.8</v>
       </c>
       <c r="V8">
-        <v>0.1640578954231321</v>
+        <v>0.3131313131313131</v>
       </c>
       <c r="W8">
-        <v>0.1093483441846795</v>
+        <v>0.138328530259366</v>
       </c>
       <c r="X8">
-        <v>0.06208341234390185</v>
+        <v>0.08986296795683044</v>
       </c>
       <c r="Y8">
-        <v>0.04726493184077763</v>
+        <v>0.04846556230253554</v>
       </c>
       <c r="Z8">
-        <v>0.9230341796031253</v>
+        <v>0.4367916303400174</v>
       </c>
       <c r="AA8">
-        <v>0.1160383942843878</v>
+        <v>0.1684394071490845</v>
       </c>
       <c r="AB8">
-        <v>0.05391755155487555</v>
+        <v>0.08540306263969002</v>
       </c>
       <c r="AC8">
-        <v>0.06212084272951223</v>
+        <v>0.08303634450939451</v>
       </c>
       <c r="AD8">
-        <v>4437.8</v>
+        <v>8</v>
       </c>
       <c r="AE8">
-        <v>235.0908226674001</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>4672.8908226674</v>
+        <v>8</v>
       </c>
       <c r="AG8">
-        <v>1527.4908226674</v>
+        <v>-16.8</v>
       </c>
       <c r="AH8">
-        <v>0.1959662082042856</v>
+        <v>0.09174311926605504</v>
       </c>
       <c r="AI8">
-        <v>0.2209886240389637</v>
+        <v>0.05434782608695653</v>
       </c>
       <c r="AJ8">
-        <v>0.07379185989757689</v>
+        <v>-0.2692307692307692</v>
       </c>
       <c r="AK8">
-        <v>0.08486064452565331</v>
+        <v>-0.1372549019607843</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="AN8">
-        <v>1.853872503968585</v>
+        <v>0.2898550724637681</v>
+      </c>
+      <c r="AO8">
+        <v>328.9473684210527</v>
       </c>
       <c r="AP8">
-        <v>0.638102942045033</v>
+        <v>-0.6086956521739131</v>
+      </c>
+      <c r="AQ8">
+        <v>328.9473684210527</v>
       </c>
     </row>
     <row r="9">
@@ -1484,7 +1442,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>National Western Life Group, Inc. (NasdaqGS:NWLI)</t>
+          <t>Aflac Incorporated (NYSE:AFL)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1493,115 +1451,121 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0414</v>
+        <v>-0.0114</v>
       </c>
       <c r="E9">
-        <v>0.113</v>
+        <v>0.128</v>
       </c>
       <c r="G9">
-        <v>0.1441810085449513</v>
+        <v>0.2678230122324159</v>
       </c>
       <c r="H9">
-        <v>0.1441810085449513</v>
+        <v>0.2678230122324159</v>
       </c>
       <c r="I9">
-        <v>0.2798816688194408</v>
+        <v>0.2660969150957289</v>
       </c>
       <c r="J9">
-        <v>0.2252059899708926</v>
+        <v>0.2532228738345085</v>
       </c>
       <c r="K9">
-        <v>187</v>
+        <v>5055</v>
       </c>
       <c r="L9">
-        <v>0.2250571669274281</v>
+        <v>0.2415424311926606</v>
       </c>
       <c r="M9">
-        <v>1.27</v>
+        <v>3374</v>
       </c>
       <c r="N9">
-        <v>0.001628831601898166</v>
+        <v>0.07542783049975968</v>
       </c>
       <c r="O9">
-        <v>0.006791443850267379</v>
+        <v>0.667457962413452</v>
       </c>
       <c r="P9">
-        <v>1.27</v>
+        <v>948</v>
       </c>
       <c r="Q9">
-        <v>0.001628831601898166</v>
+        <v>0.02119311894302673</v>
       </c>
       <c r="R9">
-        <v>0.006791443850267379</v>
+        <v>0.1875370919881306</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2426</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.7190278601066983</v>
       </c>
       <c r="U9">
-        <v>540.2</v>
+        <v>4710</v>
       </c>
       <c r="V9">
-        <v>0.6928305758625113</v>
+        <v>0.1052949263941518</v>
       </c>
       <c r="W9">
-        <v>0.08441675695196822</v>
+        <v>0.1506616595135908</v>
       </c>
       <c r="X9">
-        <v>0.05505733151989748</v>
+        <v>0.09486839055666468</v>
       </c>
       <c r="Y9">
-        <v>0.02935942543207074</v>
+        <v>0.05579326895692616</v>
       </c>
       <c r="Z9">
-        <v>0.4859170584504069</v>
+        <v>0.5470711943835191</v>
       </c>
       <c r="AA9">
-        <v>0.109431432192068</v>
+        <v>0.1385309400338718</v>
       </c>
       <c r="AB9">
-        <v>0.05497348698740829</v>
+        <v>0.08443453531164365</v>
       </c>
       <c r="AC9">
-        <v>0.05445794520465968</v>
+        <v>0.05409640472222811</v>
       </c>
       <c r="AD9">
-        <v>1.08</v>
+        <v>10712</v>
       </c>
       <c r="AE9">
-        <v>0.8116068896330357</v>
+        <v>95.61880438293053</v>
       </c>
       <c r="AF9">
-        <v>1.891606889633036</v>
+        <v>10807.61880438293</v>
       </c>
       <c r="AG9">
-        <v>-538.308393110367</v>
+        <v>6097.61880438293</v>
       </c>
       <c r="AH9">
-        <v>0.002420198570402696</v>
+        <v>0.1945947115662562</v>
       </c>
       <c r="AI9">
-        <v>0.0007394601837316642</v>
+        <v>0.3091457851659402</v>
       </c>
       <c r="AJ9">
-        <v>-2.230021167871373</v>
+        <v>0.1199631028003802</v>
       </c>
       <c r="AK9">
-        <v>-0.2667677447452753</v>
+        <v>0.2015767155220955</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="AN9">
-        <v>0.00439889864611675</v>
+        <v>1.900638750887154</v>
+      </c>
+      <c r="AO9">
+        <v>24.29824561403509</v>
       </c>
       <c r="AP9">
-        <v>-2.19255931633933</v>
+        <v>1.081905394674047</v>
+      </c>
+      <c r="AQ9">
+        <v>24.29824561403509</v>
       </c>
     </row>
     <row r="10">
@@ -1612,7 +1576,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Equity Investment Life Holding Company (NYSE:AEL)</t>
+          <t>Primerica, Inc. (NYSE:PRI)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1621,118 +1585,121 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.11</v>
+        <v>0.111</v>
+      </c>
+      <c r="E10">
+        <v>0.0295</v>
       </c>
       <c r="G10">
-        <v>0.2366547549793623</v>
+        <v>0.2594036941184812</v>
       </c>
       <c r="H10">
-        <v>0.2366547549793623</v>
+        <v>0.2594036941184812</v>
       </c>
       <c r="I10">
-        <v>0.146707532655421</v>
+        <v>0.2278177246752592</v>
       </c>
       <c r="J10">
-        <v>0.1147045047612925</v>
+        <v>0.1570636338780258</v>
       </c>
       <c r="K10">
-        <v>389.6</v>
+        <v>276</v>
       </c>
       <c r="L10">
-        <v>0.1079254272971551</v>
+        <v>0.09784805190201015</v>
       </c>
       <c r="M10">
-        <v>293.4</v>
+        <v>430.3</v>
       </c>
       <c r="N10">
-        <v>0.0814864189301783</v>
+        <v>0.08222973876817825</v>
       </c>
       <c r="O10">
-        <v>0.7530800821355235</v>
+        <v>1.559057971014493</v>
       </c>
       <c r="P10">
-        <v>28.9</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Q10">
-        <v>0.008026440037771483</v>
+        <v>0.01568919719467217</v>
       </c>
       <c r="R10">
-        <v>0.07417864476386037</v>
+        <v>0.297463768115942</v>
       </c>
       <c r="S10">
-        <v>264.5</v>
+        <v>348.1999999999999</v>
       </c>
       <c r="T10">
-        <v>0.9014996591683709</v>
+        <v>0.8092028817104345</v>
       </c>
       <c r="U10">
-        <v>12684.8</v>
+        <v>438</v>
       </c>
       <c r="V10">
-        <v>3.522968394156529</v>
+        <v>0.08370119818838503</v>
       </c>
       <c r="W10">
-        <v>0.06367365616879403</v>
+        <v>0.1314974510457859</v>
       </c>
       <c r="X10">
-        <v>0.05971465014402762</v>
+        <v>0.1009503917768379</v>
       </c>
       <c r="Y10">
-        <v>0.003959006024766412</v>
+        <v>0.03054705926894796</v>
       </c>
       <c r="Z10">
-        <v>0.8922188573910642</v>
+        <v>0.7843725644509367</v>
       </c>
       <c r="AA10">
-        <v>0.1023415221757283</v>
+        <v>0.1231964052868901</v>
       </c>
       <c r="AB10">
-        <v>0.05422456066500077</v>
+        <v>0.08183081832758599</v>
       </c>
       <c r="AC10">
-        <v>0.04811696151072748</v>
+        <v>0.04136558695930416</v>
       </c>
       <c r="AD10">
-        <v>574.4</v>
+        <v>2106.8</v>
       </c>
       <c r="AE10">
-        <v>10.2523893359779</v>
+        <v>51.52272004248191</v>
       </c>
       <c r="AF10">
-        <v>584.6523893359779</v>
+        <v>2158.322720042482</v>
       </c>
       <c r="AG10">
-        <v>-12100.14761066402</v>
+        <v>1720.322720042482</v>
       </c>
       <c r="AH10">
-        <v>0.1396934605008941</v>
+        <v>0.2920115929113927</v>
       </c>
       <c r="AI10">
-        <v>0.0840035616605596</v>
+        <v>0.5712383192132976</v>
       </c>
       <c r="AJ10">
-        <v>1.423622546155572</v>
+        <v>0.247413723004111</v>
       </c>
       <c r="AK10">
-        <v>2.113582242765809</v>
+        <v>0.5150169202874515</v>
       </c>
       <c r="AL10">
-        <v>31</v>
+        <v>92.7</v>
       </c>
       <c r="AM10">
-        <v>31</v>
+        <v>92.7</v>
       </c>
       <c r="AN10">
-        <v>1.069745786386069</v>
+        <v>3.059052431357176</v>
       </c>
       <c r="AO10">
-        <v>17.0741935483871</v>
+        <v>6.936353829557713</v>
       </c>
       <c r="AP10">
-        <v>-22.53496156190338</v>
+        <v>2.49789130409386</v>
       </c>
       <c r="AQ10">
-        <v>17.0741935483871</v>
+        <v>6.936353829557713</v>
       </c>
     </row>
     <row r="11">
@@ -1743,7 +1710,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prudential Financial, Inc. (NYSE:PRU)</t>
+          <t>Unum Group (NYSE:UNM)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1752,118 +1719,124 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0284</v>
+        <v>0.0125</v>
       </c>
       <c r="E11">
-        <v>0.0877</v>
+        <v>0.0414</v>
       </c>
       <c r="F11">
-        <v>0.0949</v>
+        <v>0.155</v>
       </c>
       <c r="G11">
-        <v>0.00282289524079722</v>
+        <v>0.1221206245194076</v>
       </c>
       <c r="H11">
-        <v>0.00282289524079722</v>
+        <v>0.1221206245194076</v>
       </c>
       <c r="I11">
-        <v>0.1262855848267936</v>
+        <v>0.1391383272396863</v>
       </c>
       <c r="J11">
-        <v>0.1063945516660884</v>
+        <v>0.1136458105747212</v>
       </c>
       <c r="K11">
-        <v>7335</v>
+        <v>1194.3</v>
       </c>
       <c r="L11">
-        <v>0.1040499326193347</v>
+        <v>0.09982113603690949</v>
       </c>
       <c r="M11">
-        <v>3912</v>
+        <v>435.9</v>
       </c>
       <c r="N11">
-        <v>0.09561355698563109</v>
+        <v>0.05340275650842266</v>
       </c>
       <c r="O11">
-        <v>0.5333333333333333</v>
+        <v>0.3649836724441095</v>
       </c>
       <c r="P11">
-        <v>1815</v>
+        <v>249.8</v>
       </c>
       <c r="Q11">
-        <v>0.0443605843376586</v>
+        <v>0.03060336906584992</v>
       </c>
       <c r="R11">
-        <v>0.2474437627811861</v>
+        <v>0.2091601775098384</v>
       </c>
       <c r="S11">
-        <v>2097</v>
+        <v>186.1</v>
       </c>
       <c r="T11">
-        <v>0.536042944785276</v>
+        <v>0.4269327827483367</v>
       </c>
       <c r="U11">
-        <v>15605</v>
+        <v>143.3</v>
       </c>
       <c r="V11">
-        <v>0.381403260930668</v>
+        <v>0.01755589586523737</v>
       </c>
       <c r="W11">
-        <v>0.1107721582071069</v>
+        <v>0.1074184670180425</v>
       </c>
       <c r="X11">
-        <v>0.07966450055848813</v>
+        <v>0.1018223453279609</v>
       </c>
       <c r="Y11">
-        <v>0.03110765764861881</v>
+        <v>0.005596121690081612</v>
       </c>
       <c r="Z11">
-        <v>0.8540139660097585</v>
+        <v>0.8445399017465589</v>
       </c>
       <c r="AA11">
-        <v>0.09086243303018632</v>
+        <v>0.09597842169668311</v>
       </c>
       <c r="AB11">
-        <v>0.05093753518039794</v>
+        <v>0.08164748812711778</v>
       </c>
       <c r="AC11">
-        <v>0.03992489784978838</v>
+        <v>0.01433093356956533</v>
       </c>
       <c r="AD11">
-        <v>34159</v>
+        <v>3485.6</v>
       </c>
       <c r="AE11">
-        <v>517.4884881759307</v>
+        <v>80.96698786748441</v>
       </c>
       <c r="AF11">
-        <v>34676.48848817593</v>
+        <v>3566.566987867484</v>
       </c>
       <c r="AG11">
-        <v>19071.48848817593</v>
+        <v>3423.266987867484</v>
       </c>
       <c r="AH11">
-        <v>0.4587371779926449</v>
+        <v>0.3040793433575519</v>
       </c>
       <c r="AI11">
-        <v>0.3566237906275616</v>
+        <v>0.2917182599610129</v>
       </c>
       <c r="AJ11">
-        <v>0.3179313266742255</v>
+        <v>0.2954717621588886</v>
       </c>
       <c r="AK11">
-        <v>0.23363192896902</v>
+        <v>0.283318133280634</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>191.9</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>191.9</v>
       </c>
       <c r="AN11">
-        <v>3.752911448033399</v>
+        <v>1.942704269312229</v>
+      </c>
+      <c r="AO11">
+        <v>8.64147993746743</v>
       </c>
       <c r="AP11">
-        <v>2.09530745859986</v>
+        <v>1.9079628736303</v>
+      </c>
+      <c r="AQ11">
+        <v>8.64147993746743</v>
       </c>
     </row>
     <row r="12">
@@ -1883,121 +1856,121 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0532</v>
+        <v>0.0496</v>
       </c>
       <c r="E12">
-        <v>0.07099999999999999</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="G12">
-        <v>0.1989691743483001</v>
+        <v>0.1973177123477725</v>
       </c>
       <c r="H12">
-        <v>0.1989691743483001</v>
+        <v>0.1973177123477725</v>
       </c>
       <c r="I12">
-        <v>0.2052202712403129</v>
+        <v>0.1843233894410516</v>
       </c>
       <c r="J12">
-        <v>0.1675125668718558</v>
+        <v>0.1502548433206263</v>
       </c>
       <c r="K12">
-        <v>771.2</v>
+        <v>706.1</v>
       </c>
       <c r="L12">
-        <v>0.1528793735751809</v>
+        <v>0.1360605827038693</v>
       </c>
       <c r="M12">
-        <v>620.4</v>
+        <v>563.9</v>
       </c>
       <c r="N12">
-        <v>0.06555506244848792</v>
+        <v>0.04809012527823024</v>
       </c>
       <c r="O12">
-        <v>0.804460580912863</v>
+        <v>0.7986120946041637</v>
       </c>
       <c r="P12">
-        <v>79.8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="Q12">
-        <v>0.008432130856526977</v>
+        <v>0.00685661654968915</v>
       </c>
       <c r="R12">
-        <v>0.1034751037344398</v>
+        <v>0.1138648916584053</v>
       </c>
       <c r="S12">
-        <v>540.6</v>
+        <v>483.5</v>
       </c>
       <c r="T12">
-        <v>0.8713733075435204</v>
+        <v>0.8574215286398298</v>
       </c>
       <c r="U12">
-        <v>96.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="V12">
-        <v>0.01017561655994421</v>
+        <v>0.007300079311609343</v>
       </c>
       <c r="W12">
-        <v>0.09376405792167687</v>
+        <v>0.08202643990613601</v>
       </c>
       <c r="X12">
-        <v>0.06103450612888447</v>
+        <v>0.09258733037963807</v>
       </c>
       <c r="Y12">
-        <v>0.0327295517927924</v>
+        <v>-0.01056089047350206</v>
       </c>
       <c r="Z12">
-        <v>0.5213208978202214</v>
+        <v>0.5195118935486769</v>
       </c>
       <c r="AA12">
-        <v>0.08732780175780573</v>
+        <v>0.07805917816835833</v>
       </c>
       <c r="AB12">
-        <v>0.05346863700103401</v>
+        <v>0.08397653214013245</v>
       </c>
       <c r="AC12">
-        <v>0.03385916475677173</v>
+        <v>-0.00591735397177412</v>
       </c>
       <c r="AD12">
-        <v>1939.8</v>
+        <v>2062.3</v>
       </c>
       <c r="AE12">
-        <v>25.88170864120598</v>
+        <v>19.47669078359357</v>
       </c>
       <c r="AF12">
-        <v>1965.681708641206</v>
+        <v>2081.776690783594</v>
       </c>
       <c r="AG12">
-        <v>1869.381708641206</v>
+        <v>1996.176690783594</v>
       </c>
       <c r="AH12">
-        <v>0.1719834511091664</v>
+        <v>0.1507695130327861</v>
       </c>
       <c r="AI12">
-        <v>0.1858997256452007</v>
+        <v>0.3230878451916838</v>
       </c>
       <c r="AJ12">
-        <v>0.1649476516568917</v>
+        <v>0.1454719089366643</v>
       </c>
       <c r="AK12">
-        <v>0.1784172875597301</v>
+        <v>0.3139740176274681</v>
       </c>
       <c r="AL12">
-        <v>85.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AM12">
-        <v>85.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AN12">
-        <v>1.833095510342938</v>
+        <v>2.098477756522447</v>
       </c>
       <c r="AO12">
-        <v>12.14906103286385</v>
+        <v>11.1943793911007</v>
       </c>
       <c r="AP12">
-        <v>1.766550787311787</v>
+        <v>2.031194483682277</v>
       </c>
       <c r="AQ12">
-        <v>12.14906103286385</v>
+        <v>11.1943793911007</v>
       </c>
     </row>
     <row r="13">
@@ -2008,7 +1981,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Genworth Financial, Inc. (NYSE:GNW)</t>
+          <t>CNO Financial Group, Inc. (NYSE:CNO)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2017,115 +1990,121 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.00703</v>
+        <v>-0.0268</v>
+      </c>
+      <c r="E13">
+        <v>-0.00483</v>
       </c>
       <c r="G13">
-        <v>0.1477272727272727</v>
+        <v>0.2671560630777596</v>
       </c>
       <c r="H13">
-        <v>0.1477272727272727</v>
+        <v>0.2671560630777596</v>
       </c>
       <c r="I13">
-        <v>0.1895886565217559</v>
+        <v>0.2000085314026632</v>
       </c>
       <c r="J13">
-        <v>0.1462195799944704</v>
+        <v>0.1538426277608682</v>
       </c>
       <c r="K13">
-        <v>1008</v>
+        <v>469.2</v>
       </c>
       <c r="L13">
-        <v>0.1168831168831169</v>
+        <v>0.1275693311582382</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>344.7</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.1318618262499522</v>
       </c>
       <c r="O13">
-        <v>-0</v>
+        <v>0.7346547314578005</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>64.5</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.02467388393711029</v>
       </c>
       <c r="R13">
-        <v>-0</v>
+        <v>0.1374680306905371</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>280.2</v>
+      </c>
+      <c r="T13">
+        <v>0.8128807658833769</v>
       </c>
       <c r="U13">
-        <v>1937</v>
+        <v>498</v>
       </c>
       <c r="V13">
-        <v>0.9426249452528103</v>
+        <v>0.1905053364446655</v>
       </c>
       <c r="W13">
-        <v>0.06831119544592031</v>
+        <v>0.08966347531961245</v>
       </c>
       <c r="X13">
-        <v>0.09070757437891108</v>
+        <v>0.1399573227736552</v>
       </c>
       <c r="Y13">
-        <v>-0.02239637893299078</v>
+        <v>-0.05029384745404274</v>
       </c>
       <c r="Z13">
-        <v>0.5522916888982806</v>
+        <v>0.4292144446483495</v>
       </c>
       <c r="AA13">
-        <v>0.08075585878514327</v>
+        <v>0.06603147803762378</v>
       </c>
       <c r="AB13">
-        <v>0.05198099809553593</v>
+        <v>0.0771322018950007</v>
       </c>
       <c r="AC13">
-        <v>0.02877486068960734</v>
+        <v>-0.01110072385737691</v>
       </c>
       <c r="AD13">
-        <v>2456</v>
+        <v>3893.6</v>
       </c>
       <c r="AE13">
-        <v>64.93713078188658</v>
+        <v>48.84310750502296</v>
       </c>
       <c r="AF13">
-        <v>2520.937130781886</v>
+        <v>3942.443107505023</v>
       </c>
       <c r="AG13">
-        <v>583.9371307818865</v>
+        <v>3444.443107505023</v>
       </c>
       <c r="AH13">
-        <v>0.5509237017688884</v>
+        <v>0.6012990447652605</v>
       </c>
       <c r="AI13">
-        <v>0.1357317430749177</v>
+        <v>0.7523253776759014</v>
       </c>
       <c r="AJ13">
-        <v>0.2212857792435512</v>
+        <v>0.5685266319617694</v>
       </c>
       <c r="AK13">
-        <v>0.03510094599368335</v>
+        <v>0.7263167234892809</v>
       </c>
       <c r="AL13">
-        <v>191</v>
+        <v>112.8</v>
       </c>
       <c r="AM13">
-        <v>191</v>
+        <v>112.8</v>
       </c>
       <c r="AN13">
-        <v>1.460340111784992</v>
+        <v>3.405878236529042</v>
       </c>
       <c r="AO13">
-        <v>8.570680628272251</v>
+        <v>6.407801418439716</v>
       </c>
       <c r="AP13">
-        <v>0.3472096151634478</v>
+        <v>3.01298382391972</v>
       </c>
       <c r="AQ13">
-        <v>8.570680628272251</v>
+        <v>6.407801418439716</v>
       </c>
     </row>
     <row r="14">
@@ -2136,7 +2115,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unum Group (NYSE:UNM)</t>
+          <t>Brighthouse Financial, Inc. (NasdaqGS:BHF)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2145,124 +2124,115 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0394</v>
-      </c>
-      <c r="E14">
-        <v>-0.0254</v>
+        <v>0.18</v>
       </c>
       <c r="F14">
-        <v>0.064</v>
+        <v>0.12</v>
       </c>
       <c r="G14">
-        <v>0.09511429043747463</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>0.09511429043747463</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>0.09468811255061156</v>
+        <v>0.1348359429540241</v>
       </c>
       <c r="J14">
-        <v>0.07604520203738373</v>
+        <v>0.1138415038762535</v>
       </c>
       <c r="K14">
-        <v>799.9</v>
+        <v>1009</v>
       </c>
       <c r="L14">
-        <v>0.06010579943192918</v>
+        <v>0.1006283035803331</v>
       </c>
       <c r="M14">
-        <v>236.1</v>
+        <v>553</v>
       </c>
       <c r="N14">
-        <v>0.04700003981367202</v>
+        <v>0.156025167169822</v>
       </c>
       <c r="O14">
-        <v>0.2951618952369046</v>
+        <v>0.5480673934588701</v>
       </c>
       <c r="P14">
-        <v>236.1</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.04700003981367202</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.2951618952369046</v>
+        <v>-0</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14">
-        <v>121.7</v>
+        <v>4793</v>
       </c>
       <c r="V14">
-        <v>0.02422661942110921</v>
+        <v>1.352312163191603</v>
       </c>
       <c r="W14">
-        <v>0.07343787297332036</v>
+        <v>0.06294055267918408</v>
       </c>
       <c r="X14">
-        <v>0.07556805800836926</v>
+        <v>0.2118717522306125</v>
       </c>
       <c r="Y14">
-        <v>-0.002130185035048901</v>
+        <v>-0.1489311995514284</v>
       </c>
       <c r="Z14">
-        <v>0.9556535242574956</v>
+        <v>0.4720809792843691</v>
       </c>
       <c r="AA14">
-        <v>0.07267286532989904</v>
+        <v>0.05374240863310707</v>
       </c>
       <c r="AB14">
-        <v>0.05272734489148245</v>
+        <v>0.08004012177671052</v>
       </c>
       <c r="AC14">
-        <v>0.0199455204384166</v>
+        <v>-0.02629771314360346</v>
       </c>
       <c r="AD14">
-        <v>3441.4</v>
+        <v>12505</v>
       </c>
       <c r="AE14">
-        <v>109.3583027697559</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>3550.758302769756</v>
+        <v>12505</v>
       </c>
       <c r="AG14">
-        <v>3429.058302769756</v>
+        <v>7712</v>
       </c>
       <c r="AH14">
-        <v>0.4141232500480818</v>
+        <v>0.7791617079872643</v>
       </c>
       <c r="AI14">
-        <v>0.242059335740242</v>
+        <v>0.6802110530896431</v>
       </c>
       <c r="AJ14">
-        <v>0.4056876922594342</v>
+        <v>0.685127439744854</v>
       </c>
       <c r="AK14">
-        <v>0.235718527257942</v>
+        <v>0.5674343315429328</v>
       </c>
       <c r="AL14">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="AM14">
-        <v>180</v>
-      </c>
-      <c r="AN14">
-        <v>2.458142857142857</v>
+        <v>147</v>
       </c>
       <c r="AO14">
-        <v>6.981111111111111</v>
-      </c>
-      <c r="AP14">
-        <v>2.449327359121254</v>
+        <v>9.197278911564625</v>
       </c>
       <c r="AQ14">
-        <v>6.981111111111111</v>
+        <v>9.197278911564625</v>
       </c>
     </row>
     <row r="15">
@@ -2273,7 +2243,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lincoln National Corporation (NYSE:LNC)</t>
+          <t>National Western Life Group, Inc. (NasdaqGS:NWLI)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2282,124 +2252,115 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0721</v>
+        <v>-0.0548</v>
       </c>
       <c r="E15">
-        <v>0.00661</v>
-      </c>
-      <c r="F15">
-        <v>0.29</v>
+        <v>0.0447</v>
       </c>
       <c r="G15">
-        <v>0.04540851676171188</v>
+        <v>0.3926470588235294</v>
       </c>
       <c r="H15">
-        <v>0.04540851676171188</v>
+        <v>0.3926470588235294</v>
       </c>
       <c r="I15">
-        <v>0.09959938240381175</v>
+        <v>0.2406862745098039</v>
       </c>
       <c r="J15">
-        <v>0.08871091873391147</v>
+        <v>0.1919934640522876</v>
       </c>
       <c r="K15">
-        <v>1328</v>
+        <v>117.5</v>
       </c>
       <c r="L15">
-        <v>0.07077759420135372</v>
+        <v>0.1919934640522876</v>
       </c>
       <c r="M15">
-        <v>824</v>
+        <v>1.27</v>
       </c>
       <c r="N15">
-        <v>0.06680070043452882</v>
+        <v>0.001243026328667906</v>
       </c>
       <c r="O15">
-        <v>0.6204819277108434</v>
+        <v>0.01080851063829787</v>
       </c>
       <c r="P15">
-        <v>319</v>
+        <v>1.27</v>
       </c>
       <c r="Q15">
-        <v>0.02586095077501784</v>
+        <v>0.001243026328667906</v>
       </c>
       <c r="R15">
-        <v>0.240210843373494</v>
+        <v>0.01080851063829787</v>
       </c>
       <c r="S15">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>0.6128640776699029</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>2614</v>
+        <v>331.1</v>
       </c>
       <c r="V15">
-        <v>0.2119138724949737</v>
+        <v>0.3240677302534991</v>
       </c>
       <c r="W15">
-        <v>0.06162698965149195</v>
+        <v>0.04596666927470464</v>
       </c>
       <c r="X15">
-        <v>0.07303057884190041</v>
+        <v>0.08630496438957291</v>
       </c>
       <c r="Y15">
-        <v>-0.01140358919040846</v>
+        <v>-0.04033829511486827</v>
       </c>
       <c r="Z15">
-        <v>0.7419993560617133</v>
+        <v>0.3034088880956631</v>
       </c>
       <c r="AA15">
-        <v>0.06582344457620529</v>
+        <v>0.05825252344973923</v>
       </c>
       <c r="AB15">
-        <v>0.05289932463559342</v>
+        <v>0.08625079426551555</v>
       </c>
       <c r="AC15">
-        <v>0.01292411994061186</v>
+        <v>-0.02799827081577631</v>
       </c>
       <c r="AD15">
-        <v>7428</v>
+        <v>1.09</v>
       </c>
       <c r="AE15">
-        <v>216.0839397864</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>7644.0839397864</v>
+        <v>1.09</v>
       </c>
       <c r="AG15">
-        <v>5030.0839397864</v>
+        <v>-330.01</v>
       </c>
       <c r="AH15">
-        <v>0.3826004957346896</v>
+        <v>0.001065712414083047</v>
       </c>
       <c r="AI15">
-        <v>0.265289847692554</v>
+        <v>0.0005622933314074357</v>
       </c>
       <c r="AJ15">
-        <v>0.289663212949933</v>
+        <v>-0.47710679639723</v>
       </c>
       <c r="AK15">
-        <v>0.191987321542429</v>
+        <v>-0.2053079837500545</v>
       </c>
       <c r="AL15">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AN15">
-        <v>3.774390243902439</v>
-      </c>
-      <c r="AO15">
-        <v>6.892592592592592</v>
+        <v>0.006765983860955929</v>
       </c>
       <c r="AP15">
-        <v>2.555936961273577</v>
-      </c>
-      <c r="AQ15">
-        <v>6.892592592592592</v>
+        <v>-2.048479205462446</v>
       </c>
     </row>
     <row r="16">
@@ -2410,7 +2371,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CNO Financial Group, Inc. (NYSE:CNO)</t>
+          <t>Genworth Financial, Inc. (NYSE:GNW)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2419,121 +2380,121 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.00865</v>
+        <v>-0.0356</v>
       </c>
       <c r="E16">
-        <v>0.108</v>
+        <v>0.118</v>
       </c>
       <c r="G16">
-        <v>0.183577456591328</v>
+        <v>0.189575394665215</v>
       </c>
       <c r="H16">
-        <v>0.183577456591328</v>
+        <v>0.189575394665215</v>
       </c>
       <c r="I16">
-        <v>0.162304414518177</v>
+        <v>0.1482517245360553</v>
       </c>
       <c r="J16">
-        <v>0.1259581409064879</v>
+        <v>0.1109221536097104</v>
       </c>
       <c r="K16">
-        <v>437</v>
+        <v>597</v>
       </c>
       <c r="L16">
-        <v>0.105975361334756</v>
+        <v>0.08124659771366358</v>
       </c>
       <c r="M16">
-        <v>474.4</v>
+        <v>34</v>
       </c>
       <c r="N16">
-        <v>0.1613715218722362</v>
+        <v>0.01294843476273897</v>
       </c>
       <c r="O16">
-        <v>1.08558352402746</v>
+        <v>0.05695142378559464</v>
       </c>
       <c r="P16">
-        <v>66.5</v>
+        <v>-0</v>
       </c>
       <c r="Q16">
-        <v>0.02262058643445132</v>
+        <v>-0</v>
       </c>
       <c r="R16">
-        <v>0.1521739130434783</v>
+        <v>-0</v>
       </c>
       <c r="S16">
-        <v>407.9</v>
+        <v>34</v>
       </c>
       <c r="T16">
-        <v>0.8598229342327151</v>
+        <v>1</v>
       </c>
       <c r="U16">
-        <v>742.1</v>
+        <v>1561</v>
       </c>
       <c r="V16">
-        <v>0.2524321382406967</v>
+        <v>0.5944854901363393</v>
       </c>
       <c r="W16">
-        <v>0.08595763095261512</v>
+        <v>0.03908091123330715</v>
       </c>
       <c r="X16">
-        <v>0.09547740156119817</v>
+        <v>0.115148374302655</v>
       </c>
       <c r="Y16">
-        <v>-0.009519770608583056</v>
+        <v>-0.07606746306934789</v>
       </c>
       <c r="Z16">
-        <v>0.5033748194779983</v>
+        <v>0.4637942666441427</v>
       </c>
       <c r="AA16">
-        <v>0.06340415644058764</v>
+        <v>0.05144505888800459</v>
       </c>
       <c r="AB16">
-        <v>0.05181311120130908</v>
+        <v>0.08204921369523574</v>
       </c>
       <c r="AC16">
-        <v>0.01159104523927856</v>
+        <v>-0.03060415480723115</v>
       </c>
       <c r="AD16">
-        <v>4029.5</v>
+        <v>2082</v>
       </c>
       <c r="AE16">
-        <v>58.60758146422608</v>
+        <v>48.23164054533037</v>
       </c>
       <c r="AF16">
-        <v>4088.107581464226</v>
+        <v>2130.23164054533</v>
       </c>
       <c r="AG16">
-        <v>3346.007581464226</v>
+        <v>569.2316405453303</v>
       </c>
       <c r="AH16">
-        <v>0.581696263656969</v>
+        <v>0.4479010657509159</v>
       </c>
       <c r="AI16">
-        <v>0.4385907366488838</v>
+        <v>0.1749068991720029</v>
       </c>
       <c r="AJ16">
-        <v>0.5323114871239507</v>
+        <v>0.1781615034172786</v>
       </c>
       <c r="AK16">
-        <v>0.3900272324524958</v>
+        <v>0.05360889268715329</v>
       </c>
       <c r="AL16">
-        <v>95.09999999999999</v>
+        <v>109</v>
       </c>
       <c r="AM16">
-        <v>95.09999999999999</v>
+        <v>109</v>
       </c>
       <c r="AN16">
-        <v>4.0562713911818</v>
+        <v>347</v>
       </c>
       <c r="AO16">
-        <v>6.921135646687698</v>
+        <v>10.02752293577982</v>
       </c>
       <c r="AP16">
-        <v>3.368237951947077</v>
+        <v>94.87194009088837</v>
       </c>
       <c r="AQ16">
-        <v>6.921135646687698</v>
+        <v>10.02752293577982</v>
       </c>
     </row>
     <row r="17">
@@ -2553,124 +2514,121 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0155</v>
-      </c>
-      <c r="E17">
-        <v>0.0815</v>
+        <v>0.0445</v>
       </c>
       <c r="F17">
-        <v>0.0594</v>
+        <v>0.039</v>
       </c>
       <c r="G17">
-        <v>0.1171725205584513</v>
+        <v>0.1290059860732174</v>
       </c>
       <c r="H17">
-        <v>0.1171725205584513</v>
+        <v>0.1290059860732174</v>
       </c>
       <c r="I17">
-        <v>0.1120233573823392</v>
+        <v>0.04559896038535755</v>
       </c>
       <c r="J17">
-        <v>0.08857287793030887</v>
+        <v>0.04531840894738365</v>
       </c>
       <c r="K17">
-        <v>5507</v>
+        <v>2401</v>
       </c>
       <c r="L17">
-        <v>0.07821443281398685</v>
+        <v>0.03259084307257944</v>
       </c>
       <c r="M17">
-        <v>5355</v>
+        <v>5516</v>
       </c>
       <c r="N17">
-        <v>0.1018756147256397</v>
+        <v>0.09714346095593675</v>
       </c>
       <c r="O17">
-        <v>0.9723987652079172</v>
+        <v>2.29737609329446</v>
       </c>
       <c r="P17">
-        <v>1657</v>
+        <v>1610</v>
       </c>
       <c r="Q17">
-        <v>0.03152341617187396</v>
+        <v>0.02835405586277341</v>
       </c>
       <c r="R17">
-        <v>0.3008897766479027</v>
+        <v>0.6705539358600583</v>
       </c>
       <c r="S17">
-        <v>3698</v>
+        <v>3906</v>
       </c>
       <c r="T17">
-        <v>0.6905695611577964</v>
+        <v>0.7081218274111675</v>
       </c>
       <c r="U17">
-        <v>18956</v>
+        <v>22200</v>
       </c>
       <c r="V17">
-        <v>0.3606263590549443</v>
+        <v>0.3909689690394844</v>
       </c>
       <c r="W17">
-        <v>0.07511320857657264</v>
+        <v>0.03477190441708906</v>
       </c>
       <c r="X17">
-        <v>0.1164765005357731</v>
+        <v>0.1523485518497094</v>
       </c>
       <c r="Y17">
-        <v>-0.04136329195920047</v>
+        <v>-0.1175766474326203</v>
       </c>
       <c r="Z17">
-        <v>0.4592298506940562</v>
+        <v>0.4874148670612378</v>
       </c>
       <c r="AA17">
-        <v>0.04067530950747861</v>
+        <v>0.02208886627251581</v>
       </c>
       <c r="AB17">
-        <v>0.04899648861505237</v>
+        <v>0.0763940833713609</v>
       </c>
       <c r="AC17">
-        <v>-0.00832117910757376</v>
+        <v>-0.05430521709884509</v>
       </c>
       <c r="AD17">
-        <v>109487</v>
+        <v>104196</v>
       </c>
       <c r="AE17">
-        <v>1517.737150334386</v>
+        <v>1203.39494725162</v>
       </c>
       <c r="AF17">
-        <v>111004.7371503344</v>
+        <v>105399.3949472516</v>
       </c>
       <c r="AG17">
-        <v>92048.73715033439</v>
+        <v>83199.39494725163</v>
       </c>
       <c r="AH17">
-        <v>0.6786423323919036</v>
+        <v>0.6498858576320178</v>
       </c>
       <c r="AI17">
-        <v>0.6155380393721911</v>
+        <v>0.806240975794155</v>
       </c>
       <c r="AJ17">
-        <v>0.6365184375343095</v>
+        <v>0.59436037895324</v>
       </c>
       <c r="AK17">
-        <v>0.5703788964954989</v>
+        <v>0.7666070099044494</v>
       </c>
       <c r="AL17">
-        <v>926</v>
+        <v>914</v>
       </c>
       <c r="AM17">
-        <v>926</v>
+        <v>914</v>
       </c>
       <c r="AN17">
-        <v>12.72660699755899</v>
+        <v>25.68934911242604</v>
       </c>
       <c r="AO17">
-        <v>8.539956803455723</v>
+        <v>3.665207877461707</v>
       </c>
       <c r="AP17">
-        <v>10.69960910732702</v>
+        <v>20.51267133807979</v>
       </c>
       <c r="AQ17">
-        <v>8.539956803455723</v>
+        <v>3.665207877461707</v>
       </c>
     </row>
     <row r="18">
@@ -2681,7 +2639,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Citizens, Inc. (NYSE:CIA)</t>
+          <t>Kansas City Life Insurance Company (OTCPK:KCLI)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2690,103 +2648,103 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.00486</v>
+        <v>0.0176</v>
       </c>
       <c r="E18">
-        <v>0.144</v>
+        <v>-0.0922</v>
       </c>
       <c r="G18">
-        <v>-0.003640065146579805</v>
+        <v>0.03135179153094463</v>
       </c>
       <c r="H18">
-        <v>-0.003640065146579805</v>
+        <v>0.03135179153094463</v>
       </c>
       <c r="I18">
-        <v>0.02771866174929859</v>
+        <v>0.02178338762214984</v>
       </c>
       <c r="J18">
-        <v>0.02771866174929859</v>
+        <v>0.0191075270438734</v>
       </c>
       <c r="K18">
-        <v>0.188</v>
+        <v>14.2</v>
       </c>
       <c r="L18">
-        <v>0.0007654723127035831</v>
+        <v>0.02890879478827361</v>
       </c>
       <c r="M18">
-        <v>9.09</v>
+        <v>7.94</v>
       </c>
       <c r="N18">
-        <v>0.03437972768532527</v>
+        <v>0.0310641627543036</v>
       </c>
       <c r="O18">
-        <v>48.35106382978724</v>
+        <v>0.5591549295774648</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>7.94</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.0310641627543036</v>
       </c>
       <c r="R18">
-        <v>-0</v>
+        <v>0.5591549295774648</v>
       </c>
       <c r="S18">
-        <v>9.09</v>
+        <v>0</v>
       </c>
       <c r="T18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>30.1</v>
+        <v>7.28</v>
       </c>
       <c r="V18">
-        <v>0.1138426626323752</v>
+        <v>0.02848200312989045</v>
       </c>
       <c r="W18">
-        <v>0.0006334231805929919</v>
+        <v>0.01698971045704714</v>
       </c>
       <c r="X18">
-        <v>0.05630946620011808</v>
+        <v>0.08626698429789872</v>
       </c>
       <c r="Y18">
-        <v>-0.05567604301952509</v>
+        <v>-0.06927727384085158</v>
       </c>
       <c r="Z18">
-        <v>0.9215362763836944</v>
+        <v>0.5909101845391334</v>
       </c>
       <c r="AA18">
-        <v>0.02554375233478776</v>
+        <v>0.01129083233158171</v>
       </c>
       <c r="AB18">
-        <v>0.05460312405852822</v>
+        <v>0.08626698429789872</v>
       </c>
       <c r="AC18">
-        <v>-0.02905937172374046</v>
+        <v>-0.07497615196631702</v>
       </c>
       <c r="AD18">
         <v>0</v>
       </c>
       <c r="AE18">
-        <v>12.01148337186134</v>
+        <v>0</v>
       </c>
       <c r="AF18">
-        <v>12.01148337186134</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>-18.08851662813866</v>
+        <v>-7.28</v>
       </c>
       <c r="AH18">
-        <v>0.04345508090089757</v>
+        <v>0</v>
       </c>
       <c r="AI18">
-        <v>0.04336095827383833</v>
+        <v>0</v>
       </c>
       <c r="AJ18">
-        <v>-0.07343756929444525</v>
+        <v>-0.02931701030927835</v>
       </c>
       <c r="AK18">
-        <v>-0.07325911448556012</v>
+        <v>-0.01484139280763272</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2798,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>-1.673313286599321</v>
+        <v>-0.4089887640449438</v>
       </c>
     </row>
     <row r="19">
@@ -2809,7 +2767,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Independence Holding Company (NYSE:IHC)</t>
+          <t>Prudential Financial, Inc. (NYSE:PRU)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2818,103 +2776,106 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.04650000000000001</v>
+        <v>0.0116</v>
       </c>
       <c r="E19">
-        <v>-0.026</v>
+        <v>-0.405</v>
+      </c>
+      <c r="F19">
+        <v>-0.0621</v>
       </c>
       <c r="G19">
-        <v>0.06533120874117915</v>
+        <v>0.1723671780839767</v>
       </c>
       <c r="H19">
-        <v>0.06533120874117915</v>
+        <v>0.1723671780839767</v>
       </c>
       <c r="I19">
-        <v>0.0363541408646781</v>
+        <v>-0.004910659494197094</v>
       </c>
       <c r="J19">
-        <v>0.0204470707774105</v>
+        <v>-0.004910659494197094</v>
       </c>
       <c r="K19">
-        <v>104.9</v>
+        <v>328</v>
       </c>
       <c r="L19">
-        <v>0.2387889824721147</v>
+        <v>0.005342193556793381</v>
       </c>
       <c r="M19">
-        <v>7.7</v>
+        <v>3327</v>
       </c>
       <c r="N19">
-        <v>0.009251471825063079</v>
+        <v>0.09089841071218781</v>
       </c>
       <c r="O19">
-        <v>0.07340324118207817</v>
+        <v>10.14329268292683</v>
       </c>
       <c r="P19">
-        <v>6.45</v>
+        <v>1811</v>
       </c>
       <c r="Q19">
-        <v>0.007749609515799592</v>
+        <v>0.04947911686196938</v>
       </c>
       <c r="R19">
-        <v>0.06148713060057198</v>
+        <v>5.521341463414634</v>
       </c>
       <c r="S19">
-        <v>1.25</v>
+        <v>1516</v>
       </c>
       <c r="T19">
-        <v>0.1623376623376623</v>
+        <v>0.4556657649534115</v>
       </c>
       <c r="U19">
-        <v>7.95</v>
+        <v>20104</v>
       </c>
       <c r="V19">
-        <v>0.009551844286915776</v>
+        <v>0.5492701078923425</v>
       </c>
       <c r="W19">
-        <v>0.2245291095890411</v>
+        <v>0.005299982225669365</v>
       </c>
       <c r="X19">
-        <v>0.05536270481797564</v>
+        <v>0.1206778893625322</v>
       </c>
       <c r="Y19">
-        <v>0.1691664047710655</v>
+        <v>-0.1153779071368629</v>
       </c>
       <c r="Z19">
-        <v>1.154994505882543</v>
+        <v>0.7594201780041638</v>
       </c>
       <c r="AA19">
-        <v>0.02361625440930063</v>
+        <v>-0.003729253907200995</v>
       </c>
       <c r="AB19">
-        <v>0.05487415764161272</v>
+        <v>0.07880014820033795</v>
       </c>
       <c r="AC19">
-        <v>-0.03125790323231209</v>
+        <v>-0.08252940210753895</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>34971</v>
       </c>
       <c r="AE19">
-        <v>10.74812959073455</v>
+        <v>407.523358123566</v>
       </c>
       <c r="AF19">
-        <v>10.74812959073455</v>
+        <v>35378.52335812357</v>
       </c>
       <c r="AG19">
-        <v>2.798129590734551</v>
+        <v>15274.52335812357</v>
       </c>
       <c r="AH19">
-        <v>0.01274912927682116</v>
+        <v>0.4915061152915539</v>
       </c>
       <c r="AI19">
-        <v>0.0186810889580541</v>
+        <v>0.6731262809090198</v>
       </c>
       <c r="AJ19">
-        <v>0.003350659630989547</v>
+        <v>0.2944439696441296</v>
       </c>
       <c r="AK19">
-        <v>0.004931510071689605</v>
+        <v>0.4706438972951442</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2923,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>-852.9512195121952</v>
       </c>
       <c r="AP19">
-        <v>0.1220824428767256</v>
+        <v>-372.5493501981358</v>
       </c>
     </row>
     <row r="20">
@@ -2937,7 +2898,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kansas City Life Insurance Company (OTCPK:KCLI)</t>
+          <t>Citizens, Inc. (NYSE:CIA)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2946,100 +2907,103 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.0226</v>
+        <v>-0.0142</v>
+      </c>
+      <c r="E20">
+        <v>0.353</v>
       </c>
       <c r="G20">
-        <v>0.04954499494438827</v>
+        <v>0.03010204081632653</v>
       </c>
       <c r="H20">
-        <v>0.04954499494438827</v>
+        <v>0.03010204081632653</v>
       </c>
       <c r="I20">
-        <v>-0.01278058645096057</v>
+        <v>-0.01773784590967477</v>
       </c>
       <c r="J20">
-        <v>-0.01278058645096057</v>
+        <v>-0.01773784590967477</v>
       </c>
       <c r="K20">
-        <v>-3.14</v>
+        <v>28.1</v>
       </c>
       <c r="L20">
-        <v>-0.00634984833164813</v>
+        <v>0.1194727891156463</v>
       </c>
       <c r="M20">
-        <v>10.5</v>
+        <v>2.18</v>
       </c>
       <c r="N20">
-        <v>0.02551640340218712</v>
+        <v>0.02046948356807512</v>
       </c>
       <c r="O20">
-        <v>-3.343949044585987</v>
+        <v>0.07758007117437722</v>
       </c>
       <c r="P20">
-        <v>10.5</v>
+        <v>-0</v>
       </c>
       <c r="Q20">
-        <v>0.02551640340218712</v>
+        <v>-0</v>
       </c>
       <c r="R20">
-        <v>-3.343949044585987</v>
+        <v>-0</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20">
-        <v>4.54</v>
+        <v>21</v>
       </c>
       <c r="V20">
-        <v>0.01103280680437424</v>
+        <v>0.1971830985915493</v>
       </c>
       <c r="W20">
-        <v>-0.003487726313451072</v>
+        <v>0.1060377358490566</v>
       </c>
       <c r="X20">
-        <v>0.05498669094562519</v>
+        <v>0.08937898222753543</v>
       </c>
       <c r="Y20">
-        <v>-0.05847441725907626</v>
+        <v>0.01665875362152118</v>
       </c>
       <c r="Z20">
-        <v>0.5817510176231148</v>
+        <v>0.9631066802863273</v>
       </c>
       <c r="AA20">
-        <v>-0.007435119173666503</v>
+        <v>-0.01708343788949728</v>
       </c>
       <c r="AB20">
-        <v>0.05498669094562519</v>
+        <v>0.08550999123317848</v>
       </c>
       <c r="AC20">
-        <v>-0.06242181011929169</v>
+        <v>-0.1025934291226758</v>
       </c>
       <c r="AD20">
         <v>0</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>9.309706789777533</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>9.309706789777533</v>
       </c>
       <c r="AG20">
-        <v>-4.54</v>
+        <v>-11.69029321022247</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>0.08038796615448555</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>-1.903711370581401</v>
       </c>
       <c r="AJ20">
-        <v>-0.01115588755651661</v>
+        <v>-0.1233027039746412</v>
       </c>
       <c r="AK20">
-        <v>-0.005461588432018863</v>
+        <v>0.4515318971206822</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3048,10 +3012,10 @@
         <v>0</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AP20">
-        <v>-2.718562874251497</v>
+        <v>6.836428777907876</v>
       </c>
     </row>
     <row r="21">
@@ -3062,7 +3026,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Brighthouse Financial, Inc. (NasdaqGS:BHF)</t>
+          <t>Lincoln National Corporation (NYSE:LNC)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3071,115 +3035,121 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.0153</v>
+        <v>0.0675</v>
       </c>
       <c r="F21">
-        <v>0.14</v>
+        <v>0.0825</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>0.1068674447686536</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>0.1068674447686536</v>
       </c>
       <c r="I21">
-        <v>-0.2658541230241859</v>
+        <v>-0.07602634506252699</v>
       </c>
       <c r="J21">
-        <v>-0.2658541230241859</v>
+        <v>-0.07602634506252699</v>
       </c>
       <c r="K21">
-        <v>-1203</v>
+        <v>-2013</v>
       </c>
       <c r="L21">
-        <v>-0.2290992191963435</v>
+        <v>-0.1048874531054606</v>
       </c>
       <c r="M21">
-        <v>438</v>
+        <v>1512</v>
       </c>
       <c r="N21">
-        <v>0.1059352778987084</v>
+        <v>0.2908643210280284</v>
       </c>
       <c r="O21">
-        <v>-0.3640897755610973</v>
+        <v>-0.7511177347242921</v>
       </c>
       <c r="P21">
-        <v>-0</v>
+        <v>312</v>
       </c>
       <c r="Q21">
-        <v>-0</v>
+        <v>0.06001962179943443</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>-0.1549925484351714</v>
       </c>
       <c r="S21">
-        <v>438</v>
+        <v>1200</v>
       </c>
       <c r="T21">
-        <v>1</v>
+        <v>0.7936507936507936</v>
       </c>
       <c r="U21">
-        <v>4108</v>
+        <v>1472</v>
       </c>
       <c r="V21">
-        <v>0.9935664876892565</v>
+        <v>0.2831694977204086</v>
       </c>
       <c r="W21">
-        <v>-0.06586006788568925</v>
+        <v>-0.09508738781294285</v>
       </c>
       <c r="X21">
-        <v>0.120600230021832</v>
+        <v>0.1406058384523799</v>
       </c>
       <c r="Y21">
-        <v>-0.1864602979075212</v>
+        <v>-0.2356932262653228</v>
       </c>
       <c r="Z21">
-        <v>0.2256456533883374</v>
+        <v>0.7876391519012663</v>
       </c>
       <c r="AA21">
-        <v>-0.05998882729577586</v>
+        <v>-0.05988132594720179</v>
       </c>
       <c r="AB21">
-        <v>0.05178229668205019</v>
+        <v>0.0805776318925995</v>
       </c>
       <c r="AC21">
-        <v>-0.111771123977826</v>
+        <v>-0.1404589578398013</v>
       </c>
       <c r="AD21">
-        <v>9317</v>
+        <v>7774</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>160.48807220009</v>
       </c>
       <c r="AF21">
-        <v>9317</v>
+        <v>7934.48807220009</v>
       </c>
       <c r="AG21">
-        <v>5209</v>
+        <v>6462.48807220009</v>
       </c>
       <c r="AH21">
-        <v>0.6926313598382349</v>
+        <v>0.6041739216820281</v>
       </c>
       <c r="AI21">
-        <v>0.3666233817337583</v>
+        <v>0.7816083726610223</v>
       </c>
       <c r="AJ21">
-        <v>0.5574938995676184</v>
+        <v>0.5542068025065123</v>
       </c>
       <c r="AK21">
-        <v>0.2444965970429477</v>
+        <v>0.7445701887533062</v>
       </c>
       <c r="AL21">
-        <v>161</v>
+        <v>271</v>
       </c>
       <c r="AM21">
-        <v>161</v>
+        <v>271</v>
+      </c>
+      <c r="AN21">
+        <v>-5.612996389891697</v>
       </c>
       <c r="AO21">
-        <v>-8.670807453416149</v>
+        <v>-5.435424354243542</v>
+      </c>
+      <c r="AP21">
+        <v>-4.666056369819559</v>
       </c>
       <c r="AQ21">
-        <v>-8.670807453416149</v>
+        <v>-5.435424354243542</v>
       </c>
     </row>
     <row r="22">
@@ -3199,22 +3169,22 @@
         </is>
       </c>
       <c r="G22">
-        <v>-0.1471471471471471</v>
+        <v>-0.08039906103286384</v>
       </c>
       <c r="H22">
-        <v>-0.1471471471471471</v>
+        <v>-0.08039906103286384</v>
       </c>
       <c r="I22">
-        <v>-0.1202368077850917</v>
+        <v>-0.09561719982545512</v>
       </c>
       <c r="J22">
-        <v>-0.1202368077850917</v>
+        <v>-0.09561719982545512</v>
       </c>
       <c r="K22">
-        <v>-19.2</v>
+        <v>-16.9</v>
       </c>
       <c r="L22">
-        <v>-0.1153153153153153</v>
+        <v>-0.09917840375586853</v>
       </c>
       <c r="M22">
         <v>-0</v>
@@ -3238,55 +3208,55 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>20.7</v>
+        <v>12.7</v>
       </c>
       <c r="V22">
-        <v>0.2003872216844143</v>
+        <v>0.1137992831541219</v>
       </c>
       <c r="W22">
-        <v>-0.0963855421686747</v>
+        <v>-0.0950506186726659</v>
       </c>
       <c r="X22">
-        <v>0.063526579753326</v>
+        <v>0.09810688800051279</v>
       </c>
       <c r="Y22">
-        <v>-0.1599121219220007</v>
+        <v>-0.1931575066731787</v>
       </c>
       <c r="Z22">
-        <v>0.8735702845939586</v>
+        <v>0.9150670907432769</v>
       </c>
       <c r="AA22">
-        <v>-0.1050353023954916</v>
+        <v>-0.08749615286929778</v>
       </c>
       <c r="AB22">
-        <v>0.05374944043553803</v>
+        <v>0.08391679388557714</v>
       </c>
       <c r="AC22">
-        <v>-0.1587847428310297</v>
+        <v>-0.1714129467548749</v>
       </c>
       <c r="AD22">
-        <v>26.8</v>
+        <v>34.8</v>
       </c>
       <c r="AE22">
-        <v>3.49714248108881</v>
+        <v>2.315854251287776</v>
       </c>
       <c r="AF22">
-        <v>30.29714248108881</v>
+        <v>37.11585425128777</v>
       </c>
       <c r="AG22">
-        <v>9.597142481088813</v>
+        <v>24.41585425128777</v>
       </c>
       <c r="AH22">
-        <v>0.2267798690782439</v>
+        <v>0.2495756383080211</v>
       </c>
       <c r="AI22">
-        <v>0.1455913431576415</v>
+        <v>0.2380505461071879</v>
       </c>
       <c r="AJ22">
-        <v>0.08500784227285835</v>
+        <v>0.1795074139385233</v>
       </c>
       <c r="AK22">
-        <v>0.05121285391028473</v>
+        <v>0.1704829006462337</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3295,10 +3265,10 @@
         <v>0</v>
       </c>
       <c r="AN22">
-        <v>-1.683417085427136</v>
+        <v>-2.966751918158567</v>
       </c>
       <c r="AP22">
-        <v>-0.6028355829829656</v>
+        <v>-2.081488000962299</v>
       </c>
     </row>
     <row r="23">
@@ -3318,37 +3288,34 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.296</v>
-      </c>
-      <c r="F23">
-        <v>-0.529</v>
+        <v>0.302</v>
       </c>
       <c r="G23">
-        <v>0.004279314073845204</v>
+        <v>-0.02694786174575278</v>
       </c>
       <c r="H23">
-        <v>0.004279314073845204</v>
+        <v>-0.02694786174575278</v>
       </c>
       <c r="I23">
-        <v>-0.04933808779477469</v>
+        <v>-0.04606967784524638</v>
       </c>
       <c r="J23">
-        <v>-0.04933808779477469</v>
+        <v>-0.04606967784524638</v>
       </c>
       <c r="K23">
-        <v>-32</v>
+        <v>-42.4</v>
       </c>
       <c r="L23">
-        <v>-0.04943611926463773</v>
+        <v>-0.04967779730521382</v>
       </c>
       <c r="M23">
-        <v>4.19</v>
+        <v>10.5</v>
       </c>
       <c r="N23">
-        <v>0.0007861458216068145</v>
+        <v>0.005403458213256484</v>
       </c>
       <c r="O23">
-        <v>-0.1309375</v>
+        <v>-0.2476415094339623</v>
       </c>
       <c r="P23">
         <v>-0</v>
@@ -3360,79 +3327,79 @@
         <v>0</v>
       </c>
       <c r="S23">
-        <v>4.19</v>
+        <v>10.5</v>
       </c>
       <c r="T23">
         <v>1</v>
       </c>
       <c r="U23">
-        <v>109.6</v>
+        <v>85.5</v>
       </c>
       <c r="V23">
-        <v>0.02056362340050283</v>
+        <v>0.04399958830794565</v>
       </c>
       <c r="W23">
-        <v>-0.2217602217602218</v>
+        <v>-0.127710843373494</v>
       </c>
       <c r="X23">
-        <v>0.0549924967082969</v>
+        <v>0.08727098631646957</v>
       </c>
       <c r="Y23">
-        <v>-0.2767527184685187</v>
+        <v>-0.2149818296899635</v>
       </c>
       <c r="Z23">
-        <v>4.62480290960125</v>
+        <v>4.482612736045049</v>
       </c>
       <c r="AA23">
-        <v>-0.228178931987436</v>
+        <v>-0.2065125246545939</v>
       </c>
       <c r="AB23">
-        <v>0.05498560333118405</v>
+        <v>0.08600869640544043</v>
       </c>
       <c r="AC23">
-        <v>-0.28316453531862</v>
+        <v>-0.2925212210600343</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>54.2</v>
       </c>
       <c r="AE23">
-        <v>1.062721147788284</v>
+        <v>0.6023502045889506</v>
       </c>
       <c r="AF23">
-        <v>1.062721147788284</v>
+        <v>54.80235020458895</v>
       </c>
       <c r="AG23">
-        <v>-108.5372788522117</v>
+        <v>-30.69764979541105</v>
       </c>
       <c r="AH23">
-        <v>0.0001993525632487999</v>
+        <v>0.0274285714423596</v>
       </c>
       <c r="AI23">
-        <v>0.003190753813954244</v>
+        <v>0.1520166239512392</v>
       </c>
       <c r="AJ23">
-        <v>-0.02078755363383668</v>
+        <v>-0.01605103899199244</v>
       </c>
       <c r="AK23">
-        <v>-0.4857064225062846</v>
+        <v>-0.1116268634525248</v>
       </c>
       <c r="AL23">
-        <v>0.338</v>
+        <v>2.69</v>
       </c>
       <c r="AM23">
-        <v>0.338</v>
+        <v>2.69</v>
       </c>
       <c r="AN23">
-        <v>-0</v>
+        <v>-1.908450704225352</v>
       </c>
       <c r="AO23">
-        <v>-94.37869822485206</v>
+        <v>-14.5724907063197</v>
       </c>
       <c r="AP23">
-        <v>5.366756272360152</v>
+        <v>1.080903161810248</v>
       </c>
       <c r="AQ23">
-        <v>-94.37869822485206</v>
+        <v>-14.5724907063197</v>
       </c>
     </row>
     <row r="24">
@@ -3452,25 +3419,25 @@
         </is>
       </c>
       <c r="F24">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="G24">
-        <v>-0.2716598346418398</v>
+        <v>-0.1503267973856209</v>
       </c>
       <c r="H24">
-        <v>-0.2716598346418398</v>
+        <v>-0.1503267973856209</v>
       </c>
       <c r="I24">
-        <v>-0.3764464024995714</v>
+        <v>-0.1620248670614414</v>
       </c>
       <c r="J24">
-        <v>-0.3764464024995714</v>
+        <v>-0.1620248670614414</v>
       </c>
       <c r="K24">
-        <v>-563.1</v>
+        <v>-579.2</v>
       </c>
       <c r="L24">
-        <v>-0.3912318488153964</v>
+        <v>-0.1645922136970731</v>
       </c>
       <c r="M24">
         <v>-0</v>
@@ -3494,67 +3461,73 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>1076.7</v>
+        <v>2112.9</v>
       </c>
       <c r="V24">
-        <v>0.6546482641211163</v>
+        <v>3.999432140829075</v>
+      </c>
+      <c r="W24">
+        <v>-0.3729075457120783</v>
       </c>
       <c r="X24">
-        <v>0.0567676223832127</v>
+        <v>0.1138366184895366</v>
+      </c>
+      <c r="Y24">
+        <v>-0.4867441642016149</v>
       </c>
       <c r="Z24">
-        <v>14.30764977724864</v>
+        <v>5.98644974046078</v>
       </c>
       <c r="AA24">
-        <v>-5.386063286869046</v>
+        <v>-0.9699537233681584</v>
       </c>
       <c r="AB24">
-        <v>0.05480042437613736</v>
+        <v>0.0821571731708003</v>
       </c>
       <c r="AC24">
-        <v>-5.440863711245183</v>
+        <v>-1.052110896538959</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>297.8</v>
       </c>
       <c r="AE24">
-        <v>100.5965355881654</v>
+        <v>111.3275359460615</v>
       </c>
       <c r="AF24">
-        <v>100.5965355881654</v>
+        <v>409.1275359460616</v>
       </c>
       <c r="AG24">
-        <v>-976.1034644118347</v>
+        <v>-1703.772464053939</v>
       </c>
       <c r="AH24">
-        <v>0.05763864967179595</v>
+        <v>0.436436439359727</v>
       </c>
       <c r="AI24">
-        <v>0.06082763715089577</v>
+        <v>0.2738970301480974</v>
       </c>
       <c r="AJ24">
-        <v>-1.459928989241853</v>
+        <v>1.449436304256769</v>
       </c>
       <c r="AK24">
-        <v>-1.691404131229118</v>
+        <v>2.751692885208015</v>
       </c>
       <c r="AL24">
-        <v>7.84</v>
+        <v>16.9</v>
       </c>
       <c r="AM24">
-        <v>7.84</v>
+        <v>16.9</v>
       </c>
       <c r="AN24">
-        <v>-0</v>
+        <v>-0.5593538692712245</v>
       </c>
       <c r="AO24">
-        <v>-68.18877551020408</v>
+        <v>-33.29585798816569</v>
       </c>
       <c r="AP24">
-        <v>1.922598905676255</v>
+        <v>3.200173674030688</v>
       </c>
       <c r="AQ24">
-        <v>-68.18877551020408</v>
+        <v>-33.29585798816569</v>
       </c>
     </row>
     <row r="25">
@@ -3573,26 +3546,23 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="F25">
-        <v>-0.487</v>
-      </c>
       <c r="G25">
-        <v>-0.071436909069686</v>
+        <v>-0.1938636212292735</v>
       </c>
       <c r="H25">
-        <v>-0.071436909069686</v>
+        <v>-0.1938636212292735</v>
       </c>
       <c r="I25">
-        <v>-0.1559906880430736</v>
+        <v>-0.2284603939245895</v>
       </c>
       <c r="J25">
-        <v>-0.1559906880430736</v>
+        <v>-0.2284603939245895</v>
       </c>
       <c r="K25">
-        <v>-534.2</v>
+        <v>-1590.5</v>
       </c>
       <c r="L25">
-        <v>-0.1558888759192249</v>
+        <v>-0.2647832456549244</v>
       </c>
       <c r="M25">
         <v>-0</v>
@@ -3616,67 +3586,192 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>956.2</v>
+        <v>1605.5</v>
       </c>
       <c r="V25">
-        <v>0.4422143088378116</v>
+        <v>3.936978911230995</v>
+      </c>
+      <c r="W25">
+        <v>-0.8210303530869296</v>
       </c>
       <c r="X25">
-        <v>0.05539799900003053</v>
+        <v>0.1170814846908515</v>
+      </c>
+      <c r="Y25">
+        <v>-0.9381118377777812</v>
       </c>
       <c r="Z25">
-        <v>112.1905982933495</v>
+        <v>31.98858727110587</v>
       </c>
       <c r="AA25">
-        <v>-17.50068861974367</v>
+        <v>-7.308125249047958</v>
       </c>
       <c r="AB25">
-        <v>0.05494167715498206</v>
+        <v>0.08322020577090435</v>
       </c>
       <c r="AC25">
-        <v>-17.55563029689865</v>
+        <v>-7.391345454818862</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>303.9</v>
       </c>
       <c r="AE25">
-        <v>30.54444893002354</v>
+        <v>49.07947113112189</v>
       </c>
       <c r="AF25">
-        <v>30.54444893002354</v>
+        <v>352.9794711311218</v>
       </c>
       <c r="AG25">
-        <v>-925.6555510699765</v>
+        <v>-1252.520528868878</v>
       </c>
       <c r="AH25">
-        <v>0.01392914529114338</v>
+        <v>0.463970814835887</v>
       </c>
       <c r="AI25">
-        <v>0.01456061482875241</v>
+        <v>0.2100218853113982</v>
       </c>
       <c r="AJ25">
-        <v>-0.7485219796772444</v>
+        <v>1.482763217020503</v>
       </c>
       <c r="AK25">
-        <v>-0.8108799897696485</v>
+        <v>-16.66040622558161</v>
       </c>
       <c r="AL25">
-        <v>6.28</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AM25">
-        <v>6.28</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AN25">
-        <v>-0</v>
+        <v>-0.231489945155393</v>
       </c>
       <c r="AO25">
-        <v>-85.31847133757961</v>
+        <v>-169.6794081381011</v>
       </c>
       <c r="AP25">
-        <v>1.850792880133516</v>
+        <v>0.9540832791505773</v>
       </c>
       <c r="AQ25">
-        <v>-85.31847133757961</v>
+        <v>-169.6794081381011</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pekin Life Insurance Company (OTCPK:PKIN)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>-0.0145</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>-0.01204111947856088</v>
+      </c>
+      <c r="J26">
+        <v>-0.01204111947856088</v>
+      </c>
+      <c r="K26">
+        <v>-3.77</v>
+      </c>
+      <c r="L26">
+        <v>-0.01455036665380162</v>
+      </c>
+      <c r="M26">
+        <v>0.341</v>
+      </c>
+      <c r="N26">
+        <v>0.001700748129675811</v>
+      </c>
+      <c r="O26">
+        <v>-0.09045092838196288</v>
+      </c>
+      <c r="P26">
+        <v>0.341</v>
+      </c>
+      <c r="Q26">
+        <v>0.001700748129675811</v>
+      </c>
+      <c r="R26">
+        <v>-0.09045092838196288</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0.08626774251807136</v>
+      </c>
+      <c r="Z26">
+        <v>60675.11461573897</v>
+      </c>
+      <c r="AA26">
+        <v>-730.5963044634883</v>
+      </c>
+      <c r="AB26">
+        <v>0.08626678374264614</v>
+      </c>
+      <c r="AC26">
+        <v>-730.682571247231</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>0.004270284475619106</v>
+      </c>
+      <c r="AF26">
+        <v>0.004270284475619106</v>
+      </c>
+      <c r="AG26">
+        <v>0.004270284475619106</v>
+      </c>
+      <c r="AH26">
+        <v>2.129772333307626e-05</v>
+      </c>
+      <c r="AI26">
+        <v>1</v>
+      </c>
+      <c r="AJ26">
+        <v>2.129772333307626e-05</v>
+      </c>
+      <c r="AK26">
+        <v>1</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AP26">
+        <v>4.270284475619106</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_states/united_states_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ26"/>
+  <dimension ref="A1:AQ23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03105</v>
+        <v>-0.007345000000000001</v>
       </c>
       <c r="E2">
-        <v>0.04650000000000001</v>
+        <v>-0.117</v>
       </c>
       <c r="F2">
-        <v>0.0825</v>
+        <v>0.0898</v>
       </c>
       <c r="G2">
-        <v>0.1429236371297488</v>
+        <v>0.08584427785570893</v>
       </c>
       <c r="H2">
-        <v>0.1429236371297488</v>
+        <v>0.08584427785570893</v>
       </c>
       <c r="I2">
-        <v>0.08391171025722445</v>
+        <v>0.001285292310542593</v>
       </c>
       <c r="J2">
-        <v>0.07314289201831981</v>
+        <v>0.001141982349823795</v>
       </c>
       <c r="K2">
-        <v>15306.226</v>
+        <v>1556.185</v>
       </c>
       <c r="L2">
-        <v>0.06068823406214149</v>
+        <v>0.007194973549132222</v>
       </c>
       <c r="M2">
-        <v>19119.079</v>
+        <v>15463.076</v>
       </c>
       <c r="N2">
-        <v>0.0915357874053616</v>
+        <v>0.07363930585187443</v>
       </c>
       <c r="O2">
-        <v>1.249104710723597</v>
+        <v>9.93652811201753</v>
       </c>
       <c r="P2">
-        <v>5853.451</v>
+        <v>5932.29</v>
       </c>
       <c r="Q2">
-        <v>0.02802437535425745</v>
+        <v>0.02825115246875953</v>
       </c>
       <c r="R2">
-        <v>0.3824228781150886</v>
+        <v>3.812072472103252</v>
       </c>
       <c r="S2">
-        <v>13265.628</v>
+        <v>9530.786</v>
       </c>
       <c r="T2">
-        <v>0.6938424178277625</v>
+        <v>0.6163577026977038</v>
       </c>
       <c r="U2">
-        <v>67845.88</v>
+        <v>65235.97</v>
       </c>
       <c r="V2">
-        <v>0.3248234942702875</v>
+        <v>0.310671146373057</v>
       </c>
       <c r="W2">
-        <v>0.07248349629266004</v>
+        <v>0.03420910701903074</v>
       </c>
       <c r="X2">
-        <v>0.09477540510670333</v>
+        <v>0.08196354147483029</v>
       </c>
       <c r="Y2">
-        <v>-0.02229190881404329</v>
+        <v>-0.04775443445579955</v>
       </c>
       <c r="Z2">
-        <v>0.6495091917970077</v>
+        <v>0.936971284070234</v>
       </c>
       <c r="AA2">
-        <v>0.05599746604142315</v>
+        <v>-0.02561306958794109</v>
       </c>
       <c r="AB2">
-        <v>0.08369078258206245</v>
+        <v>0.07242563299507214</v>
       </c>
       <c r="AC2">
-        <v>-0.02714799197968988</v>
+        <v>-0.1002212393737126</v>
       </c>
       <c r="AD2">
-        <v>190586.59</v>
+        <v>191456.946</v>
       </c>
       <c r="AE2">
-        <v>2514.311398276825</v>
+        <v>2299.244768979127</v>
       </c>
       <c r="AF2">
-        <v>193100.9013982768</v>
+        <v>193756.1907689791</v>
       </c>
       <c r="AG2">
-        <v>125255.0213982768</v>
+        <v>128520.2207689791</v>
       </c>
       <c r="AH2">
-        <v>0.480385285428418</v>
+        <v>0.4799031535600744</v>
       </c>
       <c r="AI2">
-        <v>0.615141850023759</v>
+        <v>0.5987062681711945</v>
       </c>
       <c r="AJ2">
-        <v>0.3748747239067743</v>
+        <v>0.3796709549943575</v>
       </c>
       <c r="AK2">
-        <v>0.509028278512668</v>
+        <v>0.4973907941779214</v>
       </c>
       <c r="AL2">
-        <v>2244.076</v>
+        <v>2607.354</v>
       </c>
       <c r="AM2">
-        <v>2244.076</v>
+        <v>2607.354</v>
       </c>
       <c r="AN2">
-        <v>9.08105978373645</v>
+        <v>30.07442478564209</v>
       </c>
       <c r="AO2">
-        <v>9.374119236603395</v>
+        <v>0.05443104388587045</v>
       </c>
       <c r="AP2">
-        <v>5.968144650318473</v>
+        <v>20.18820311147541</v>
       </c>
       <c r="AQ2">
-        <v>9.374119236603395</v>
+        <v>0.05443104388587045</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Equity Investment Life Holding Company (NYSE:AEL)</t>
+          <t>Principal Financial Group, Inc. (NasdaqGS:PFG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,112 +725,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.107</v>
+        <v>0.00544</v>
       </c>
       <c r="E3">
-        <v>0.388</v>
+        <v>-0.0655</v>
+      </c>
+      <c r="F3">
+        <v>0.0898</v>
       </c>
       <c r="G3">
-        <v>0.3417633534727049</v>
+        <v>0.4513787789479665</v>
       </c>
       <c r="H3">
-        <v>0.3417633534727049</v>
+        <v>0.4513787789479665</v>
       </c>
       <c r="I3">
-        <v>0.9267251592520813</v>
+        <v>0.1285138202253424</v>
       </c>
       <c r="J3">
-        <v>0.7266454482190176</v>
+        <v>0.1054554893569252</v>
       </c>
       <c r="K3">
-        <v>1332.5</v>
+        <v>1533.4</v>
       </c>
       <c r="L3">
-        <v>0.7124525477196172</v>
+        <v>0.1088961956637527</v>
       </c>
       <c r="M3">
-        <v>554</v>
+        <v>1362.8</v>
       </c>
       <c r="N3">
-        <v>0.1416988515742896</v>
+        <v>0.0726598030486407</v>
       </c>
       <c r="O3">
-        <v>0.4157598499061914</v>
+        <v>0.8887439676535803</v>
       </c>
       <c r="P3">
-        <v>31.5</v>
+        <v>622.7</v>
       </c>
       <c r="Q3">
-        <v>0.008056884159909967</v>
+        <v>0.03320021966421233</v>
       </c>
       <c r="R3">
-        <v>0.02363977485928705</v>
+        <v>0.4060910395200208</v>
       </c>
       <c r="S3">
-        <v>522.5</v>
+        <v>740.1000000000001</v>
       </c>
       <c r="T3">
-        <v>0.9431407942238267</v>
+        <v>0.5430730848253595</v>
       </c>
       <c r="U3">
-        <v>1808.1</v>
+        <v>4564.3</v>
       </c>
       <c r="V3">
-        <v>0.4624651507788322</v>
+        <v>0.2433527583320448</v>
       </c>
       <c r="W3">
-        <v>0.2090130505709625</v>
+        <v>0.162329825750037</v>
       </c>
       <c r="X3">
-        <v>0.09431889800585067</v>
+        <v>0.08136618415647326</v>
       </c>
       <c r="Y3">
-        <v>0.1146941525651118</v>
+        <v>0.08096364159356378</v>
+      </c>
+      <c r="Z3">
+        <v>1.656118565942421</v>
+      </c>
+      <c r="AA3">
+        <v>0.1746467938045472</v>
       </c>
       <c r="AB3">
-        <v>0.08346477127854775</v>
+        <v>0.07179958823925493</v>
+      </c>
+      <c r="AC3">
+        <v>0.1028472055652923</v>
       </c>
       <c r="AD3">
-        <v>873.5</v>
+        <v>4529.4</v>
       </c>
       <c r="AE3">
-        <v>10.77967325416197</v>
+        <v>190.2917163044302</v>
       </c>
       <c r="AF3">
-        <v>884.2796732541619</v>
+        <v>4719.69171630443</v>
       </c>
       <c r="AG3">
-        <v>-923.820326745838</v>
+        <v>155.3917163044298</v>
       </c>
       <c r="AH3">
-        <v>0.1844562834063732</v>
+        <v>0.201046762669095</v>
       </c>
       <c r="AI3">
-        <v>0.2159476575172314</v>
+        <v>0.3005772607609781</v>
       </c>
       <c r="AJ3">
-        <v>-0.3093963681862009</v>
+        <v>0.008216874798164015</v>
       </c>
       <c r="AK3">
-        <v>-0.4039830935838307</v>
+        <v>0.01395175275875867</v>
       </c>
       <c r="AL3">
-        <v>33.5</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>33.5</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.499197055680331</v>
-      </c>
-      <c r="AO3">
-        <v>51.72835820895523</v>
+        <v>2.097818535500903</v>
       </c>
       <c r="AP3">
-        <v>-0.5279546503596607</v>
-      </c>
-      <c r="AQ3">
-        <v>51.72835820895523</v>
+        <v>0.07197059714901106</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Novus Acquisition &amp; Development Corp. (OTCPK:NDEV)</t>
+          <t>Primerica, Inc. (NYSE:PRI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -849,80 +855,122 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="E4">
+        <v>0.0307</v>
+      </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.2383616594531827</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.2383616594531827</v>
       </c>
       <c r="I4">
-        <v>0.3609022556390977</v>
+        <v>0.2486003962168326</v>
       </c>
       <c r="J4">
-        <v>0.3609022556390977</v>
+        <v>0.19095744255745</v>
       </c>
       <c r="K4">
-        <v>0.096</v>
+        <v>472.3</v>
       </c>
       <c r="L4">
-        <v>0.3609022556390977</v>
+        <v>0.1661916323586333</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>436.1</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0604971839192076</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.9233538005504974</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>91.2</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.01265155508697944</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.1930976074528901</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>344.9</v>
+      </c>
+      <c r="T4">
+        <v>0.7908736528319193</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>468.8</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.0650334322892101</v>
+      </c>
+      <c r="W4">
+        <v>0.2915432098765432</v>
       </c>
       <c r="X4">
-        <v>0.08626698429789872</v>
+        <v>0.08255708823833752</v>
+      </c>
+      <c r="Y4">
+        <v>0.2089861216382057</v>
+      </c>
+      <c r="Z4">
+        <v>0.8865387969776758</v>
+      </c>
+      <c r="AA4">
+        <v>0.1692911813988153</v>
       </c>
       <c r="AB4">
-        <v>0.08626698429789872</v>
+        <v>0.07141769155396553</v>
+      </c>
+      <c r="AC4">
+        <v>0.09787348984484977</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2089.1</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>44.51266995691637</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2133.612669956916</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1664.812669956916</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.2283840825865888</v>
+      </c>
+      <c r="AI4">
+        <v>0.4798827264036905</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>0.1876180824536136</v>
+      </c>
+      <c r="AK4">
+        <v>0.4185772676441227</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>92.40000000000001</v>
+      </c>
+      <c r="AN4">
+        <v>2.789185580774366</v>
+      </c>
+      <c r="AO4">
+        <v>7.634199134199133</v>
+      </c>
+      <c r="AP4">
+        <v>2.222713845069314</v>
+      </c>
+      <c r="AQ4">
+        <v>7.634199134199133</v>
       </c>
     </row>
     <row r="5">
@@ -933,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>F&amp;G Annuities &amp; Life, Inc. (NYSE:FG)</t>
+          <t>Aflac Incorporated (NYSE:AFL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -942,112 +990,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.353</v>
+        <v>-0.027</v>
       </c>
       <c r="E5">
-        <v>0.665</v>
+        <v>-0.0257</v>
+      </c>
+      <c r="F5">
+        <v>0.08039999999999999</v>
       </c>
       <c r="G5">
-        <v>0.3436406067677946</v>
+        <v>0.2534705974107004</v>
       </c>
       <c r="H5">
-        <v>0.3436406067677946</v>
+        <v>0.2534705974107004</v>
       </c>
       <c r="I5">
-        <v>0.2790396090767829</v>
+        <v>0.2843986485503273</v>
       </c>
       <c r="J5">
-        <v>0.2115397468379067</v>
+        <v>0.2369536881153347</v>
       </c>
       <c r="K5">
-        <v>702</v>
+        <v>4370</v>
       </c>
       <c r="L5">
-        <v>0.2047841306884481</v>
+        <v>0.2272136432173868</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>3669</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.07610249049496694</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.8395881006864988</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>969</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.02009902242835186</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.2217391304347826</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2700</v>
+      </c>
+      <c r="T5">
+        <v>0.7358953393295176</v>
       </c>
       <c r="U5">
-        <v>1384</v>
+        <v>5502</v>
       </c>
       <c r="V5">
-        <v>0.5533122776156398</v>
+        <v>0.1141226227046356</v>
+      </c>
+      <c r="W5">
+        <v>0.1809373964889036</v>
       </c>
       <c r="X5">
-        <v>0.09456836123051325</v>
+        <v>0.0813957205635448</v>
+      </c>
+      <c r="Y5">
+        <v>0.09954167592535881</v>
       </c>
       <c r="Z5">
-        <v>279.5833882337852</v>
+        <v>0.6354906519152869</v>
       </c>
       <c r="AA5">
-        <v>59.14299916705912</v>
+        <v>0.1505818537341456</v>
       </c>
       <c r="AB5">
-        <v>0.08502527521290887</v>
+        <v>0.0726692099158721</v>
       </c>
       <c r="AC5">
-        <v>59.05797389184621</v>
+        <v>0.07791264381827349</v>
       </c>
       <c r="AD5">
-        <v>571</v>
+        <v>12074</v>
       </c>
       <c r="AE5">
-        <v>12.26110042394055</v>
+        <v>110.8039621577752</v>
       </c>
       <c r="AF5">
-        <v>583.2611004239405</v>
+        <v>12184.80396215778</v>
       </c>
       <c r="AG5">
-        <v>-800.7388995760595</v>
+        <v>6682.803962157775</v>
       </c>
       <c r="AH5">
-        <v>0.1890904674716209</v>
+        <v>0.2017481784883405</v>
       </c>
       <c r="AI5">
-        <v>0.2582788590364709</v>
+        <v>0.3495975353332257</v>
       </c>
       <c r="AJ5">
-        <v>-0.4708674680236067</v>
+        <v>0.1217399225017806</v>
       </c>
       <c r="AK5">
-        <v>-0.9159036118475027</v>
+        <v>0.2276794970003777</v>
       </c>
       <c r="AL5">
-        <v>31</v>
+        <v>203</v>
       </c>
       <c r="AM5">
-        <v>31</v>
+        <v>203</v>
       </c>
       <c r="AN5">
-        <v>0.562007874015748</v>
+        <v>2.180603214737222</v>
       </c>
       <c r="AO5">
-        <v>30.87096774193548</v>
+        <v>26.83743842364532</v>
       </c>
       <c r="AP5">
-        <v>-0.7881288381654128</v>
+        <v>1.206935879024341</v>
       </c>
       <c r="AQ5">
-        <v>30.87096774193548</v>
+        <v>26.83743842364532</v>
       </c>
     </row>
     <row r="6">
@@ -1058,7 +1118,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Midwest Holding Inc. (NasdaqCM:MDWT)</t>
+          <t>Globe Life Inc. (NYSE:GL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1067,109 +1127,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.537</v>
+        <v>0.0451</v>
+      </c>
+      <c r="E6">
+        <v>-0.129</v>
+      </c>
+      <c r="F6">
+        <v>0.07000000000000001</v>
       </c>
       <c r="G6">
-        <v>-0.3146666666666667</v>
+        <v>0.1905099811394745</v>
       </c>
       <c r="H6">
-        <v>-0.3146666666666667</v>
+        <v>0.1905099811394745</v>
       </c>
       <c r="I6">
-        <v>0.2041031360922816</v>
+        <v>0.1983081429709078</v>
       </c>
       <c r="J6">
-        <v>0.1020515680461408</v>
+        <v>0.1621223378528986</v>
       </c>
       <c r="K6">
-        <v>9.9</v>
+        <v>783.6</v>
       </c>
       <c r="L6">
-        <v>0.264</v>
+        <v>0.1463277996676066</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>568.2</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.04959803074344672</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.725114854517611</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.00725377746353471</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.1060490045941807</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>485.1</v>
+      </c>
+      <c r="T6">
+        <v>0.8537486800422386</v>
       </c>
       <c r="U6">
-        <v>208.5</v>
+        <v>85.5</v>
       </c>
       <c r="V6">
-        <v>4.389473684210526</v>
+        <v>0.007463272841542933</v>
       </c>
       <c r="W6">
-        <v>0.1235955056179775</v>
+        <v>0.1796588407923698</v>
       </c>
       <c r="X6">
-        <v>0.08824610420635261</v>
+        <v>0.07990351216036089</v>
       </c>
       <c r="Y6">
-        <v>0.03534940141162493</v>
+        <v>0.09975532863200888</v>
       </c>
       <c r="Z6">
-        <v>13.68282562269671</v>
+        <v>0.9123993201796244</v>
       </c>
       <c r="AA6">
-        <v>1.396353810098112</v>
+        <v>0.1479203108429161</v>
       </c>
       <c r="AB6">
-        <v>0.08577105061102079</v>
+        <v>0.07230734700646796</v>
       </c>
       <c r="AC6">
-        <v>1.310582759487091</v>
+        <v>0.07561296383644814</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2246.1</v>
       </c>
       <c r="AE6">
-        <v>2.640661982697205</v>
+        <v>12.75031788245926</v>
       </c>
       <c r="AF6">
-        <v>2.640661982697205</v>
+        <v>2258.850317882459</v>
       </c>
       <c r="AG6">
-        <v>-205.8593380173028</v>
+        <v>2173.350317882459</v>
       </c>
       <c r="AH6">
-        <v>0.05266508016205407</v>
+        <v>0.1646998542121746</v>
       </c>
       <c r="AI6">
-        <v>0.0620738338244773</v>
+        <v>0.3282282221673311</v>
       </c>
       <c r="AJ6">
-        <v>1.299950736058331</v>
+        <v>0.159459865746084</v>
       </c>
       <c r="AK6">
-        <v>1.240420337154153</v>
+        <v>0.3197772684608692</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>101.3</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>101.3</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>2.067641833362484</v>
+      </c>
+      <c r="AO6">
+        <v>10.47186574531096</v>
       </c>
       <c r="AP6">
-        <v>-24.44304654681819</v>
+        <v>2.000672292331341</v>
+      </c>
+      <c r="AQ6">
+        <v>10.47186574531096</v>
       </c>
     </row>
     <row r="7">
@@ -1180,7 +1255,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Principal Financial Group, Inc. (NasdaqGS:PFG)</t>
+          <t>UTG, Inc. (OTCPK:UTGN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1189,118 +1264,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.05139999999999999</v>
+        <v>-0.0611</v>
       </c>
       <c r="E7">
-        <v>0.243</v>
-      </c>
-      <c r="F7">
-        <v>0.055</v>
+        <v>-0.117</v>
       </c>
       <c r="G7">
-        <v>0.12777955332138</v>
+        <v>1.029017857142857</v>
       </c>
       <c r="H7">
-        <v>0.12777955332138</v>
+        <v>1.029017857142857</v>
       </c>
       <c r="I7">
-        <v>0.3618397520645849</v>
+        <v>0.4397321428571428</v>
       </c>
       <c r="J7">
-        <v>0.290044082043427</v>
+        <v>0.3634520772594752</v>
       </c>
       <c r="K7">
-        <v>5292.9</v>
+        <v>16.1</v>
       </c>
       <c r="L7">
-        <v>0.2867117714929553</v>
+        <v>0.3593750000000001</v>
       </c>
       <c r="M7">
-        <v>2451.3</v>
+        <v>0.846</v>
       </c>
       <c r="N7">
-        <v>0.1193787803523946</v>
+        <v>0.008886554621848739</v>
       </c>
       <c r="O7">
-        <v>0.4631298531995693</v>
+        <v>0.05254658385093167</v>
       </c>
       <c r="P7">
-        <v>654.6</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.03187914560383368</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.1236751119424134</v>
+        <v>-0</v>
       </c>
       <c r="S7">
-        <v>1796.7</v>
+        <v>0.846</v>
       </c>
       <c r="T7">
-        <v>0.7329580222738955</v>
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>4239.6</v>
+        <v>27.6</v>
       </c>
       <c r="V7">
-        <v>0.206469333489174</v>
+        <v>0.2899159663865546</v>
       </c>
       <c r="W7">
-        <v>0.3293509305755194</v>
+        <v>0.1161616161616162</v>
       </c>
       <c r="X7">
-        <v>0.09468241965674198</v>
+        <v>0.07460816978577145</v>
       </c>
       <c r="Y7">
-        <v>0.2346685109187774</v>
+        <v>0.04155344637584472</v>
       </c>
       <c r="Z7">
-        <v>1.159983389079865</v>
+        <v>0.367816091954023</v>
       </c>
       <c r="AA7">
-        <v>0.3364463172712928</v>
+        <v>0.1336835226701518</v>
       </c>
       <c r="AB7">
-        <v>0.08336244719388838</v>
+        <v>0.07460816978577145</v>
       </c>
       <c r="AC7">
-        <v>0.2530838700774044</v>
+        <v>0.05907535288438037</v>
       </c>
       <c r="AD7">
-        <v>4654</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>199.9244453065915</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>4853.924445306591</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>614.3244453065909</v>
+        <v>-27.6</v>
       </c>
       <c r="AH7">
-        <v>0.1911917886049032</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>0.3325215153977927</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>0.02904864906083566</v>
+        <v>-0.4082840236686391</v>
       </c>
       <c r="AK7">
-        <v>0.05931075387750449</v>
+        <v>-0.2185273159144893</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="AN7">
-        <v>0.6636530865429863</v>
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>364.8148148148148</v>
       </c>
       <c r="AP7">
-        <v>0.08760170052998001</v>
+        <v>-1.346341463414634</v>
+      </c>
+      <c r="AQ7">
+        <v>364.8148148148148</v>
       </c>
     </row>
     <row r="8">
@@ -1311,7 +1389,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UTG, Inc. (OTCPK:UTGN)</t>
+          <t>Unum Group (NYSE:UNM)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1320,118 +1398,124 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.184</v>
+        <v>0.0118</v>
+      </c>
+      <c r="E8">
+        <v>0.163</v>
+      </c>
+      <c r="F8">
+        <v>0.0692</v>
       </c>
       <c r="G8">
-        <v>0.2914171656686627</v>
+        <v>0.1578943072842277</v>
       </c>
       <c r="H8">
-        <v>0.2914171656686627</v>
+        <v>0.1578943072842277</v>
       </c>
       <c r="I8">
-        <v>0.499001996007984</v>
+        <v>0.135798912473702</v>
       </c>
       <c r="J8">
-        <v>0.38562874251497</v>
+        <v>0.1064497510722725</v>
       </c>
       <c r="K8">
-        <v>19.2</v>
+        <v>1149.4</v>
       </c>
       <c r="L8">
-        <v>0.3832335329341317</v>
+        <v>0.09380942664762294</v>
       </c>
       <c r="M8">
-        <v>0.748</v>
+        <v>509.7</v>
       </c>
       <c r="N8">
-        <v>0.009444444444444445</v>
+        <v>0.0577891156462585</v>
       </c>
       <c r="O8">
-        <v>0.03895833333333334</v>
+        <v>0.4434487558726292</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>271.5</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.03078231292517007</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.2362101966243257</v>
       </c>
       <c r="S8">
-        <v>0.748</v>
+        <v>238.2</v>
       </c>
       <c r="T8">
-        <v>1</v>
+        <v>0.4673337257210123</v>
       </c>
       <c r="U8">
-        <v>24.8</v>
+        <v>165.9</v>
       </c>
       <c r="V8">
-        <v>0.3131313131313131</v>
+        <v>0.01880952380952381</v>
       </c>
       <c r="W8">
-        <v>0.138328530259366</v>
+        <v>0.1327328367688666</v>
       </c>
       <c r="X8">
-        <v>0.08986296795683044</v>
+        <v>0.08590972487021625</v>
       </c>
       <c r="Y8">
-        <v>0.04846556230253554</v>
+        <v>0.04682311189865032</v>
       </c>
       <c r="Z8">
-        <v>0.4367916303400174</v>
+        <v>1.04503219874607</v>
       </c>
       <c r="AA8">
-        <v>0.1684394071490845</v>
+        <v>0.1112434174190287</v>
       </c>
       <c r="AB8">
-        <v>0.08540306263969002</v>
+        <v>0.07047059200789858</v>
       </c>
       <c r="AC8">
-        <v>0.08303634450939451</v>
+        <v>0.0407728254111301</v>
       </c>
       <c r="AD8">
-        <v>8</v>
+        <v>3644.5</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>67.11912457982696</v>
       </c>
       <c r="AF8">
-        <v>8</v>
+        <v>3711.619124579827</v>
       </c>
       <c r="AG8">
-        <v>-16.8</v>
+        <v>3545.719124579827</v>
       </c>
       <c r="AH8">
-        <v>0.09174311926605504</v>
+        <v>0.2961803329387633</v>
       </c>
       <c r="AI8">
-        <v>0.05434782608695653</v>
+        <v>0.2784469117384214</v>
       </c>
       <c r="AJ8">
-        <v>-0.2692307692307692</v>
+        <v>0.2867378022141762</v>
       </c>
       <c r="AK8">
-        <v>-0.1372549019607843</v>
+        <v>0.2693533761763079</v>
       </c>
       <c r="AL8">
-        <v>0.076</v>
+        <v>192.8</v>
       </c>
       <c r="AM8">
-        <v>0.076</v>
+        <v>192.8</v>
       </c>
       <c r="AN8">
-        <v>0.2898550724637681</v>
+        <v>2.041507954290836</v>
       </c>
       <c r="AO8">
-        <v>328.9473684210527</v>
+        <v>8.605290456431534</v>
       </c>
       <c r="AP8">
-        <v>-0.6086956521739131</v>
+        <v>1.986174728086392</v>
       </c>
       <c r="AQ8">
-        <v>328.9473684210527</v>
+        <v>8.605290456431534</v>
       </c>
     </row>
     <row r="9">
@@ -1442,7 +1526,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aflac Incorporated (NYSE:AFL)</t>
+          <t>Genworth Financial, Inc. (NYSE:GNW)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1451,121 +1535,121 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.0114</v>
+        <v>-0.0039</v>
       </c>
       <c r="E9">
-        <v>0.128</v>
+        <v>-0.147</v>
       </c>
       <c r="G9">
-        <v>0.2678230122324159</v>
+        <v>0.1641851106639839</v>
       </c>
       <c r="H9">
-        <v>0.2678230122324159</v>
+        <v>0.1641851106639839</v>
       </c>
       <c r="I9">
-        <v>0.2660969150957289</v>
+        <v>0.1153257864515084</v>
       </c>
       <c r="J9">
-        <v>0.2532228738345085</v>
+        <v>0.08414252999407634</v>
       </c>
       <c r="K9">
-        <v>5055</v>
+        <v>362</v>
       </c>
       <c r="L9">
-        <v>0.2415424311926606</v>
+        <v>0.04855801475519785</v>
       </c>
       <c r="M9">
-        <v>3374</v>
+        <v>291</v>
       </c>
       <c r="N9">
-        <v>0.07542783049975968</v>
+        <v>0.09659109768646065</v>
       </c>
       <c r="O9">
-        <v>0.667457962413452</v>
+        <v>0.8038674033149171</v>
       </c>
       <c r="P9">
-        <v>948</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.02119311894302673</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.1875370919881306</v>
+        <v>-0</v>
       </c>
       <c r="S9">
-        <v>2426</v>
+        <v>291</v>
       </c>
       <c r="T9">
-        <v>0.7190278601066983</v>
+        <v>1</v>
       </c>
       <c r="U9">
-        <v>4710</v>
+        <v>1993</v>
       </c>
       <c r="V9">
-        <v>0.1052949263941518</v>
+        <v>0.6615328442924951</v>
       </c>
       <c r="W9">
-        <v>0.1506616595135908</v>
+        <v>0.03896243676676354</v>
       </c>
       <c r="X9">
-        <v>0.09486839055666468</v>
+        <v>0.09727039562569109</v>
       </c>
       <c r="Y9">
-        <v>0.05579326895692616</v>
+        <v>-0.05830795885892755</v>
       </c>
       <c r="Z9">
-        <v>0.5470711943835191</v>
+        <v>0.7554545253140071</v>
       </c>
       <c r="AA9">
-        <v>0.1385309400338718</v>
+        <v>0.06356585505539455</v>
       </c>
       <c r="AB9">
-        <v>0.08443453531164365</v>
+        <v>0.06821485153037428</v>
       </c>
       <c r="AC9">
-        <v>0.05409640472222811</v>
+        <v>-0.004648996474979725</v>
       </c>
       <c r="AD9">
-        <v>10712</v>
+        <v>2486</v>
       </c>
       <c r="AE9">
-        <v>95.61880438293053</v>
+        <v>56.23131002002509</v>
       </c>
       <c r="AF9">
-        <v>10807.61880438293</v>
+        <v>2542.231310020025</v>
       </c>
       <c r="AG9">
-        <v>6097.61880438293</v>
+        <v>549.2313100200249</v>
       </c>
       <c r="AH9">
-        <v>0.1945947115662562</v>
+        <v>0.4576530596218768</v>
       </c>
       <c r="AI9">
-        <v>0.3091457851659402</v>
+        <v>0.2226076898976197</v>
       </c>
       <c r="AJ9">
-        <v>0.1199631028003802</v>
+        <v>0.1541948067541306</v>
       </c>
       <c r="AK9">
-        <v>0.2015767155220955</v>
+        <v>0.05826008633481364</v>
       </c>
       <c r="AL9">
-        <v>228</v>
+        <v>116</v>
       </c>
       <c r="AM9">
-        <v>228</v>
+        <v>116</v>
       </c>
       <c r="AN9">
-        <v>1.900638750887154</v>
+        <v>355.1428571428572</v>
       </c>
       <c r="AO9">
-        <v>24.29824561403509</v>
+        <v>7.448275862068965</v>
       </c>
       <c r="AP9">
-        <v>1.081905394674047</v>
+        <v>78.46161571714642</v>
       </c>
       <c r="AQ9">
-        <v>24.29824561403509</v>
+        <v>7.448275862068965</v>
       </c>
     </row>
     <row r="10">
@@ -1576,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Primerica, Inc. (NYSE:PRI)</t>
+          <t>CNO Financial Group, Inc. (NYSE:CNO)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1585,121 +1669,118 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.111</v>
-      </c>
-      <c r="E10">
-        <v>0.0295</v>
+        <v>-0.0311</v>
       </c>
       <c r="G10">
-        <v>0.2594036941184812</v>
+        <v>0.2530696979670372</v>
       </c>
       <c r="H10">
-        <v>0.2594036941184812</v>
+        <v>0.2530696979670372</v>
       </c>
       <c r="I10">
-        <v>0.2278177246752592</v>
+        <v>0.07486908883916177</v>
       </c>
       <c r="J10">
-        <v>0.1570636338780258</v>
+        <v>0.05540312574097971</v>
       </c>
       <c r="K10">
-        <v>276</v>
+        <v>44.4</v>
       </c>
       <c r="L10">
-        <v>0.09784805190201015</v>
+        <v>0.01124079090609889</v>
       </c>
       <c r="M10">
-        <v>430.3</v>
+        <v>173.2</v>
       </c>
       <c r="N10">
-        <v>0.08222973876817825</v>
+        <v>0.05534253578732106</v>
       </c>
       <c r="O10">
-        <v>1.559057971014493</v>
+        <v>3.900900900900901</v>
       </c>
       <c r="P10">
-        <v>82.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="Q10">
-        <v>0.01568919719467217</v>
+        <v>0.02156825153374233</v>
       </c>
       <c r="R10">
-        <v>0.297463768115942</v>
+        <v>1.52027027027027</v>
       </c>
       <c r="S10">
-        <v>348.1999999999999</v>
+        <v>105.7</v>
       </c>
       <c r="T10">
-        <v>0.8092028817104345</v>
+        <v>0.6102771362586605</v>
       </c>
       <c r="U10">
-        <v>438</v>
+        <v>460.8</v>
       </c>
       <c r="V10">
-        <v>0.08370119818838503</v>
+        <v>0.147239263803681</v>
       </c>
       <c r="W10">
-        <v>0.1314974510457859</v>
+        <v>0.03420910701903074</v>
       </c>
       <c r="X10">
-        <v>0.1009503917768379</v>
+        <v>0.1106057546463296</v>
       </c>
       <c r="Y10">
-        <v>0.03054705926894796</v>
+        <v>-0.07639664762729888</v>
       </c>
       <c r="Z10">
-        <v>0.7843725644509367</v>
+        <v>0.833246678763771</v>
       </c>
       <c r="AA10">
-        <v>0.1231964052868901</v>
+        <v>0.04616447051680293</v>
       </c>
       <c r="AB10">
-        <v>0.08183081832758599</v>
+        <v>0.06660738874238674</v>
       </c>
       <c r="AC10">
-        <v>0.04136558695930416</v>
+        <v>-0.02044291822558381</v>
       </c>
       <c r="AD10">
-        <v>2106.8</v>
+        <v>4148</v>
       </c>
       <c r="AE10">
-        <v>51.52272004248191</v>
+        <v>46.87292997097437</v>
       </c>
       <c r="AF10">
-        <v>2158.322720042482</v>
+        <v>4194.872929970974</v>
       </c>
       <c r="AG10">
-        <v>1720.322720042482</v>
+        <v>3734.072929970974</v>
       </c>
       <c r="AH10">
-        <v>0.2920115929113927</v>
+        <v>0.5727201083378975</v>
       </c>
       <c r="AI10">
-        <v>0.5712383192132976</v>
+        <v>0.6893823486559018</v>
       </c>
       <c r="AJ10">
-        <v>0.247413723004111</v>
+        <v>0.5440342172578968</v>
       </c>
       <c r="AK10">
-        <v>0.5150169202874515</v>
+        <v>0.6639328086930367</v>
       </c>
       <c r="AL10">
-        <v>92.7</v>
+        <v>222.7</v>
       </c>
       <c r="AM10">
-        <v>92.7</v>
+        <v>222.7</v>
       </c>
       <c r="AN10">
-        <v>3.059052431357176</v>
+        <v>6.2451068955134</v>
       </c>
       <c r="AO10">
-        <v>6.936353829557713</v>
+        <v>1.269420745397396</v>
       </c>
       <c r="AP10">
-        <v>2.49789130409386</v>
+        <v>5.621910463672048</v>
       </c>
       <c r="AQ10">
-        <v>6.936353829557713</v>
+        <v>1.269420745397396</v>
       </c>
     </row>
     <row r="11">
@@ -1710,7 +1791,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unum Group (NYSE:UNM)</t>
+          <t>MetLife, Inc. (NYSE:MET)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1719,124 +1800,121 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0125</v>
-      </c>
-      <c r="E11">
-        <v>0.0414</v>
+        <v>-0.0105</v>
       </c>
       <c r="F11">
-        <v>0.155</v>
+        <v>0.0917</v>
       </c>
       <c r="G11">
-        <v>0.1221206245194076</v>
+        <v>0.06526550384597526</v>
       </c>
       <c r="H11">
-        <v>0.1221206245194076</v>
+        <v>0.06526550384597526</v>
       </c>
       <c r="I11">
-        <v>0.1391383272396863</v>
+        <v>0.03921882951733422</v>
       </c>
       <c r="J11">
-        <v>0.1136458105747212</v>
+        <v>0.03921882951733422</v>
       </c>
       <c r="K11">
-        <v>1194.3</v>
+        <v>-196</v>
       </c>
       <c r="L11">
-        <v>0.09982113603690949</v>
+        <v>-0.003033445281909213</v>
       </c>
       <c r="M11">
-        <v>435.9</v>
+        <v>4413</v>
       </c>
       <c r="N11">
-        <v>0.05340275650842266</v>
+        <v>0.09015542771222175</v>
       </c>
       <c r="O11">
-        <v>0.3649836724441095</v>
+        <v>-22.51530612244898</v>
       </c>
       <c r="P11">
-        <v>249.8</v>
+        <v>1573</v>
       </c>
       <c r="Q11">
-        <v>0.03060336906584992</v>
+        <v>0.03213561925930768</v>
       </c>
       <c r="R11">
-        <v>0.2091601775098384</v>
+        <v>-8.025510204081632</v>
       </c>
       <c r="S11">
-        <v>186.1</v>
+        <v>2840</v>
       </c>
       <c r="T11">
-        <v>0.4269327827483367</v>
+        <v>0.6435531384545661</v>
       </c>
       <c r="U11">
-        <v>143.3</v>
+        <v>14912</v>
       </c>
       <c r="V11">
-        <v>0.01755589586523737</v>
+        <v>0.3046448533978361</v>
       </c>
       <c r="W11">
-        <v>0.1074184670180425</v>
+        <v>-0.007816238634550965</v>
       </c>
       <c r="X11">
-        <v>0.1018223453279609</v>
+        <v>0.1339881493086953</v>
       </c>
       <c r="Y11">
-        <v>0.005596121690081612</v>
+        <v>-0.1418043879432463</v>
       </c>
       <c r="Z11">
-        <v>0.8445399017465589</v>
+        <v>0.6518219120306374</v>
       </c>
       <c r="AA11">
-        <v>0.09597842169668311</v>
+        <v>0.02556369244359239</v>
       </c>
       <c r="AB11">
-        <v>0.08164748812711778</v>
+        <v>0.06498892768878878</v>
       </c>
       <c r="AC11">
-        <v>0.01433093356956533</v>
+        <v>-0.03942523524519639</v>
       </c>
       <c r="AD11">
-        <v>3485.6</v>
+        <v>107168</v>
       </c>
       <c r="AE11">
-        <v>80.96698786748441</v>
+        <v>1059.76884198242</v>
       </c>
       <c r="AF11">
-        <v>3566.566987867484</v>
+        <v>108227.7688419824</v>
       </c>
       <c r="AG11">
-        <v>3423.266987867484</v>
+        <v>93315.76884198243</v>
       </c>
       <c r="AH11">
-        <v>0.3040793433575519</v>
+        <v>0.6885744461745394</v>
       </c>
       <c r="AI11">
-        <v>0.2917182599610129</v>
+        <v>0.8069306186892969</v>
       </c>
       <c r="AJ11">
-        <v>0.2954717621588886</v>
+        <v>0.6559311963728023</v>
       </c>
       <c r="AK11">
-        <v>0.283318133280634</v>
+        <v>0.7827796913689515</v>
       </c>
       <c r="AL11">
-        <v>191.9</v>
+        <v>1024</v>
       </c>
       <c r="AM11">
-        <v>191.9</v>
+        <v>1024</v>
       </c>
       <c r="AN11">
-        <v>1.942704269312229</v>
+        <v>33.88175782484983</v>
       </c>
       <c r="AO11">
-        <v>8.64147993746743</v>
+        <v>2.4423828125</v>
       </c>
       <c r="AP11">
-        <v>1.9079628736303</v>
+        <v>29.50229808472413</v>
       </c>
       <c r="AQ11">
-        <v>8.64147993746743</v>
+        <v>2.4423828125</v>
       </c>
     </row>
     <row r="12">
@@ -1847,7 +1925,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Globe Life Inc. (NYSE:GL)</t>
+          <t>National Western Life Group, Inc. (NasdaqGS:NWLI)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1856,121 +1934,112 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0496</v>
-      </c>
-      <c r="E12">
-        <v>0.04650000000000001</v>
+        <v>-0.0285</v>
       </c>
       <c r="G12">
-        <v>0.1973177123477725</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="H12">
-        <v>0.1973177123477725</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="I12">
-        <v>0.1843233894410516</v>
+        <v>-0.01846764346764346</v>
       </c>
       <c r="J12">
-        <v>0.1502548433206263</v>
+        <v>-0.01846764346764346</v>
       </c>
       <c r="K12">
-        <v>706.1</v>
+        <v>-21.5</v>
       </c>
       <c r="L12">
-        <v>0.1360605827038693</v>
+        <v>-0.03281440781440781</v>
       </c>
       <c r="M12">
-        <v>563.9</v>
+        <v>1.27</v>
       </c>
       <c r="N12">
-        <v>0.04809012527823024</v>
+        <v>0.0007231110858053864</v>
       </c>
       <c r="O12">
-        <v>0.7986120946041637</v>
+        <v>-0.05906976744186047</v>
       </c>
       <c r="P12">
-        <v>80.40000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="Q12">
-        <v>0.00685661654968915</v>
+        <v>0.0007231110858053864</v>
       </c>
       <c r="R12">
-        <v>0.1138648916584053</v>
+        <v>-0.05906976744186047</v>
       </c>
       <c r="S12">
-        <v>483.5</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>0.8574215286398298</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>85.59999999999999</v>
+        <v>320.7</v>
       </c>
       <c r="V12">
-        <v>0.007300079311609343</v>
+        <v>0.1825997836360531</v>
       </c>
       <c r="W12">
-        <v>0.08202643990613601</v>
+        <v>-0.01109734695984309</v>
       </c>
       <c r="X12">
-        <v>0.09258733037963807</v>
+        <v>0.07461957710285574</v>
       </c>
       <c r="Y12">
-        <v>-0.01056089047350206</v>
+        <v>-0.08571692406269883</v>
       </c>
       <c r="Z12">
-        <v>0.5195118935486769</v>
+        <v>0.4076173175147289</v>
       </c>
       <c r="AA12">
-        <v>0.07805917816835833</v>
+        <v>-0.007527731291099236</v>
       </c>
       <c r="AB12">
-        <v>0.08397653214013245</v>
+        <v>0.07460408927156463</v>
       </c>
       <c r="AC12">
-        <v>-0.00591735397177412</v>
+        <v>-0.08213182056266387</v>
       </c>
       <c r="AD12">
-        <v>2062.3</v>
+        <v>0.746</v>
       </c>
       <c r="AE12">
-        <v>19.47669078359357</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>2081.776690783594</v>
+        <v>0.746</v>
       </c>
       <c r="AG12">
-        <v>1996.176690783594</v>
+        <v>-319.954</v>
       </c>
       <c r="AH12">
-        <v>0.1507695130327861</v>
+        <v>0.0004245762489997416</v>
       </c>
       <c r="AI12">
-        <v>0.3230878451916838</v>
+        <v>0.0003323167825320757</v>
       </c>
       <c r="AJ12">
-        <v>0.1454719089366643</v>
+        <v>-0.2227555199095483</v>
       </c>
       <c r="AK12">
-        <v>0.3139740176274681</v>
+        <v>-0.1662836395990741</v>
       </c>
       <c r="AL12">
-        <v>85.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>85.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AN12">
-        <v>2.098477756522447</v>
-      </c>
-      <c r="AO12">
-        <v>11.1943793911007</v>
+        <v>-0.8515981735159818</v>
       </c>
       <c r="AP12">
-        <v>2.031194483682277</v>
-      </c>
-      <c r="AQ12">
-        <v>11.1943793911007</v>
+        <v>365.2442922374429</v>
       </c>
     </row>
     <row r="13">
@@ -1981,7 +2050,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CNO Financial Group, Inc. (NYSE:CNO)</t>
+          <t>Kansas City Life Insurance Company (OTCPK:KCLI)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1990,121 +2059,112 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.0268</v>
-      </c>
-      <c r="E13">
-        <v>-0.00483</v>
+        <v>0.0201</v>
       </c>
       <c r="G13">
-        <v>0.2671560630777596</v>
+        <v>-0.02881493506493506</v>
       </c>
       <c r="H13">
-        <v>0.2671560630777596</v>
+        <v>-0.02881493506493506</v>
       </c>
       <c r="I13">
-        <v>0.2000085314026632</v>
+        <v>-0.03003246753246753</v>
       </c>
       <c r="J13">
-        <v>0.1538426277608682</v>
+        <v>-0.03003246753246753</v>
       </c>
       <c r="K13">
-        <v>469.2</v>
+        <v>-11.8</v>
       </c>
       <c r="L13">
-        <v>0.1275693311582382</v>
+        <v>-0.0239448051948052</v>
       </c>
       <c r="M13">
-        <v>344.7</v>
+        <v>5.42</v>
       </c>
       <c r="N13">
-        <v>0.1318618262499522</v>
+        <v>0.01599291826497492</v>
       </c>
       <c r="O13">
-        <v>0.7346547314578005</v>
+        <v>-0.4593220338983051</v>
       </c>
       <c r="P13">
-        <v>64.5</v>
+        <v>5.42</v>
       </c>
       <c r="Q13">
-        <v>0.02467388393711029</v>
+        <v>0.01599291826497492</v>
       </c>
       <c r="R13">
-        <v>0.1374680306905371</v>
+        <v>-0.4593220338983051</v>
       </c>
       <c r="S13">
-        <v>280.2</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>0.8128807658833769</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>498</v>
+        <v>7.34</v>
       </c>
       <c r="V13">
-        <v>0.1905053364446655</v>
+        <v>0.02165830628503983</v>
       </c>
       <c r="W13">
-        <v>0.08966347531961245</v>
+        <v>-0.02020893988696695</v>
       </c>
       <c r="X13">
-        <v>0.1399573227736552</v>
+        <v>0.07460816978577145</v>
       </c>
       <c r="Y13">
-        <v>-0.05029384745404274</v>
+        <v>-0.0948171096727384</v>
       </c>
       <c r="Z13">
-        <v>0.4292144446483495</v>
+        <v>0.8528459927660386</v>
       </c>
       <c r="AA13">
-        <v>0.06603147803762378</v>
+        <v>-0.02561306958794109</v>
       </c>
       <c r="AB13">
-        <v>0.0771322018950007</v>
+        <v>0.07460816978577145</v>
       </c>
       <c r="AC13">
-        <v>-0.01110072385737691</v>
+        <v>-0.1002212393737126</v>
       </c>
       <c r="AD13">
-        <v>3893.6</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>48.84310750502296</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>3942.443107505023</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>3444.443107505023</v>
+        <v>-7.34</v>
       </c>
       <c r="AH13">
-        <v>0.6012990447652605</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>0.7523253776759014</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>0.5685266319617694</v>
+        <v>-0.0221377729521052</v>
       </c>
       <c r="AK13">
-        <v>0.7263167234892809</v>
+        <v>-0.01472240051347882</v>
       </c>
       <c r="AL13">
-        <v>112.8</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>112.8</v>
+        <v>0</v>
       </c>
       <c r="AN13">
-        <v>3.405878236529042</v>
-      </c>
-      <c r="AO13">
-        <v>6.407801418439716</v>
+        <v>-0</v>
       </c>
       <c r="AP13">
-        <v>3.01298382391972</v>
-      </c>
-      <c r="AQ13">
-        <v>6.407801418439716</v>
+        <v>0.833144154370034</v>
       </c>
     </row>
     <row r="14">
@@ -2115,7 +2175,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Brighthouse Financial, Inc. (NasdaqGS:BHF)</t>
+          <t>Prudential Financial, Inc. (NYSE:PRU)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2124,115 +2184,118 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.18</v>
+        <v>-0.0331</v>
+      </c>
+      <c r="E14">
+        <v>-0.283</v>
       </c>
       <c r="F14">
-        <v>0.12</v>
+        <v>0.105</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>-0.04682981737729734</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>-0.04682981737729734</v>
       </c>
       <c r="I14">
-        <v>0.1348359429540241</v>
+        <v>-0.02980483384088237</v>
       </c>
       <c r="J14">
-        <v>0.1138415038762535</v>
+        <v>-0.02668411565210873</v>
       </c>
       <c r="K14">
-        <v>1009</v>
+        <v>1328</v>
       </c>
       <c r="L14">
-        <v>0.1006283035803331</v>
+        <v>0.02577289576338618</v>
       </c>
       <c r="M14">
-        <v>553</v>
+        <v>2966</v>
       </c>
       <c r="N14">
-        <v>0.156025167169822</v>
+        <v>0.07915285628125683</v>
       </c>
       <c r="O14">
-        <v>0.5480673934588701</v>
+        <v>2.233433734939759</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>1837</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.04902353236300364</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>1.38328313253012</v>
       </c>
       <c r="S14">
-        <v>553</v>
+        <v>1129</v>
       </c>
       <c r="T14">
-        <v>1</v>
+        <v>0.3806473364801079</v>
       </c>
       <c r="U14">
-        <v>4793</v>
+        <v>16892</v>
       </c>
       <c r="V14">
-        <v>1.352312163191603</v>
+        <v>0.4507923291648653</v>
       </c>
       <c r="W14">
-        <v>0.06294055267918408</v>
+        <v>0.08047509392800872</v>
       </c>
       <c r="X14">
-        <v>0.2118717522306125</v>
+        <v>0.09772237145327833</v>
       </c>
       <c r="Y14">
-        <v>-0.1489311995514284</v>
+        <v>-0.01724727752526961</v>
       </c>
       <c r="Z14">
-        <v>0.4720809792843691</v>
+        <v>1.624290774516963</v>
       </c>
       <c r="AA14">
-        <v>0.05374240863310707</v>
+        <v>-0.04334276287986392</v>
       </c>
       <c r="AB14">
-        <v>0.08004012177671052</v>
+        <v>0.06814632320044828</v>
       </c>
       <c r="AC14">
-        <v>-0.02629771314360346</v>
+        <v>-0.1114890860803122</v>
       </c>
       <c r="AD14">
-        <v>12505</v>
+        <v>31897</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>353.7683665957285</v>
       </c>
       <c r="AF14">
-        <v>12505</v>
+        <v>32250.76836659573</v>
       </c>
       <c r="AG14">
-        <v>7712</v>
+        <v>15358.76836659573</v>
       </c>
       <c r="AH14">
-        <v>0.7791617079872643</v>
+        <v>0.4625585247666688</v>
       </c>
       <c r="AI14">
-        <v>0.6802110530896431</v>
+        <v>0.5447970296257701</v>
       </c>
       <c r="AJ14">
-        <v>0.685127439744854</v>
+        <v>0.2907174547133385</v>
       </c>
       <c r="AK14">
-        <v>0.5674343315429328</v>
+        <v>0.3630419434415209</v>
       </c>
       <c r="AL14">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>147</v>
-      </c>
-      <c r="AO14">
-        <v>9.197278911564625</v>
-      </c>
-      <c r="AQ14">
-        <v>9.197278911564625</v>
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>-22.81616595135909</v>
+      </c>
+      <c r="AP14">
+        <v>-10.98624346680667</v>
       </c>
     </row>
     <row r="15">
@@ -2243,7 +2306,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>National Western Life Group, Inc. (NasdaqGS:NWLI)</t>
+          <t>American Equity Investment Life Holding Company (NYSE:AEL)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2252,115 +2315,121 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.0548</v>
+        <v>-0.0558</v>
       </c>
       <c r="E15">
-        <v>0.0447</v>
+        <v>-0.5429999999999999</v>
       </c>
       <c r="G15">
-        <v>0.3926470588235294</v>
+        <v>0.6664606764718</v>
       </c>
       <c r="H15">
-        <v>0.3926470588235294</v>
+        <v>0.6664606764718</v>
       </c>
       <c r="I15">
-        <v>0.2406862745098039</v>
+        <v>-0.06838147533630173</v>
       </c>
       <c r="J15">
-        <v>0.1919934640522876</v>
+        <v>-0.06453725028604779</v>
       </c>
       <c r="K15">
-        <v>117.5</v>
+        <v>8.82</v>
       </c>
       <c r="L15">
-        <v>0.1919934640522876</v>
+        <v>0.003633667037449017</v>
       </c>
       <c r="M15">
-        <v>1.27</v>
+        <v>384.3</v>
       </c>
       <c r="N15">
-        <v>0.001243026328667906</v>
+        <v>0.08715076197387518</v>
       </c>
       <c r="O15">
-        <v>0.01080851063829787</v>
+        <v>43.57142857142857</v>
       </c>
       <c r="P15">
-        <v>1.27</v>
+        <v>30.6</v>
       </c>
       <c r="Q15">
-        <v>0.001243026328667906</v>
+        <v>0.006939404934687953</v>
       </c>
       <c r="R15">
-        <v>0.01080851063829787</v>
+        <v>3.469387755102041</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>353.7</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>0.9203747072599531</v>
       </c>
       <c r="U15">
-        <v>331.1</v>
+        <v>10188.4</v>
       </c>
       <c r="V15">
-        <v>0.3240677302534991</v>
+        <v>2.310504354136429</v>
       </c>
       <c r="W15">
-        <v>0.04596666927470464</v>
+        <v>0.002749633693923996</v>
       </c>
       <c r="X15">
-        <v>0.08630496438957291</v>
+        <v>0.08002228232215772</v>
       </c>
       <c r="Y15">
-        <v>-0.04033829511486827</v>
+        <v>-0.07727264862823373</v>
       </c>
       <c r="Z15">
-        <v>0.3034088880956631</v>
+        <v>1.057191119048869</v>
       </c>
       <c r="AA15">
-        <v>0.05825252344973923</v>
+        <v>-0.06822820785024376</v>
       </c>
       <c r="AB15">
-        <v>0.08625079426551555</v>
+        <v>0.07299572711198606</v>
       </c>
       <c r="AC15">
-        <v>-0.02799827081577631</v>
+        <v>-0.1412239349622298</v>
       </c>
       <c r="AD15">
-        <v>1.09</v>
+        <v>866.1</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>22.86177541902605</v>
       </c>
       <c r="AF15">
-        <v>1.09</v>
+        <v>888.961775419026</v>
       </c>
       <c r="AG15">
-        <v>-330.01</v>
+        <v>-9299.438224580974</v>
       </c>
       <c r="AH15">
-        <v>0.001065712414083047</v>
+        <v>0.1677741645936976</v>
       </c>
       <c r="AI15">
-        <v>0.0005622933314074357</v>
+        <v>0.299771786906076</v>
       </c>
       <c r="AJ15">
-        <v>-0.47710679639723</v>
+        <v>1.90178852499315</v>
       </c>
       <c r="AK15">
-        <v>-0.2053079837500545</v>
+        <v>1.287486883514148</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>42.2</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>42.2</v>
       </c>
       <c r="AN15">
-        <v>0.006765983860955929</v>
+        <v>-5.623660801246672</v>
+      </c>
+      <c r="AO15">
+        <v>-3.914691943127961</v>
       </c>
       <c r="AP15">
-        <v>-2.048479205462446</v>
+        <v>60.38204158548778</v>
+      </c>
+      <c r="AQ15">
+        <v>-3.914691943127961</v>
       </c>
     </row>
     <row r="16">
@@ -2371,7 +2440,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Genworth Financial, Inc. (NYSE:GNW)</t>
+          <t>Vericity, Inc. (NasdaqCM:VERY)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2380,37 +2449,34 @@
         </is>
       </c>
       <c r="D16">
-        <v>-0.0356</v>
-      </c>
-      <c r="E16">
-        <v>0.118</v>
+        <v>0.0723</v>
       </c>
       <c r="G16">
-        <v>0.189575394665215</v>
+        <v>-0.1057142857142857</v>
       </c>
       <c r="H16">
-        <v>0.189575394665215</v>
+        <v>-0.1057142857142857</v>
       </c>
       <c r="I16">
-        <v>0.1482517245360553</v>
+        <v>-0.084366038756808</v>
       </c>
       <c r="J16">
-        <v>0.1109221536097104</v>
+        <v>-0.084366038756808</v>
       </c>
       <c r="K16">
-        <v>597</v>
+        <v>-15.2</v>
       </c>
       <c r="L16">
-        <v>0.08124659771366358</v>
+        <v>-0.08685714285714285</v>
       </c>
       <c r="M16">
-        <v>34</v>
+        <v>-0</v>
       </c>
       <c r="N16">
-        <v>0.01294843476273897</v>
+        <v>-0</v>
       </c>
       <c r="O16">
-        <v>0.05695142378559464</v>
+        <v>0</v>
       </c>
       <c r="P16">
         <v>-0</v>
@@ -2419,82 +2485,73 @@
         <v>-0</v>
       </c>
       <c r="R16">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>34</v>
-      </c>
-      <c r="T16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>1561</v>
+        <v>7.63</v>
       </c>
       <c r="V16">
-        <v>0.5944854901363393</v>
+        <v>0.04582582582582582</v>
       </c>
       <c r="W16">
-        <v>0.03908091123330715</v>
+        <v>-0.1279461279461279</v>
       </c>
       <c r="X16">
-        <v>0.115148374302655</v>
+        <v>0.0824989167780978</v>
       </c>
       <c r="Y16">
-        <v>-0.07606746306934789</v>
+        <v>-0.2104450447242258</v>
       </c>
       <c r="Z16">
-        <v>0.4637942666441427</v>
+        <v>1.221041399186726</v>
       </c>
       <c r="AA16">
-        <v>0.05144505888800459</v>
+        <v>-0.1030144260074543</v>
       </c>
       <c r="AB16">
-        <v>0.08204921369523574</v>
+        <v>0.07242563299507214</v>
       </c>
       <c r="AC16">
-        <v>-0.03060415480723115</v>
+        <v>-0.1754400590025265</v>
       </c>
       <c r="AD16">
-        <v>2082</v>
+        <v>46.5</v>
       </c>
       <c r="AE16">
-        <v>48.23164054533037</v>
+        <v>2.420283912206997</v>
       </c>
       <c r="AF16">
-        <v>2130.23164054533</v>
+        <v>48.920283912207</v>
       </c>
       <c r="AG16">
-        <v>569.2316405453303</v>
+        <v>41.29028391220699</v>
       </c>
       <c r="AH16">
-        <v>0.4479010657509159</v>
+        <v>0.2270922822297649</v>
       </c>
       <c r="AI16">
-        <v>0.1749068991720029</v>
+        <v>0.3300512090584254</v>
       </c>
       <c r="AJ16">
-        <v>0.1781615034172786</v>
+        <v>0.1987113311306339</v>
       </c>
       <c r="AK16">
-        <v>0.05360889268715329</v>
+        <v>0.2936923005148146</v>
       </c>
       <c r="AL16">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>347</v>
-      </c>
-      <c r="AO16">
-        <v>10.02752293577982</v>
+        <v>-4.90506329113924</v>
       </c>
       <c r="AP16">
-        <v>94.87194009088837</v>
-      </c>
-      <c r="AQ16">
-        <v>10.02752293577982</v>
+        <v>-4.355515180612552</v>
       </c>
     </row>
     <row r="17">
@@ -2505,7 +2562,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MetLife, Inc. (NYSE:MET)</t>
+          <t>Brighthouse Financial, Inc. (NasdaqGS:BHF)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2514,121 +2571,112 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0445</v>
-      </c>
-      <c r="F17">
-        <v>0.039</v>
+        <v>-0.092</v>
       </c>
       <c r="G17">
-        <v>0.1290059860732174</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>0.1290059860732174</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>0.04559896038535755</v>
+        <v>-1.193933604012419</v>
       </c>
       <c r="J17">
-        <v>0.04531840894738365</v>
+        <v>-1.193933604012419</v>
       </c>
       <c r="K17">
-        <v>2401</v>
+        <v>-3933</v>
       </c>
       <c r="L17">
-        <v>0.03259084307257944</v>
+        <v>-0.9393360401241939</v>
       </c>
       <c r="M17">
-        <v>5516</v>
+        <v>283</v>
       </c>
       <c r="N17">
-        <v>0.09714346095593675</v>
+        <v>0.08329163846131207</v>
       </c>
       <c r="O17">
-        <v>2.29737609329446</v>
+        <v>-0.07195525044495296</v>
       </c>
       <c r="P17">
-        <v>1610</v>
+        <v>-0</v>
       </c>
       <c r="Q17">
-        <v>0.02835405586277341</v>
+        <v>-0</v>
       </c>
       <c r="R17">
-        <v>0.6705539358600583</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>3906</v>
+        <v>283</v>
       </c>
       <c r="T17">
-        <v>0.7081218274111675</v>
+        <v>1</v>
       </c>
       <c r="U17">
-        <v>22200</v>
+        <v>3839</v>
       </c>
       <c r="V17">
-        <v>0.3909689690394844</v>
+        <v>1.129881978985785</v>
       </c>
       <c r="W17">
-        <v>0.03477190441708906</v>
+        <v>-0.6764705882352942</v>
       </c>
       <c r="X17">
-        <v>0.1523485518497094</v>
+        <v>0.1582030730264163</v>
       </c>
       <c r="Y17">
-        <v>-0.1175766474326203</v>
+        <v>-0.8346736612617105</v>
       </c>
       <c r="Z17">
-        <v>0.4874148670612378</v>
+        <v>0.3095519739760461</v>
       </c>
       <c r="AA17">
-        <v>0.02208886627251581</v>
+        <v>-0.3695845039183794</v>
       </c>
       <c r="AB17">
-        <v>0.0763940833713609</v>
+        <v>0.06809146677128139</v>
       </c>
       <c r="AC17">
-        <v>-0.05430521709884509</v>
+        <v>-0.4376759706896608</v>
       </c>
       <c r="AD17">
-        <v>104196</v>
+        <v>10576</v>
       </c>
       <c r="AE17">
-        <v>1203.39494725162</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>105399.3949472516</v>
+        <v>10576</v>
       </c>
       <c r="AG17">
-        <v>83199.39494725163</v>
+        <v>6737</v>
       </c>
       <c r="AH17">
-        <v>0.6498858576320178</v>
+        <v>0.7568503689073044</v>
       </c>
       <c r="AI17">
-        <v>0.806240975794155</v>
+        <v>0.7189666893269885</v>
       </c>
       <c r="AJ17">
-        <v>0.59436037895324</v>
+        <v>0.6647458730894846</v>
       </c>
       <c r="AK17">
-        <v>0.7666070099044494</v>
+        <v>0.6197221966700396</v>
       </c>
       <c r="AL17">
-        <v>914</v>
+        <v>150</v>
       </c>
       <c r="AM17">
-        <v>914</v>
-      </c>
-      <c r="AN17">
-        <v>25.68934911242604</v>
+        <v>150</v>
       </c>
       <c r="AO17">
-        <v>3.665207877461707</v>
-      </c>
-      <c r="AP17">
-        <v>20.51267133807979</v>
+        <v>-33.32666666666667</v>
       </c>
       <c r="AQ17">
-        <v>3.665207877461707</v>
+        <v>-33.32666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -2639,7 +2687,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kansas City Life Insurance Company (OTCPK:KCLI)</t>
+          <t>Lincoln National Corporation (NYSE:LNC)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2648,46 +2696,43 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.0176</v>
-      </c>
-      <c r="E18">
-        <v>-0.0922</v>
+        <v>-0.0108</v>
       </c>
       <c r="G18">
-        <v>0.03135179153094463</v>
+        <v>-0.1165977073865563</v>
       </c>
       <c r="H18">
-        <v>0.03135179153094463</v>
+        <v>-0.1165977073865563</v>
       </c>
       <c r="I18">
-        <v>0.02178338762214984</v>
+        <v>-0.4513317080024652</v>
       </c>
       <c r="J18">
-        <v>0.0191075270438734</v>
+        <v>-0.4513317080024652</v>
       </c>
       <c r="K18">
-        <v>14.2</v>
+        <v>-2303</v>
       </c>
       <c r="L18">
-        <v>0.02890879478827361</v>
+        <v>-0.1562097266499356</v>
       </c>
       <c r="M18">
-        <v>7.94</v>
+        <v>305</v>
       </c>
       <c r="N18">
-        <v>0.0310641627543036</v>
+        <v>0.06665501114559202</v>
       </c>
       <c r="O18">
-        <v>0.5591549295774648</v>
+        <v>-0.1324359531046461</v>
       </c>
       <c r="P18">
-        <v>7.94</v>
+        <v>305</v>
       </c>
       <c r="Q18">
-        <v>0.0310641627543036</v>
+        <v>0.06665501114559202</v>
       </c>
       <c r="R18">
-        <v>0.5591549295774648</v>
+        <v>-0.1324359531046461</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2696,67 +2741,73 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>7.28</v>
+        <v>2529</v>
       </c>
       <c r="V18">
-        <v>0.02848200312989045</v>
+        <v>0.5526902399580401</v>
       </c>
       <c r="W18">
-        <v>0.01698971045704714</v>
+        <v>-1.038791159224177</v>
       </c>
       <c r="X18">
-        <v>0.08626698429789872</v>
+        <v>0.1193835451364902</v>
       </c>
       <c r="Y18">
-        <v>-0.06927727384085158</v>
+        <v>-1.158174704360667</v>
       </c>
       <c r="Z18">
-        <v>0.5909101845391334</v>
+        <v>1.9553266014383</v>
       </c>
       <c r="AA18">
-        <v>0.01129083233158171</v>
+        <v>-0.8825008947298036</v>
       </c>
       <c r="AB18">
-        <v>0.08626698429789872</v>
+        <v>0.06860066159388867</v>
       </c>
       <c r="AC18">
-        <v>-0.07497615196631702</v>
+        <v>-0.9511015563236923</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>7464</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>164.9168554017188</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>7628.916855401719</v>
       </c>
       <c r="AG18">
-        <v>-7.28</v>
+        <v>5099.916855401719</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>0.6250793808481691</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>0.7045599774434805</v>
       </c>
       <c r="AJ18">
-        <v>-0.02931701030927835</v>
+        <v>0.5270841356374084</v>
       </c>
       <c r="AK18">
-        <v>-0.01484139280763272</v>
+        <v>0.6145280094091087</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="AN18">
-        <v>0</v>
+        <v>-1.132109813438495</v>
+      </c>
+      <c r="AO18">
+        <v>-20.32012195121951</v>
       </c>
       <c r="AP18">
-        <v>-0.4089887640449438</v>
+        <v>-0.7735350910665432</v>
+      </c>
+      <c r="AQ18">
+        <v>-20.32012195121951</v>
       </c>
     </row>
     <row r="19">
@@ -2767,7 +2818,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Prudential Financial, Inc. (NYSE:PRU)</t>
+          <t>Pekin Life Insurance Company (OTCPK:PKIN)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2775,107 +2826,89 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D19">
-        <v>0.0116</v>
-      </c>
-      <c r="E19">
-        <v>-0.405</v>
-      </c>
-      <c r="F19">
-        <v>-0.0621</v>
-      </c>
       <c r="G19">
-        <v>0.1723671780839767</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>0.1723671780839767</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>-0.004910659494197094</v>
+        <v>-0.001751297404704507</v>
       </c>
       <c r="J19">
-        <v>-0.004910659494197094</v>
+        <v>-0.0008756487023522535</v>
       </c>
       <c r="K19">
-        <v>328</v>
+        <v>0.155</v>
       </c>
       <c r="L19">
-        <v>0.005342193556793381</v>
+        <v>0.0006047600468201326</v>
       </c>
       <c r="M19">
-        <v>3327</v>
+        <v>-0</v>
       </c>
       <c r="N19">
-        <v>0.09089841071218781</v>
+        <v>-0</v>
       </c>
       <c r="O19">
-        <v>10.14329268292683</v>
+        <v>-0</v>
       </c>
       <c r="P19">
-        <v>1811</v>
+        <v>-0</v>
       </c>
       <c r="Q19">
-        <v>0.04947911686196938</v>
+        <v>-0</v>
       </c>
       <c r="R19">
-        <v>5.521341463414634</v>
+        <v>-0</v>
       </c>
       <c r="S19">
-        <v>1516</v>
-      </c>
-      <c r="T19">
-        <v>0.4556657649534115</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>20104</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>0.5492701078923425</v>
-      </c>
-      <c r="W19">
-        <v>0.005299982225669365</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>0.1206778893625322</v>
-      </c>
-      <c r="Y19">
-        <v>-0.1153779071368629</v>
+        <v>0.07460875638271279</v>
       </c>
       <c r="Z19">
-        <v>0.7594201780041638</v>
+        <v>59776.69504117321</v>
       </c>
       <c r="AA19">
-        <v>-0.003729253907200995</v>
+        <v>-52.34338544370971</v>
       </c>
       <c r="AB19">
-        <v>0.07880014820033795</v>
+        <v>0.07460800359116415</v>
       </c>
       <c r="AC19">
-        <v>-0.08252940210753895</v>
+        <v>-52.41799344730088</v>
       </c>
       <c r="AD19">
-        <v>34971</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>407.523358123566</v>
+        <v>0.00428762412882587</v>
       </c>
       <c r="AF19">
-        <v>35378.52335812357</v>
+        <v>0.00428762412882587</v>
       </c>
       <c r="AG19">
-        <v>15274.52335812357</v>
+        <v>0.00428762412882587</v>
       </c>
       <c r="AH19">
-        <v>0.4915061152915539</v>
+        <v>2.184172429812406e-05</v>
       </c>
       <c r="AI19">
-        <v>0.6731262809090198</v>
+        <v>1</v>
       </c>
       <c r="AJ19">
-        <v>0.2944439696441296</v>
+        <v>2.184172429812406e-05</v>
       </c>
       <c r="AK19">
-        <v>0.4706438972951442</v>
+        <v>1</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2884,10 +2917,10 @@
         <v>0</v>
       </c>
       <c r="AN19">
-        <v>-852.9512195121952</v>
+        <v>0</v>
       </c>
       <c r="AP19">
-        <v>-372.5493501981358</v>
+        <v>4.28762412882587</v>
       </c>
     </row>
     <row r="20">
@@ -2898,7 +2931,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Citizens, Inc. (NYSE:CIA)</t>
+          <t>F&amp;G Annuities &amp; Life, Inc. (NYSE:FG)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2907,115 +2940,109 @@
         </is>
       </c>
       <c r="D20">
-        <v>-0.0142</v>
-      </c>
-      <c r="E20">
-        <v>0.353</v>
+        <v>0.107</v>
       </c>
       <c r="G20">
-        <v>0.03010204081632653</v>
+        <v>0.1772969935375105</v>
       </c>
       <c r="H20">
-        <v>0.03010204081632653</v>
+        <v>0.1772969935375105</v>
       </c>
       <c r="I20">
-        <v>-0.01773784590967477</v>
+        <v>-0.01416606861466468</v>
       </c>
       <c r="J20">
-        <v>-0.01773784590967477</v>
+        <v>-0.01416606861466468</v>
       </c>
       <c r="K20">
-        <v>28.1</v>
+        <v>-89</v>
       </c>
       <c r="L20">
-        <v>0.1194727891156463</v>
+        <v>-0.02500702444506884</v>
       </c>
       <c r="M20">
-        <v>2.18</v>
+        <v>93</v>
       </c>
       <c r="N20">
-        <v>0.02046948356807512</v>
+        <v>0.01610975419633114</v>
       </c>
       <c r="O20">
-        <v>0.07758007117437722</v>
+        <v>-1.044943820224719</v>
       </c>
       <c r="P20">
-        <v>-0</v>
+        <v>75</v>
       </c>
       <c r="Q20">
-        <v>-0</v>
+        <v>0.01299173725510575</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>-0.8426966292134831</v>
       </c>
       <c r="S20">
-        <v>2.18</v>
+        <v>18</v>
       </c>
       <c r="T20">
-        <v>1</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="U20">
-        <v>21</v>
+        <v>1742</v>
       </c>
       <c r="V20">
-        <v>0.1971830985915493</v>
+        <v>0.3017547506452563</v>
       </c>
       <c r="W20">
-        <v>0.1060377358490566</v>
+        <v>-0.05313432835820896</v>
       </c>
       <c r="X20">
-        <v>0.08937898222753543</v>
+        <v>0.08196354147483029</v>
       </c>
       <c r="Y20">
-        <v>0.01665875362152118</v>
-      </c>
-      <c r="Z20">
-        <v>0.9631066802863273</v>
-      </c>
-      <c r="AA20">
-        <v>-0.01708343788949728</v>
+        <v>-0.1350978698330392</v>
       </c>
       <c r="AB20">
-        <v>0.08550999123317848</v>
-      </c>
-      <c r="AC20">
-        <v>-0.1025934291226758</v>
+        <v>0.07254187767120115</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1569</v>
       </c>
       <c r="AE20">
-        <v>9.309706789777533</v>
+        <v>12.08519099795796</v>
       </c>
       <c r="AF20">
-        <v>9.309706789777533</v>
+        <v>1581.085190997958</v>
       </c>
       <c r="AG20">
-        <v>-11.69029321022247</v>
+        <v>-160.9148090020421</v>
       </c>
       <c r="AH20">
-        <v>0.08038796615448555</v>
+        <v>0.2149970594084648</v>
       </c>
       <c r="AI20">
-        <v>-1.903711370581401</v>
+        <v>0.3999623369105315</v>
       </c>
       <c r="AJ20">
-        <v>-0.1233027039746412</v>
+        <v>-0.02867342010455792</v>
       </c>
       <c r="AK20">
-        <v>0.4515318971206822</v>
+        <v>-0.07277639489295949</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="AN20">
-        <v>-0</v>
+        <v>-36.48837209302326</v>
+      </c>
+      <c r="AO20">
+        <v>-0.6493506493506493</v>
       </c>
       <c r="AP20">
-        <v>6.836428777907876</v>
+        <v>3.742204860512608</v>
+      </c>
+      <c r="AQ20">
+        <v>-0.6493506493506493</v>
       </c>
     </row>
     <row r="21">
@@ -3026,7 +3053,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lincoln National Corporation (NYSE:LNC)</t>
+          <t>Oscar Health, Inc. (NYSE:OSCR)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3034,122 +3061,107 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D21">
-        <v>0.0675</v>
-      </c>
       <c r="F21">
-        <v>0.0825</v>
+        <v>0.57</v>
       </c>
       <c r="G21">
-        <v>0.1068674447686536</v>
+        <v>-0.1056036463215159</v>
       </c>
       <c r="H21">
-        <v>0.1068674447686536</v>
+        <v>-0.1056036463215159</v>
       </c>
       <c r="I21">
-        <v>-0.07602634506252699</v>
+        <v>-0.05881709586934059</v>
       </c>
       <c r="J21">
-        <v>-0.07602634506252699</v>
+        <v>-0.05881709586934059</v>
       </c>
       <c r="K21">
-        <v>-2013</v>
+        <v>-346.7</v>
       </c>
       <c r="L21">
-        <v>-0.1048874531054606</v>
+        <v>-0.06371873334436051</v>
       </c>
       <c r="M21">
-        <v>1512</v>
+        <v>-0</v>
       </c>
       <c r="N21">
-        <v>0.2908643210280284</v>
+        <v>-0</v>
       </c>
       <c r="O21">
-        <v>-0.7511177347242921</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>312</v>
+        <v>-0</v>
       </c>
       <c r="Q21">
-        <v>0.06001962179943443</v>
+        <v>-0</v>
       </c>
       <c r="R21">
-        <v>-0.1549925484351714</v>
+        <v>0</v>
       </c>
       <c r="S21">
-        <v>1200</v>
-      </c>
-      <c r="T21">
-        <v>0.7936507936507936</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>1472</v>
+        <v>1399.8</v>
       </c>
       <c r="V21">
-        <v>0.2831694977204086</v>
+        <v>0.677541142303969</v>
       </c>
       <c r="W21">
-        <v>-0.09508738781294285</v>
+        <v>-0.3204251386321627</v>
       </c>
       <c r="X21">
-        <v>0.1406058384523799</v>
+        <v>0.0798045379680779</v>
       </c>
       <c r="Y21">
-        <v>-0.2356932262653228</v>
-      </c>
-      <c r="Z21">
-        <v>0.7876391519012663</v>
-      </c>
-      <c r="AA21">
-        <v>-0.05988132594720179</v>
+        <v>-0.4002296766002406</v>
       </c>
       <c r="AB21">
-        <v>0.0805776318925995</v>
-      </c>
-      <c r="AC21">
-        <v>-0.1404589578398013</v>
+        <v>0.07337458764425529</v>
       </c>
       <c r="AD21">
-        <v>7774</v>
+        <v>298.6</v>
       </c>
       <c r="AE21">
-        <v>160.48807220009</v>
+        <v>101.1485016733453</v>
       </c>
       <c r="AF21">
-        <v>7934.48807220009</v>
+        <v>399.7485016733453</v>
       </c>
       <c r="AG21">
-        <v>6462.48807220009</v>
+        <v>-1000.051498326655</v>
       </c>
       <c r="AH21">
-        <v>0.6041739216820281</v>
+        <v>0.1621205493593778</v>
       </c>
       <c r="AI21">
-        <v>0.7816083726610223</v>
+        <v>0.3025765091259842</v>
       </c>
       <c r="AJ21">
-        <v>0.5542068025065123</v>
+        <v>-0.9381799371702813</v>
       </c>
       <c r="AK21">
-        <v>0.7445701887533062</v>
+        <v>12.714970720243</v>
       </c>
       <c r="AL21">
-        <v>271</v>
+        <v>24.5</v>
       </c>
       <c r="AM21">
-        <v>271</v>
+        <v>24.5</v>
       </c>
       <c r="AN21">
-        <v>-5.612996389891697</v>
+        <v>-1.093372391065544</v>
       </c>
       <c r="AO21">
-        <v>-5.435424354243542</v>
+        <v>-12.75918367346939</v>
       </c>
       <c r="AP21">
-        <v>-4.666056369819559</v>
+        <v>3.661850964213309</v>
       </c>
       <c r="AQ21">
-        <v>-5.435424354243542</v>
+        <v>-12.75918367346939</v>
       </c>
     </row>
     <row r="22">
@@ -3160,7 +3172,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vericity, Inc. (NasdaqCM:VERY)</t>
+          <t>Bright Health Group, Inc. (NYSE:BHG)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3169,22 +3181,22 @@
         </is>
       </c>
       <c r="G22">
-        <v>-0.08039906103286384</v>
+        <v>-0.1545800834391438</v>
       </c>
       <c r="H22">
-        <v>-0.08039906103286384</v>
+        <v>-0.1545800834391438</v>
       </c>
       <c r="I22">
-        <v>-0.09561719982545512</v>
+        <v>-0.134139144641727</v>
       </c>
       <c r="J22">
-        <v>-0.09561719982545512</v>
+        <v>-0.134139144641727</v>
       </c>
       <c r="K22">
-        <v>-16.9</v>
+        <v>-1590.5</v>
       </c>
       <c r="L22">
-        <v>-0.09917840375586853</v>
+        <v>-0.5769998186105568</v>
       </c>
       <c r="M22">
         <v>-0</v>
@@ -3208,67 +3220,64 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>12.7</v>
+        <v>113.4</v>
       </c>
       <c r="V22">
-        <v>0.1137992831541219</v>
+        <v>1.868204283360791</v>
       </c>
       <c r="W22">
-        <v>-0.0950506186726659</v>
+        <v>-4.309130316987266</v>
       </c>
       <c r="X22">
-        <v>0.09810688800051279</v>
+        <v>0.2509970731926651</v>
       </c>
       <c r="Y22">
-        <v>-0.1931575066731787</v>
-      </c>
-      <c r="Z22">
-        <v>0.9150670907432769</v>
-      </c>
-      <c r="AA22">
-        <v>-0.08749615286929778</v>
+        <v>-4.560127390179932</v>
       </c>
       <c r="AB22">
-        <v>0.08391679388557714</v>
-      </c>
-      <c r="AC22">
-        <v>-0.1714129467548749</v>
+        <v>0.07279191202374423</v>
       </c>
       <c r="AD22">
-        <v>34.8</v>
+        <v>353.9</v>
       </c>
       <c r="AE22">
-        <v>2.315854251287776</v>
+        <v>44.77276102460274</v>
       </c>
       <c r="AF22">
-        <v>37.11585425128777</v>
+        <v>398.6727610246027</v>
       </c>
       <c r="AG22">
-        <v>24.41585425128777</v>
+        <v>285.2727610246027</v>
       </c>
       <c r="AH22">
-        <v>0.2495756383080211</v>
+        <v>0.8678633015492421</v>
       </c>
       <c r="AI22">
-        <v>0.2380505461071879</v>
+        <v>0.6719889858689635</v>
       </c>
       <c r="AJ22">
-        <v>0.1795074139385233</v>
+        <v>0.8245526618331566</v>
       </c>
       <c r="AK22">
-        <v>0.1704829006462337</v>
+        <v>0.5944758365019535</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>33.4</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>33.4</v>
       </c>
       <c r="AN22">
-        <v>-2.966751918158567</v>
+        <v>-1.101805728518057</v>
+      </c>
+      <c r="AO22">
+        <v>-11.19461077844311</v>
       </c>
       <c r="AP22">
-        <v>-2.081488000962299</v>
+        <v>-0.8881468275983895</v>
+      </c>
+      <c r="AQ22">
+        <v>-11.19461077844311</v>
       </c>
     </row>
     <row r="23">
@@ -3279,7 +3288,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Trupanion, Inc. (NasdaqGM:TRUP)</t>
+          <t>Citizens, Inc. (NYSE:CIA)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3288,34 +3297,34 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.302</v>
+        <v>-0.00419</v>
       </c>
       <c r="G23">
-        <v>-0.02694786174575278</v>
+        <v>-0.02708419742845293</v>
       </c>
       <c r="H23">
-        <v>-0.02694786174575278</v>
+        <v>-0.02708419742845293</v>
       </c>
       <c r="I23">
-        <v>-0.04606967784524638</v>
+        <v>-0.02494058355502609</v>
       </c>
       <c r="J23">
-        <v>-0.04606967784524638</v>
+        <v>-0.02494058355502609</v>
       </c>
       <c r="K23">
-        <v>-42.4</v>
+        <v>-5.29</v>
       </c>
       <c r="L23">
-        <v>-0.04967779730521382</v>
+        <v>-0.02194110327664869</v>
       </c>
       <c r="M23">
-        <v>10.5</v>
+        <v>1.24</v>
       </c>
       <c r="N23">
-        <v>0.005403458213256484</v>
+        <v>0.009302325581395349</v>
       </c>
       <c r="O23">
-        <v>-0.2476415094339623</v>
+        <v>-0.2344045368620038</v>
       </c>
       <c r="P23">
         <v>-0</v>
@@ -3327,451 +3336,64 @@
         <v>0</v>
       </c>
       <c r="S23">
-        <v>10.5</v>
+        <v>1.24</v>
       </c>
       <c r="T23">
         <v>1</v>
       </c>
       <c r="U23">
-        <v>85.5</v>
+        <v>16.8</v>
       </c>
       <c r="V23">
-        <v>0.04399958830794565</v>
+        <v>0.1260315078769692</v>
       </c>
       <c r="W23">
-        <v>-0.127710843373494</v>
+        <v>0.3725352112676056</v>
       </c>
       <c r="X23">
-        <v>0.08727098631646957</v>
+        <v>0.07640446260948956</v>
       </c>
       <c r="Y23">
-        <v>-0.2149818296899635</v>
-      </c>
-      <c r="Z23">
-        <v>4.482612736045049</v>
-      </c>
-      <c r="AA23">
-        <v>-0.2065125246545939</v>
+        <v>0.2961307486581161</v>
       </c>
       <c r="AB23">
-        <v>0.08600869640544043</v>
-      </c>
-      <c r="AC23">
-        <v>-0.2925212210600343</v>
+        <v>0.0740056448540711</v>
       </c>
       <c r="AD23">
-        <v>54.2</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>0.6023502045889506</v>
+        <v>8.915873475583947</v>
       </c>
       <c r="AF23">
-        <v>54.80235020458895</v>
+        <v>8.915873475583947</v>
       </c>
       <c r="AG23">
-        <v>-30.69764979541105</v>
+        <v>-7.884126524416054</v>
       </c>
       <c r="AH23">
-        <v>0.0274285714423596</v>
+        <v>0.06269253394639278</v>
       </c>
       <c r="AI23">
-        <v>0.1520166239512392</v>
+        <v>0.05516706548587203</v>
       </c>
       <c r="AJ23">
-        <v>-0.01605103899199244</v>
+        <v>-0.06286386488350647</v>
       </c>
       <c r="AK23">
-        <v>-0.1116268634525248</v>
+        <v>-0.05444241943370471</v>
       </c>
       <c r="AL23">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AM23">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AN23">
-        <v>-1.908450704225352</v>
-      </c>
-      <c r="AO23">
-        <v>-14.5724907063197</v>
+        <v>-0</v>
       </c>
       <c r="AP23">
-        <v>1.080903161810248</v>
-      </c>
-      <c r="AQ23">
-        <v>-14.5724907063197</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Oscar Health, Inc. (NYSE:OSCR)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="F24">
-        <v>0.46</v>
-      </c>
-      <c r="G24">
-        <v>-0.1503267973856209</v>
-      </c>
-      <c r="H24">
-        <v>-0.1503267973856209</v>
-      </c>
-      <c r="I24">
-        <v>-0.1620248670614414</v>
-      </c>
-      <c r="J24">
-        <v>-0.1620248670614414</v>
-      </c>
-      <c r="K24">
-        <v>-579.2</v>
-      </c>
-      <c r="L24">
-        <v>-0.1645922136970731</v>
-      </c>
-      <c r="M24">
-        <v>-0</v>
-      </c>
-      <c r="N24">
-        <v>-0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>-0</v>
-      </c>
-      <c r="Q24">
-        <v>-0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>2112.9</v>
-      </c>
-      <c r="V24">
-        <v>3.999432140829075</v>
-      </c>
-      <c r="W24">
-        <v>-0.3729075457120783</v>
-      </c>
-      <c r="X24">
-        <v>0.1138366184895366</v>
-      </c>
-      <c r="Y24">
-        <v>-0.4867441642016149</v>
-      </c>
-      <c r="Z24">
-        <v>5.98644974046078</v>
-      </c>
-      <c r="AA24">
-        <v>-0.9699537233681584</v>
-      </c>
-      <c r="AB24">
-        <v>0.0821571731708003</v>
-      </c>
-      <c r="AC24">
-        <v>-1.052110896538959</v>
-      </c>
-      <c r="AD24">
-        <v>297.8</v>
-      </c>
-      <c r="AE24">
-        <v>111.3275359460615</v>
-      </c>
-      <c r="AF24">
-        <v>409.1275359460616</v>
-      </c>
-      <c r="AG24">
-        <v>-1703.772464053939</v>
-      </c>
-      <c r="AH24">
-        <v>0.436436439359727</v>
-      </c>
-      <c r="AI24">
-        <v>0.2738970301480974</v>
-      </c>
-      <c r="AJ24">
-        <v>1.449436304256769</v>
-      </c>
-      <c r="AK24">
-        <v>2.751692885208015</v>
-      </c>
-      <c r="AL24">
-        <v>16.9</v>
-      </c>
-      <c r="AM24">
-        <v>16.9</v>
-      </c>
-      <c r="AN24">
-        <v>-0.5593538692712245</v>
-      </c>
-      <c r="AO24">
-        <v>-33.29585798816569</v>
-      </c>
-      <c r="AP24">
-        <v>3.200173674030688</v>
-      </c>
-      <c r="AQ24">
-        <v>-33.29585798816569</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Bright Health Group, Inc. (NYSE:BHG)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="G25">
-        <v>-0.1938636212292735</v>
-      </c>
-      <c r="H25">
-        <v>-0.1938636212292735</v>
-      </c>
-      <c r="I25">
-        <v>-0.2284603939245895</v>
-      </c>
-      <c r="J25">
-        <v>-0.2284603939245895</v>
-      </c>
-      <c r="K25">
-        <v>-1590.5</v>
-      </c>
-      <c r="L25">
-        <v>-0.2647832456549244</v>
-      </c>
-      <c r="M25">
-        <v>-0</v>
-      </c>
-      <c r="N25">
-        <v>-0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>-0</v>
-      </c>
-      <c r="Q25">
-        <v>-0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>1605.5</v>
-      </c>
-      <c r="V25">
-        <v>3.936978911230995</v>
-      </c>
-      <c r="W25">
-        <v>-0.8210303530869296</v>
-      </c>
-      <c r="X25">
-        <v>0.1170814846908515</v>
-      </c>
-      <c r="Y25">
-        <v>-0.9381118377777812</v>
-      </c>
-      <c r="Z25">
-        <v>31.98858727110587</v>
-      </c>
-      <c r="AA25">
-        <v>-7.308125249047958</v>
-      </c>
-      <c r="AB25">
-        <v>0.08322020577090435</v>
-      </c>
-      <c r="AC25">
-        <v>-7.391345454818862</v>
-      </c>
-      <c r="AD25">
-        <v>303.9</v>
-      </c>
-      <c r="AE25">
-        <v>49.07947113112189</v>
-      </c>
-      <c r="AF25">
-        <v>352.9794711311218</v>
-      </c>
-      <c r="AG25">
-        <v>-1252.520528868878</v>
-      </c>
-      <c r="AH25">
-        <v>0.463970814835887</v>
-      </c>
-      <c r="AI25">
-        <v>0.2100218853113982</v>
-      </c>
-      <c r="AJ25">
-        <v>1.482763217020503</v>
-      </c>
-      <c r="AK25">
-        <v>-16.66040622558161</v>
-      </c>
-      <c r="AL25">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="AM25">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="AN25">
-        <v>-0.231489945155393</v>
-      </c>
-      <c r="AO25">
-        <v>-169.6794081381011</v>
-      </c>
-      <c r="AP25">
-        <v>0.9540832791505773</v>
-      </c>
-      <c r="AQ25">
-        <v>-169.6794081381011</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Pekin Life Insurance Company (OTCPK:PKIN)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>-0.0145</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>-0.01204111947856088</v>
-      </c>
-      <c r="J26">
-        <v>-0.01204111947856088</v>
-      </c>
-      <c r="K26">
-        <v>-3.77</v>
-      </c>
-      <c r="L26">
-        <v>-0.01455036665380162</v>
-      </c>
-      <c r="M26">
-        <v>0.341</v>
-      </c>
-      <c r="N26">
-        <v>0.001700748129675811</v>
-      </c>
-      <c r="O26">
-        <v>-0.09045092838196288</v>
-      </c>
-      <c r="P26">
-        <v>0.341</v>
-      </c>
-      <c r="Q26">
-        <v>0.001700748129675811</v>
-      </c>
-      <c r="R26">
-        <v>-0.09045092838196288</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
-      <c r="U26">
-        <v>0</v>
-      </c>
-      <c r="V26">
-        <v>0</v>
-      </c>
-      <c r="X26">
-        <v>0.08626774251807136</v>
-      </c>
-      <c r="Z26">
-        <v>60675.11461573897</v>
-      </c>
-      <c r="AA26">
-        <v>-730.5963044634883</v>
-      </c>
-      <c r="AB26">
-        <v>0.08626678374264614</v>
-      </c>
-      <c r="AC26">
-        <v>-730.682571247231</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0.004270284475619106</v>
-      </c>
-      <c r="AF26">
-        <v>0.004270284475619106</v>
-      </c>
-      <c r="AG26">
-        <v>0.004270284475619106</v>
-      </c>
-      <c r="AH26">
-        <v>2.129772333307626e-05</v>
-      </c>
-      <c r="AI26">
-        <v>1</v>
-      </c>
-      <c r="AJ26">
-        <v>2.129772333307626e-05</v>
-      </c>
-      <c r="AK26">
-        <v>1</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>0</v>
-      </c>
-      <c r="AN26">
-        <v>0</v>
-      </c>
-      <c r="AP26">
-        <v>4.270284475619106</v>
+        <v>2.113706843006985</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_states/united_states_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.09119999999999999</v>
+        <v>0.0156</v>
       </c>
       <c r="E2">
-        <v>0.04559999999999999</v>
+        <v>0.0648</v>
       </c>
       <c r="F2">
-        <v>0.10425</v>
+        <v>0.10195</v>
       </c>
       <c r="G2">
-        <v>0.2479920584784767</v>
+        <v>0.06538216575453906</v>
       </c>
       <c r="H2">
-        <v>0.2479920584784767</v>
+        <v>0.06538216575453906</v>
       </c>
       <c r="I2">
-        <v>0.1497783962291633</v>
+        <v>0.08540104735432537</v>
       </c>
       <c r="J2">
-        <v>0.1372804832454744</v>
+        <v>0.07268377389719692</v>
       </c>
       <c r="K2">
-        <v>2609</v>
+        <v>14425.2</v>
       </c>
       <c r="L2">
-        <v>0.1177240321270643</v>
+        <v>0.06153693892847439</v>
       </c>
       <c r="M2">
-        <v>4057</v>
+        <v>17250.664</v>
       </c>
       <c r="N2">
-        <v>0.0672631985582431</v>
+        <v>0.07607149298559636</v>
       </c>
       <c r="O2">
-        <v>1.555001916443082</v>
+        <v>1.195870005268558</v>
       </c>
       <c r="P2">
-        <v>1056</v>
+        <v>6009.82</v>
       </c>
       <c r="Q2">
-        <v>0.01750799548373298</v>
+        <v>0.0265019352283887</v>
       </c>
       <c r="R2">
-        <v>0.4047527788424684</v>
+        <v>0.4166195269389679</v>
       </c>
       <c r="S2">
-        <v>3001</v>
+        <v>11240.844</v>
       </c>
       <c r="T2">
-        <v>0.7397091446881933</v>
+        <v>0.6516180478618098</v>
       </c>
       <c r="U2">
-        <v>11242</v>
+        <v>73077.17999999999</v>
       </c>
       <c r="V2">
-        <v>0.186387201920574</v>
+        <v>0.3222536932941922</v>
       </c>
       <c r="W2">
-        <v>-0.06344296710410123</v>
+        <v>0.1466209369397459</v>
       </c>
       <c r="X2">
-        <v>0.1199915753345326</v>
+        <v>0.08799618870454878</v>
       </c>
       <c r="Y2">
-        <v>-0.1834345424386338</v>
+        <v>0.05862474823519712</v>
       </c>
       <c r="Z2">
-        <v>0.5521168193578715</v>
+        <v>0.9528055126416657</v>
       </c>
       <c r="AA2">
-        <v>9.000232889806725E-05</v>
+        <v>0.1288197205498126</v>
       </c>
       <c r="AB2">
-        <v>0.07392506056728193</v>
+        <v>0.07619422708741699</v>
       </c>
       <c r="AC2">
-        <v>-0.07383505823838385</v>
+        <v>0.04931333464277118</v>
       </c>
       <c r="AD2">
-        <v>20850</v>
+        <v>141946.2</v>
       </c>
       <c r="AE2">
-        <v>93.05591384640999</v>
+        <v>2188.439320608067</v>
       </c>
       <c r="AF2">
-        <v>20943.05591384641</v>
+        <v>144134.6393206081</v>
       </c>
       <c r="AG2">
-        <v>9701.055913846409</v>
+        <v>71057.45932060806</v>
       </c>
       <c r="AH2">
-        <v>0.2577341822673737</v>
+        <v>0.3886038991804785</v>
       </c>
       <c r="AI2">
-        <v>0.4077455194444651</v>
+        <v>0.4903874152048797</v>
       </c>
       <c r="AJ2">
-        <v>0.1385541390612123</v>
+        <v>0.2385867112815659</v>
       </c>
       <c r="AK2">
-        <v>0.2417946310954</v>
+        <v>0.3217558933750259</v>
       </c>
       <c r="AL2">
-        <v>365</v>
+        <v>2644.023</v>
       </c>
       <c r="AM2">
-        <v>365</v>
+        <v>2644.023</v>
       </c>
       <c r="AN2">
-        <v>4.327252350414046</v>
+        <v>5.964852860222464</v>
       </c>
       <c r="AO2">
-        <v>9.038356164383561</v>
+        <v>7.529624364084579</v>
       </c>
       <c r="AP2">
-        <v>2.013377314373619</v>
+        <v>2.985971371327097</v>
       </c>
       <c r="AQ2">
-        <v>9.038356164383561</v>
+        <v>7.529624364084579</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aflac Incorporated (NYSE:AFL)</t>
+          <t>UTG, Inc. (OTCPK:UTGN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,124 +725,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0454</v>
+        <v>0.235</v>
       </c>
       <c r="E3">
-        <v>0.04559999999999999</v>
-      </c>
-      <c r="F3">
-        <v>0.0785</v>
+        <v>0.736</v>
       </c>
       <c r="G3">
-        <v>0.317651138596694</v>
+        <v>0.03431498079385404</v>
       </c>
       <c r="H3">
-        <v>0.317651138596694</v>
+        <v>0.03431498079385404</v>
       </c>
       <c r="I3">
-        <v>0.2766378925691086</v>
+        <v>0.7387964148527529</v>
       </c>
       <c r="J3">
-        <v>0.2304710701652963</v>
+        <v>0.5851472471190782</v>
       </c>
       <c r="K3">
-        <v>3809</v>
+        <v>45.6</v>
       </c>
       <c r="L3">
-        <v>0.2201479597734366</v>
+        <v>0.5838668373879642</v>
       </c>
       <c r="M3">
-        <v>3807</v>
+        <v>0.444</v>
       </c>
       <c r="N3">
-        <v>0.06625028931207244</v>
+        <v>0.004774193548387097</v>
       </c>
       <c r="O3">
-        <v>0.9994749278025729</v>
+        <v>0.009736842105263158</v>
       </c>
       <c r="P3">
-        <v>1056</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.01837675479735973</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.2772381202415332</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>2751</v>
+        <v>0.444</v>
       </c>
       <c r="T3">
-        <v>0.7226162332545312</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>5612</v>
+        <v>36</v>
       </c>
       <c r="V3">
-        <v>0.09766131432081707</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="W3">
-        <v>0.1680268207684503</v>
+        <v>0.2974559686888454</v>
       </c>
       <c r="X3">
-        <v>0.08500339832303949</v>
+        <v>0.07950638590704137</v>
       </c>
       <c r="Y3">
-        <v>0.0830234224454108</v>
+        <v>0.217949582781804</v>
       </c>
       <c r="Z3">
-        <v>0.5898263796460899</v>
+        <v>0.6213206046141606</v>
       </c>
       <c r="AA3">
-        <v>0.1359379169287567</v>
+        <v>0.3635640413683373</v>
       </c>
       <c r="AB3">
-        <v>0.07725814076759389</v>
+        <v>0.07950638590704137</v>
       </c>
       <c r="AC3">
-        <v>0.05867977616116281</v>
+        <v>0.2840576554612959</v>
       </c>
       <c r="AD3">
-        <v>12345</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>93.05591384640999</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>12438.05591384641</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>6826.05591384641</v>
+        <v>-36</v>
       </c>
       <c r="AH3">
-        <v>0.177935735148473</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.3337457672221971</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.1061760864013324</v>
+        <v>-0.631578947368421</v>
       </c>
       <c r="AK3">
-        <v>0.2156319136036363</v>
+        <v>-0.2130177514792899</v>
       </c>
       <c r="AL3">
-        <v>194</v>
+        <v>0.023</v>
       </c>
       <c r="AM3">
-        <v>194</v>
+        <v>0.023</v>
       </c>
       <c r="AN3">
-        <v>2.562106967187597</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>24.56701030927835</v>
+        <v>2508.695652173913</v>
       </c>
       <c r="AP3">
-        <v>1.416693836798541</v>
+        <v>-0.6060606060606061</v>
       </c>
       <c r="AQ3">
-        <v>24.56701030927835</v>
+        <v>2508.695652173913</v>
       </c>
     </row>
     <row r="4">
@@ -853,123 +850,1856 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>F&amp;G Annuities &amp; Life, Inc. (NYSE:FG)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.342</v>
+      </c>
+      <c r="E4">
+        <v>-0.373</v>
+      </c>
+      <c r="G4">
+        <v>0.01662667123757285</v>
+      </c>
+      <c r="H4">
+        <v>0.01662667123757285</v>
+      </c>
+      <c r="I4">
+        <v>0.01900798407463044</v>
+      </c>
+      <c r="J4">
+        <v>0.01900798407463044</v>
+      </c>
+      <c r="K4">
+        <v>13</v>
+      </c>
+      <c r="L4">
+        <v>0.002228316763798423</v>
+      </c>
+      <c r="M4">
+        <v>32</v>
+      </c>
+      <c r="N4">
+        <v>0.006124050293763037</v>
+      </c>
+      <c r="O4">
+        <v>2.461538461538462</v>
+      </c>
+      <c r="P4">
+        <v>26</v>
+      </c>
+      <c r="Q4">
+        <v>0.004975790863682467</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4">
+        <v>6</v>
+      </c>
+      <c r="T4">
+        <v>0.1875</v>
+      </c>
+      <c r="U4">
+        <v>3539</v>
+      </c>
+      <c r="V4">
+        <v>0.6772816871758559</v>
+      </c>
+      <c r="W4">
+        <v>0.005480607082630692</v>
+      </c>
+      <c r="X4">
+        <v>0.08941712531778628</v>
+      </c>
+      <c r="Y4">
+        <v>-0.08393651823515559</v>
+      </c>
+      <c r="Z4">
+        <v>12.6678175166555</v>
+      </c>
+      <c r="AA4">
+        <v>0.2407896736169122</v>
+      </c>
+      <c r="AB4">
+        <v>0.07591514264033573</v>
+      </c>
+      <c r="AC4">
+        <v>0.1648745309765764</v>
+      </c>
+      <c r="AD4">
+        <v>2038</v>
+      </c>
+      <c r="AE4">
+        <v>10.53710454303009</v>
+      </c>
+      <c r="AF4">
+        <v>2048.53710454303</v>
+      </c>
+      <c r="AG4">
+        <v>-1490.46289545697</v>
+      </c>
+      <c r="AH4">
+        <v>0.2816308744752577</v>
+      </c>
+      <c r="AI4">
+        <v>0.3140224500472936</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.3990703888113302</v>
+      </c>
+      <c r="AK4">
+        <v>-0.4993949960240747</v>
+      </c>
+      <c r="AL4">
+        <v>120</v>
+      </c>
+      <c r="AM4">
+        <v>120</v>
+      </c>
+      <c r="AN4">
+        <v>11.3854748603352</v>
+      </c>
+      <c r="AO4">
+        <v>0.925</v>
+      </c>
+      <c r="AP4">
+        <v>-8.326608354508211</v>
+      </c>
+      <c r="AQ4">
+        <v>0.925</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Primerica, Inc. (NYSE:PRI)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0885</v>
+      </c>
+      <c r="E5">
+        <v>0.04849999999999999</v>
+      </c>
+      <c r="G5">
+        <v>0.2790719908218873</v>
+      </c>
+      <c r="H5">
+        <v>0.2790719908218873</v>
+      </c>
+      <c r="I5">
+        <v>0.3131160230204649</v>
+      </c>
+      <c r="J5">
+        <v>0.2405053770779137</v>
+      </c>
+      <c r="K5">
+        <v>455.4</v>
+      </c>
+      <c r="L5">
+        <v>0.1451289078683196</v>
+      </c>
+      <c r="M5">
+        <v>567.4</v>
+      </c>
+      <c r="N5">
+        <v>0.06264283427360146</v>
+      </c>
+      <c r="O5">
+        <v>1.245937637241985</v>
+      </c>
+      <c r="P5">
+        <v>105.5</v>
+      </c>
+      <c r="Q5">
+        <v>0.01164754849465096</v>
+      </c>
+      <c r="R5">
+        <v>0.2316644707949056</v>
+      </c>
+      <c r="S5">
+        <v>461.9</v>
+      </c>
+      <c r="T5">
+        <v>0.8140641522735284</v>
+      </c>
+      <c r="U5">
+        <v>550.1</v>
+      </c>
+      <c r="V5">
+        <v>0.06073285712708524</v>
+      </c>
+      <c r="W5">
+        <v>0.1969297297297297</v>
+      </c>
+      <c r="X5">
+        <v>0.08528653454865348</v>
+      </c>
+      <c r="Y5">
+        <v>0.1116431951810762</v>
+      </c>
+      <c r="Z5">
+        <v>0.8115574519105113</v>
+      </c>
+      <c r="AA5">
+        <v>0.1951839309921284</v>
+      </c>
+      <c r="AB5">
+        <v>0.07664485369689854</v>
+      </c>
+      <c r="AC5">
+        <v>0.1185390772952298</v>
+      </c>
+      <c r="AD5">
+        <v>2009.6</v>
+      </c>
+      <c r="AE5">
+        <v>61.4161568204157</v>
+      </c>
+      <c r="AF5">
+        <v>2071.016156820416</v>
+      </c>
+      <c r="AG5">
+        <v>1520.916156820416</v>
+      </c>
+      <c r="AH5">
+        <v>0.1860965926021178</v>
+      </c>
+      <c r="AI5">
+        <v>0.5154581683148386</v>
+      </c>
+      <c r="AJ5">
+        <v>0.1437726952442476</v>
+      </c>
+      <c r="AK5">
+        <v>0.4385930358887734</v>
+      </c>
+      <c r="AL5">
+        <v>89</v>
+      </c>
+      <c r="AM5">
+        <v>89</v>
+      </c>
+      <c r="AN5">
+        <v>1.968054372202799</v>
+      </c>
+      <c r="AO5">
+        <v>11.11685393258427</v>
+      </c>
+      <c r="AP5">
+        <v>1.489473373897441</v>
+      </c>
+      <c r="AQ5">
+        <v>11.11685393258427</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Globe Life Inc. (NYSE:GL)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.0515</v>
+      </c>
+      <c r="E6">
+        <v>0.08109999999999999</v>
+      </c>
+      <c r="F6">
+        <v>0.06</v>
+      </c>
+      <c r="G6">
+        <v>0.2302051505892623</v>
+      </c>
+      <c r="H6">
+        <v>0.2302051505892623</v>
+      </c>
+      <c r="I6">
+        <v>0.2576904454308274</v>
+      </c>
+      <c r="J6">
+        <v>0.2079988612760191</v>
+      </c>
+      <c r="K6">
+        <v>1090.4</v>
+      </c>
+      <c r="L6">
+        <v>0.1903797468354431</v>
+      </c>
+      <c r="M6">
+        <v>1182.1</v>
+      </c>
+      <c r="N6">
+        <v>0.1262711502307298</v>
+      </c>
+      <c r="O6">
+        <v>1.084097578870139</v>
+      </c>
+      <c r="P6">
+        <v>86.5</v>
+      </c>
+      <c r="Q6">
+        <v>0.009239873525893009</v>
+      </c>
+      <c r="R6">
+        <v>0.07932868672046954</v>
+      </c>
+      <c r="S6">
+        <v>1095.6</v>
+      </c>
+      <c r="T6">
+        <v>0.9268251416969799</v>
+      </c>
+      <c r="U6">
+        <v>134.5</v>
+      </c>
+      <c r="V6">
+        <v>0.01436720218766023</v>
+      </c>
+      <c r="W6">
+        <v>0.2358590556120352</v>
+      </c>
+      <c r="X6">
+        <v>0.08799618870454878</v>
+      </c>
+      <c r="Y6">
+        <v>0.1478628669074864</v>
+      </c>
+      <c r="Z6">
+        <v>0.9072922564335384</v>
+      </c>
+      <c r="AA6">
+        <v>0.1887157561827259</v>
+      </c>
+      <c r="AB6">
+        <v>0.0763005864792354</v>
+      </c>
+      <c r="AC6">
+        <v>0.1124151697034905</v>
+      </c>
+      <c r="AD6">
+        <v>3133.1</v>
+      </c>
+      <c r="AE6">
+        <v>10.83986897468264</v>
+      </c>
+      <c r="AF6">
+        <v>3143.939868974683</v>
+      </c>
+      <c r="AG6">
+        <v>3009.439868974683</v>
+      </c>
+      <c r="AH6">
+        <v>0.2514037700023303</v>
+      </c>
+      <c r="AI6">
+        <v>0.4039734998991895</v>
+      </c>
+      <c r="AJ6">
+        <v>0.2432649074652207</v>
+      </c>
+      <c r="AK6">
+        <v>0.3934916554479385</v>
+      </c>
+      <c r="AL6">
+        <v>117.1</v>
+      </c>
+      <c r="AM6">
+        <v>117.1</v>
+      </c>
+      <c r="AN6">
+        <v>2.090001267435577</v>
+      </c>
+      <c r="AO6">
+        <v>12.5935098206661</v>
+      </c>
+      <c r="AP6">
+        <v>2.007511136072339</v>
+      </c>
+      <c r="AQ6">
+        <v>12.5935098206661</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Unum Group (NYSE:UNM)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0156</v>
+      </c>
+      <c r="E7">
+        <v>0.108</v>
+      </c>
+      <c r="F7">
+        <v>0.0819</v>
+      </c>
+      <c r="G7">
+        <v>0.1519014051485644</v>
+      </c>
+      <c r="H7">
+        <v>0.1519014051485644</v>
+      </c>
+      <c r="I7">
+        <v>0.1918257593045163</v>
+      </c>
+      <c r="J7">
+        <v>0.1511770696510419</v>
+      </c>
+      <c r="K7">
+        <v>1761</v>
+      </c>
+      <c r="L7">
+        <v>0.1376232826396161</v>
+      </c>
+      <c r="M7">
+        <v>866.5999999999999</v>
+      </c>
+      <c r="N7">
+        <v>0.06498151633536041</v>
+      </c>
+      <c r="O7">
+        <v>0.492106757524134</v>
+      </c>
+      <c r="P7">
+        <v>290.7</v>
+      </c>
+      <c r="Q7">
+        <v>0.02179797691978914</v>
+      </c>
+      <c r="R7">
+        <v>0.1650766609880749</v>
+      </c>
+      <c r="S7">
+        <v>575.8999999999999</v>
+      </c>
+      <c r="T7">
+        <v>0.6645511193168704</v>
+      </c>
+      <c r="U7">
+        <v>163.4</v>
+      </c>
+      <c r="V7">
+        <v>0.01225245761504488</v>
+      </c>
+      <c r="W7">
+        <v>0.1830922947359666</v>
+      </c>
+      <c r="X7">
+        <v>0.0864466743729714</v>
+      </c>
+      <c r="Y7">
+        <v>0.09664562036299515</v>
+      </c>
+      <c r="Z7">
+        <v>0.9988930704233642</v>
+      </c>
+      <c r="AA7">
+        <v>0.1510097272813361</v>
+      </c>
+      <c r="AB7">
+        <v>0.07619422708741699</v>
+      </c>
+      <c r="AC7">
+        <v>0.07481550019391908</v>
+      </c>
+      <c r="AD7">
+        <v>3600.1</v>
+      </c>
+      <c r="AE7">
+        <v>61.17974545634936</v>
+      </c>
+      <c r="AF7">
+        <v>3661.279745456349</v>
+      </c>
+      <c r="AG7">
+        <v>3497.879745456349</v>
+      </c>
+      <c r="AH7">
+        <v>0.2154025973582818</v>
+      </c>
+      <c r="AI7">
+        <v>0.2505549843857204</v>
+      </c>
+      <c r="AJ7">
+        <v>0.2077868571987833</v>
+      </c>
+      <c r="AK7">
+        <v>0.2420798688291903</v>
+      </c>
+      <c r="AL7">
+        <v>197.8</v>
+      </c>
+      <c r="AM7">
+        <v>197.8</v>
+      </c>
+      <c r="AN7">
+        <v>1.392904124429312</v>
+      </c>
+      <c r="AO7">
+        <v>12.37411526794742</v>
+      </c>
+      <c r="AP7">
+        <v>1.353354385768146</v>
+      </c>
+      <c r="AQ7">
+        <v>12.37411526794742</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Citizens, Inc. (NYSE:CIA)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.00167</v>
+      </c>
+      <c r="G8">
+        <v>0.107487922705314</v>
+      </c>
+      <c r="H8">
+        <v>0.107487922705314</v>
+      </c>
+      <c r="I8">
+        <v>0.08021977507350404</v>
+      </c>
+      <c r="J8">
+        <v>0.08021977507350404</v>
+      </c>
+      <c r="K8">
+        <v>22</v>
+      </c>
+      <c r="L8">
+        <v>0.08856682769726248</v>
+      </c>
+      <c r="M8">
+        <v>0.2</v>
+      </c>
+      <c r="N8">
+        <v>0.0009995002498750627</v>
+      </c>
+      <c r="O8">
+        <v>0.009090909090909092</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>-0</v>
+      </c>
+      <c r="S8">
+        <v>0.2</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>32.4</v>
+      </c>
+      <c r="V8">
+        <v>0.1619190404797601</v>
+      </c>
+      <c r="W8">
+        <v>0.1440733464309103</v>
+      </c>
+      <c r="X8">
+        <v>0.08050027445490679</v>
+      </c>
+      <c r="Y8">
+        <v>0.06357307197600351</v>
+      </c>
+      <c r="Z8">
+        <v>1.727795196367828</v>
+      </c>
+      <c r="AA8">
+        <v>0.1386033420257079</v>
+      </c>
+      <c r="AB8">
+        <v>0.07909494276280413</v>
+      </c>
+      <c r="AC8">
+        <v>0.05950839926290377</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>7.867039358707961</v>
+      </c>
+      <c r="AF8">
+        <v>7.867039358707961</v>
+      </c>
+      <c r="AG8">
+        <v>-24.53296064129204</v>
+      </c>
+      <c r="AH8">
+        <v>0.03782829905626848</v>
+      </c>
+      <c r="AI8">
+        <v>0.03651156753312497</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.1397355718414079</v>
+      </c>
+      <c r="AK8">
+        <v>-0.1340108013284756</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>-1.110088716800544</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Aflac Incorporated (NYSE:AFL)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>-0.0454</v>
+      </c>
+      <c r="E9">
+        <v>0.04559999999999999</v>
+      </c>
+      <c r="F9">
+        <v>0.0785</v>
+      </c>
+      <c r="G9">
+        <v>0.317651138596694</v>
+      </c>
+      <c r="H9">
+        <v>0.317651138596694</v>
+      </c>
+      <c r="I9">
+        <v>0.2766378925691086</v>
+      </c>
+      <c r="J9">
+        <v>0.2304710701652963</v>
+      </c>
+      <c r="K9">
+        <v>3809</v>
+      </c>
+      <c r="L9">
+        <v>0.2201479597734366</v>
+      </c>
+      <c r="M9">
+        <v>3807</v>
+      </c>
+      <c r="N9">
+        <v>0.06625028931207244</v>
+      </c>
+      <c r="O9">
+        <v>0.9994749278025729</v>
+      </c>
+      <c r="P9">
+        <v>1056</v>
+      </c>
+      <c r="Q9">
+        <v>0.01837675479735973</v>
+      </c>
+      <c r="R9">
+        <v>0.2772381202415332</v>
+      </c>
+      <c r="S9">
+        <v>2751</v>
+      </c>
+      <c r="T9">
+        <v>0.7226162332545312</v>
+      </c>
+      <c r="U9">
+        <v>5612</v>
+      </c>
+      <c r="V9">
+        <v>0.09766131432081707</v>
+      </c>
+      <c r="W9">
+        <v>0.1680268207684503</v>
+      </c>
+      <c r="X9">
+        <v>0.08497819402351274</v>
+      </c>
+      <c r="Y9">
+        <v>0.08304862674493756</v>
+      </c>
+      <c r="Z9">
+        <v>0.5898263796460899</v>
+      </c>
+      <c r="AA9">
+        <v>0.1359379169287567</v>
+      </c>
+      <c r="AB9">
+        <v>0.07723742121363235</v>
+      </c>
+      <c r="AC9">
+        <v>0.05870049571512435</v>
+      </c>
+      <c r="AD9">
+        <v>12345</v>
+      </c>
+      <c r="AE9">
+        <v>93.05591384640999</v>
+      </c>
+      <c r="AF9">
+        <v>12438.05591384641</v>
+      </c>
+      <c r="AG9">
+        <v>6826.05591384641</v>
+      </c>
+      <c r="AH9">
+        <v>0.177935735148473</v>
+      </c>
+      <c r="AI9">
+        <v>0.3337457672221971</v>
+      </c>
+      <c r="AJ9">
+        <v>0.1061760864013324</v>
+      </c>
+      <c r="AK9">
+        <v>0.2156319136036363</v>
+      </c>
+      <c r="AL9">
+        <v>194</v>
+      </c>
+      <c r="AM9">
+        <v>194</v>
+      </c>
+      <c r="AN9">
+        <v>2.562106967187597</v>
+      </c>
+      <c r="AO9">
+        <v>24.56701030927835</v>
+      </c>
+      <c r="AP9">
+        <v>1.416693836798541</v>
+      </c>
+      <c r="AQ9">
+        <v>24.56701030927835</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kansas City Life Insurance Company (OTCPK:KCLI)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.0193</v>
+      </c>
+      <c r="E10">
+        <v>0.263</v>
+      </c>
+      <c r="G10">
+        <v>0.1329057544984857</v>
+      </c>
+      <c r="H10">
+        <v>0.1329057544984857</v>
+      </c>
+      <c r="I10">
+        <v>0.1273828612150365</v>
+      </c>
+      <c r="J10">
+        <v>0.1010154997327632</v>
+      </c>
+      <c r="K10">
+        <v>56.7</v>
+      </c>
+      <c r="L10">
+        <v>0.1010154997327632</v>
+      </c>
+      <c r="M10">
+        <v>5.42</v>
+      </c>
+      <c r="N10">
+        <v>0.01526330611095466</v>
+      </c>
+      <c r="O10">
+        <v>0.09559082892416225</v>
+      </c>
+      <c r="P10">
+        <v>5.42</v>
+      </c>
+      <c r="Q10">
+        <v>0.01526330611095466</v>
+      </c>
+      <c r="R10">
+        <v>0.09559082892416225</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>7.58</v>
+      </c>
+      <c r="V10">
+        <v>0.0213460996902281</v>
+      </c>
+      <c r="W10">
+        <v>0.126477805041267</v>
+      </c>
+      <c r="X10">
+        <v>0.07950638590704137</v>
+      </c>
+      <c r="Y10">
+        <v>0.04697141913422564</v>
+      </c>
+      <c r="Z10">
+        <v>1.275247074860843</v>
+      </c>
+      <c r="AA10">
+        <v>0.1288197205498126</v>
+      </c>
+      <c r="AB10">
+        <v>0.07950638590704137</v>
+      </c>
+      <c r="AC10">
+        <v>0.04931333464277118</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>-7.58</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>-0.02181169429097606</v>
+      </c>
+      <c r="AK10">
+        <v>-0.01174611045682762</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>-0.10066401062417</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Prudential Financial, Inc. (NYSE:PRU)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.0256</v>
+      </c>
+      <c r="E11">
+        <v>0.0101</v>
+      </c>
+      <c r="F11">
+        <v>0.0322</v>
+      </c>
+      <c r="G11">
+        <v>0.04495655510785846</v>
+      </c>
+      <c r="H11">
+        <v>0.04495655510785846</v>
+      </c>
+      <c r="I11">
+        <v>0.07233765567915854</v>
+      </c>
+      <c r="J11">
+        <v>0.05756397799046221</v>
+      </c>
+      <c r="K11">
+        <v>4101</v>
+      </c>
+      <c r="L11">
+        <v>0.05620425951813173</v>
+      </c>
+      <c r="M11">
+        <v>2883</v>
+      </c>
+      <c r="N11">
+        <v>0.06832287832934804</v>
+      </c>
+      <c r="O11">
+        <v>0.7029992684711046</v>
+      </c>
+      <c r="P11">
+        <v>1879</v>
+      </c>
+      <c r="Q11">
+        <v>0.044529548519197</v>
+      </c>
+      <c r="R11">
+        <v>0.4581809314801268</v>
+      </c>
+      <c r="S11">
+        <v>1004</v>
+      </c>
+      <c r="T11">
+        <v>0.3482483524106833</v>
+      </c>
+      <c r="U11">
+        <v>20198</v>
+      </c>
+      <c r="V11">
+        <v>0.4786630234117834</v>
+      </c>
+      <c r="W11">
+        <v>0.1588672813202138</v>
+      </c>
+      <c r="X11">
+        <v>0.1072989870648406</v>
+      </c>
+      <c r="Y11">
+        <v>0.05156829425537324</v>
+      </c>
+      <c r="Z11">
+        <v>1.774764814000851</v>
+      </c>
+      <c r="AA11">
+        <v>0.1021625226913917</v>
+      </c>
+      <c r="AB11">
+        <v>0.07145407078975322</v>
+      </c>
+      <c r="AC11">
+        <v>0.03070845190163853</v>
+      </c>
+      <c r="AD11">
+        <v>46097</v>
+      </c>
+      <c r="AE11">
+        <v>294.0530785725928</v>
+      </c>
+      <c r="AF11">
+        <v>46391.05307857259</v>
+      </c>
+      <c r="AG11">
+        <v>26193.05307857259</v>
+      </c>
+      <c r="AH11">
+        <v>0.5236734364108571</v>
+      </c>
+      <c r="AI11">
+        <v>0.5874809651738918</v>
+      </c>
+      <c r="AJ11">
+        <v>0.3829967487743309</v>
+      </c>
+      <c r="AK11">
+        <v>0.4457022430801411</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>8.133855627900411</v>
+      </c>
+      <c r="AP11">
+        <v>4.621786931796904</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CNO Financial Group, Inc. (NYSE:CNO)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.0396</v>
+      </c>
+      <c r="E12">
+        <v>0.114</v>
+      </c>
+      <c r="G12">
+        <v>0.1907667816396922</v>
+      </c>
+      <c r="H12">
+        <v>0.1907667816396922</v>
+      </c>
+      <c r="I12">
+        <v>0.1359437455424685</v>
+      </c>
+      <c r="J12">
+        <v>0.1053285533420312</v>
+      </c>
+      <c r="K12">
+        <v>274.2</v>
+      </c>
+      <c r="L12">
+        <v>0.0606261607853542</v>
+      </c>
+      <c r="M12">
+        <v>346.8</v>
+      </c>
+      <c r="N12">
+        <v>0.09030309342776795</v>
+      </c>
+      <c r="O12">
+        <v>1.264770240700219</v>
+      </c>
+      <c r="P12">
+        <v>68</v>
+      </c>
+      <c r="Q12">
+        <v>0.01770648890740548</v>
+      </c>
+      <c r="R12">
+        <v>0.2479941648431802</v>
+      </c>
+      <c r="S12">
+        <v>278.8</v>
+      </c>
+      <c r="T12">
+        <v>0.803921568627451</v>
+      </c>
+      <c r="U12">
+        <v>1164.7</v>
+      </c>
+      <c r="V12">
+        <v>0.30327570044787</v>
+      </c>
+      <c r="W12">
+        <v>0.145071689328607</v>
+      </c>
+      <c r="X12">
+        <v>0.1084116577248857</v>
+      </c>
+      <c r="Y12">
+        <v>0.03666003160372125</v>
+      </c>
+      <c r="Z12">
+        <v>0.7985778381321801</v>
+      </c>
+      <c r="AA12">
+        <v>0.08411304842146931</v>
+      </c>
+      <c r="AB12">
+        <v>0.0713036693177076</v>
+      </c>
+      <c r="AC12">
+        <v>0.01280937910376172</v>
+      </c>
+      <c r="AD12">
+        <v>4304.9</v>
+      </c>
+      <c r="AE12">
+        <v>86.26813830261786</v>
+      </c>
+      <c r="AF12">
+        <v>4391.168138302617</v>
+      </c>
+      <c r="AG12">
+        <v>3226.468138302617</v>
+      </c>
+      <c r="AH12">
+        <v>0.5334546303358541</v>
+      </c>
+      <c r="AI12">
+        <v>0.6203118946874542</v>
+      </c>
+      <c r="AJ12">
+        <v>0.4565626632843299</v>
+      </c>
+      <c r="AK12">
+        <v>0.5455397122438562</v>
+      </c>
+      <c r="AL12">
+        <v>256.1</v>
+      </c>
+      <c r="AM12">
+        <v>256.1</v>
+      </c>
+      <c r="AN12">
+        <v>4.693012100730404</v>
+      </c>
+      <c r="AO12">
+        <v>2.381882077313549</v>
+      </c>
+      <c r="AP12">
+        <v>3.517353252264926</v>
+      </c>
+      <c r="AQ12">
+        <v>2.381882077313549</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MetLife, Inc. (NYSE:MET)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.00924</v>
+      </c>
+      <c r="E13">
+        <v>-0.126</v>
+      </c>
+      <c r="F13">
+        <v>0.14</v>
+      </c>
+      <c r="G13">
+        <v>0.04099854227405248</v>
+      </c>
+      <c r="H13">
+        <v>0.04099854227405248</v>
+      </c>
+      <c r="I13">
+        <v>0.0885340036049079</v>
+      </c>
+      <c r="J13">
+        <v>0.06463221451898235</v>
+      </c>
+      <c r="K13">
+        <v>3762</v>
+      </c>
+      <c r="L13">
+        <v>0.05273043283247365</v>
+      </c>
+      <c r="M13">
+        <v>5195</v>
+      </c>
+      <c r="N13">
+        <v>0.0916300087837814</v>
+      </c>
+      <c r="O13">
+        <v>1.380914407230197</v>
+      </c>
+      <c r="P13">
+        <v>1535</v>
+      </c>
+      <c r="Q13">
+        <v>0.02707450692648786</v>
+      </c>
+      <c r="R13">
+        <v>0.4080276448697501</v>
+      </c>
+      <c r="S13">
+        <v>3660</v>
+      </c>
+      <c r="T13">
+        <v>0.7045235803657363</v>
+      </c>
+      <c r="U13">
+        <v>21765</v>
+      </c>
+      <c r="V13">
+        <v>0.3838935786677579</v>
+      </c>
+      <c r="W13">
+        <v>0.1466209369397459</v>
+      </c>
+      <c r="X13">
+        <v>0.1010896537781224</v>
+      </c>
+      <c r="Y13">
+        <v>0.04553128316162353</v>
+      </c>
+      <c r="Z13">
+        <v>0.6485337663455478</v>
+      </c>
+      <c r="AA13">
+        <v>0.04191617350924902</v>
+      </c>
+      <c r="AB13">
+        <v>0.0724245346618433</v>
+      </c>
+      <c r="AC13">
+        <v>-0.03050836115259428</v>
+      </c>
+      <c r="AD13">
+        <v>47202</v>
+      </c>
+      <c r="AE13">
+        <v>1203.150234057254</v>
+      </c>
+      <c r="AF13">
+        <v>48405.15023405726</v>
+      </c>
+      <c r="AG13">
+        <v>26640.15023405726</v>
+      </c>
+      <c r="AH13">
+        <v>0.4605603883734172</v>
+      </c>
+      <c r="AI13">
+        <v>0.6083406708714459</v>
+      </c>
+      <c r="AJ13">
+        <v>0.319673298601082</v>
+      </c>
+      <c r="AK13">
+        <v>0.4608691612312867</v>
+      </c>
+      <c r="AL13">
+        <v>1047</v>
+      </c>
+      <c r="AM13">
+        <v>1047</v>
+      </c>
+      <c r="AN13">
+        <v>6.482010436693217</v>
+      </c>
+      <c r="AO13">
+        <v>6.027698185291309</v>
+      </c>
+      <c r="AP13">
+        <v>3.658356252960348</v>
+      </c>
+      <c r="AQ13">
+        <v>6.027698185291309</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Genworth Financial, Inc. (NYSE:GNW)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>-0.0158</v>
+      </c>
+      <c r="E14">
+        <v>0.232</v>
+      </c>
+      <c r="G14">
+        <v>0.06113654726636143</v>
+      </c>
+      <c r="H14">
+        <v>0.06113654726636143</v>
+      </c>
+      <c r="I14">
+        <v>0.05580862132007925</v>
+      </c>
+      <c r="J14">
+        <v>0.03818484616637002</v>
+      </c>
+      <c r="K14">
+        <v>88</v>
+      </c>
+      <c r="L14">
+        <v>0.01185025585779693</v>
+      </c>
+      <c r="M14">
+        <v>170</v>
+      </c>
+      <c r="N14">
+        <v>0.05695142378559464</v>
+      </c>
+      <c r="O14">
+        <v>1.931818181818182</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>-0</v>
+      </c>
+      <c r="S14">
+        <v>170</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>2057</v>
+      </c>
+      <c r="V14">
+        <v>0.6891122278056951</v>
+      </c>
+      <c r="W14">
+        <v>0.01092353525322741</v>
+      </c>
+      <c r="X14">
+        <v>0.09711184010173513</v>
+      </c>
+      <c r="Y14">
+        <v>-0.08618830484850772</v>
+      </c>
+      <c r="Z14">
+        <v>0.8633050813432858</v>
+      </c>
+      <c r="AA14">
+        <v>0.03296517172573892</v>
+      </c>
+      <c r="AB14">
+        <v>0.07427153986899571</v>
+      </c>
+      <c r="AC14">
+        <v>-0.04130636814325678</v>
+      </c>
+      <c r="AD14">
+        <v>2026</v>
+      </c>
+      <c r="AE14">
+        <v>52.82589038545757</v>
+      </c>
+      <c r="AF14">
+        <v>2078.825890385458</v>
+      </c>
+      <c r="AG14">
+        <v>21.82589038545757</v>
+      </c>
+      <c r="AH14">
+        <v>0.4105247564558776</v>
+      </c>
+      <c r="AI14">
+        <v>0.1834178423500343</v>
+      </c>
+      <c r="AJ14">
+        <v>0.007258780914201726</v>
+      </c>
+      <c r="AK14">
+        <v>0.002352732566435036</v>
+      </c>
+      <c r="AL14">
+        <v>118</v>
+      </c>
+      <c r="AM14">
+        <v>118</v>
+      </c>
+      <c r="AN14">
+        <v>4.469446282814912</v>
+      </c>
+      <c r="AO14">
+        <v>3.516949152542373</v>
+      </c>
+      <c r="AP14">
+        <v>0.04814888679783271</v>
+      </c>
+      <c r="AQ14">
+        <v>3.516949152542373</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Principal Financial Group, Inc. (NasdaqGS:PFG)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>-0.0248</v>
+      </c>
+      <c r="F15">
+        <v>0.122</v>
+      </c>
+      <c r="G15">
+        <v>0.07397717982440549</v>
+      </c>
+      <c r="H15">
+        <v>0.07397717982440549</v>
+      </c>
+      <c r="I15">
+        <v>-0.01827819526900851</v>
+      </c>
+      <c r="J15">
+        <v>-0.01827819526900851</v>
+      </c>
+      <c r="K15">
+        <v>-206.1</v>
+      </c>
+      <c r="L15">
+        <v>-0.01465183236768208</v>
+      </c>
+      <c r="M15">
+        <v>1638.7</v>
+      </c>
+      <c r="N15">
+        <v>0.09255211598524769</v>
+      </c>
+      <c r="O15">
+        <v>-7.950994662785056</v>
+      </c>
+      <c r="P15">
+        <v>651.7</v>
+      </c>
+      <c r="Q15">
+        <v>0.03680735582326596</v>
+      </c>
+      <c r="R15">
+        <v>-3.162057253760311</v>
+      </c>
+      <c r="S15">
+        <v>987</v>
+      </c>
+      <c r="T15">
+        <v>0.6023067065356685</v>
+      </c>
+      <c r="U15">
+        <v>6174.5</v>
+      </c>
+      <c r="V15">
+        <v>0.3487295051875949</v>
+      </c>
+      <c r="W15">
+        <v>-0.01931294276397166</v>
+      </c>
+      <c r="X15">
+        <v>0.08574798567603609</v>
+      </c>
+      <c r="Y15">
+        <v>-0.1050609284400078</v>
+      </c>
+      <c r="Z15">
+        <v>1.527116398622451</v>
+      </c>
+      <c r="AA15">
+        <v>-0.0279129317325262</v>
+      </c>
+      <c r="AB15">
+        <v>0.07646164189495078</v>
+      </c>
+      <c r="AC15">
+        <v>-0.104374573627477</v>
+      </c>
+      <c r="AD15">
+        <v>4203.5</v>
+      </c>
+      <c r="AE15">
+        <v>168.0511687575409</v>
+      </c>
+      <c r="AF15">
+        <v>4371.551168757541</v>
+      </c>
+      <c r="AG15">
+        <v>-1802.948831242459</v>
+      </c>
+      <c r="AH15">
+        <v>0.1980115701606869</v>
+      </c>
+      <c r="AI15">
+        <v>0.2738251991871012</v>
+      </c>
+      <c r="AJ15">
+        <v>-0.1133733913151155</v>
+      </c>
+      <c r="AK15">
+        <v>-0.1841575665592722</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>132.185534591195</v>
+      </c>
+      <c r="AP15">
+        <v>-56.69650412712137</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Lincoln National Corporation (NYSE:LNC)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>-0.0493</v>
+      </c>
+      <c r="E16">
+        <v>-0.162</v>
+      </c>
+      <c r="F16">
+        <v>0.17</v>
+      </c>
+      <c r="G16">
+        <v>-0.2267257290513104</v>
+      </c>
+      <c r="H16">
+        <v>-0.2267257290513104</v>
+      </c>
+      <c r="I16">
+        <v>-0.06200361729838328</v>
+      </c>
+      <c r="J16">
+        <v>-0.06200361729838328</v>
+      </c>
+      <c r="K16">
+        <v>353</v>
+      </c>
+      <c r="L16">
+        <v>0.02606127722406792</v>
+      </c>
+      <c r="M16">
+        <v>306</v>
+      </c>
+      <c r="N16">
+        <v>0.05664883277486717</v>
+      </c>
+      <c r="O16">
+        <v>0.8668555240793201</v>
+      </c>
+      <c r="P16">
+        <v>306</v>
+      </c>
+      <c r="Q16">
+        <v>0.05664883277486717</v>
+      </c>
+      <c r="R16">
+        <v>0.8668555240793201</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>6013</v>
+      </c>
+      <c r="V16">
+        <v>1.113168076716589</v>
+      </c>
+      <c r="W16">
+        <v>0.1595119746949842</v>
+      </c>
+      <c r="X16">
+        <v>0.1104933742458954</v>
+      </c>
+      <c r="Y16">
+        <v>0.04901860044908876</v>
+      </c>
+      <c r="Z16">
+        <v>1.899934008690472</v>
+      </c>
+      <c r="AA16">
+        <v>-0.1178027811670272</v>
+      </c>
+      <c r="AB16">
+        <v>0.07248388369537404</v>
+      </c>
+      <c r="AC16">
+        <v>-0.1902866648624013</v>
+      </c>
+      <c r="AD16">
+        <v>6482</v>
+      </c>
+      <c r="AE16">
+        <v>139.1949815330074</v>
+      </c>
+      <c r="AF16">
+        <v>6621.194981533007</v>
+      </c>
+      <c r="AG16">
+        <v>608.1949815330072</v>
+      </c>
+      <c r="AH16">
+        <v>0.5507155299703663</v>
+      </c>
+      <c r="AI16">
+        <v>0.4235072537699519</v>
+      </c>
+      <c r="AJ16">
+        <v>0.1011989366539428</v>
+      </c>
+      <c r="AK16">
+        <v>0.06321407919706243</v>
+      </c>
+      <c r="AL16">
+        <v>334</v>
+      </c>
+      <c r="AM16">
+        <v>334</v>
+      </c>
+      <c r="AN16">
+        <v>-7.968039336201598</v>
+      </c>
+      <c r="AO16">
+        <v>-2.559880239520958</v>
+      </c>
+      <c r="AP16">
+        <v>-0.7476275126404514</v>
+      </c>
+      <c r="AQ16">
+        <v>-2.559880239520958</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>Brighthouse Financial, Inc. (NasdaqGS:BHF)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D17">
         <v>-0.137</v>
       </c>
-      <c r="F4">
+      <c r="F17">
         <v>0.13</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <v>-0.3018518518518519</v>
       </c>
-      <c r="J4">
+      <c r="J17">
         <v>-0.3018518518518519</v>
       </c>
-      <c r="K4">
+      <c r="K17">
         <v>-1200</v>
       </c>
-      <c r="L4">
+      <c r="L17">
         <v>-0.2469135802469136</v>
       </c>
-      <c r="M4">
+      <c r="M17">
         <v>250</v>
       </c>
-      <c r="N4">
+      <c r="N17">
         <v>0.08767622922073368</v>
       </c>
-      <c r="O4">
+      <c r="O17">
         <v>-0.2083333333333333</v>
       </c>
-      <c r="P4">
+      <c r="P17">
         <v>-0</v>
       </c>
-      <c r="Q4">
+      <c r="Q17">
         <v>-0</v>
       </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
         <v>250</v>
       </c>
-      <c r="T4">
+      <c r="T17">
         <v>1</v>
       </c>
-      <c r="U4">
+      <c r="U17">
         <v>5630</v>
       </c>
-      <c r="V4">
+      <c r="V17">
         <v>1.974468682050922</v>
       </c>
-      <c r="W4">
+      <c r="W17">
         <v>-0.2949127549766528</v>
       </c>
-      <c r="X4">
-        <v>0.1549797523460257</v>
-      </c>
-      <c r="Y4">
-        <v>-0.4498925073226785</v>
-      </c>
-      <c r="Z4">
+      <c r="X17">
+        <v>0.154909559472497</v>
+      </c>
+      <c r="Y17">
+        <v>-0.4498223144491498</v>
+      </c>
+      <c r="Z17">
         <v>0.4497501388117712</v>
       </c>
-      <c r="AA4">
+      <c r="AA17">
         <v>-0.1357579122709606</v>
       </c>
-      <c r="AB4">
-        <v>0.07059198036696997</v>
-      </c>
-      <c r="AC4">
-        <v>-0.2063498926379305</v>
-      </c>
-      <c r="AD4">
+      <c r="AB17">
+        <v>0.07057435612340865</v>
+      </c>
+      <c r="AC17">
+        <v>-0.2063322683943692</v>
+      </c>
+      <c r="AD17">
         <v>8505</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
         <v>8505</v>
       </c>
-      <c r="AG4">
+      <c r="AG17">
         <v>2875</v>
       </c>
-      <c r="AH4">
+      <c r="AH17">
         <v>0.7489169102884717</v>
       </c>
-      <c r="AI4">
+      <c r="AI17">
         <v>0.6034054629301171</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ17">
         <v>0.5020606314613021</v>
       </c>
-      <c r="AK4">
+      <c r="AK17">
         <v>0.3396337861783816</v>
       </c>
-      <c r="AL4">
+      <c r="AL17">
         <v>171</v>
       </c>
-      <c r="AM4">
+      <c r="AM17">
         <v>171</v>
       </c>
-      <c r="AO4">
+      <c r="AO17">
         <v>-8.578947368421053</v>
       </c>
-      <c r="AQ4">
+      <c r="AQ17">
         <v>-8.578947368421053</v>
       </c>
     </row>
